--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4278" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4118" uniqueCount="197">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -607,37 +607,13 @@
     <t>184.24408</t>
   </si>
   <si>
-    <t>TVS-RM-KDK-20</t>
-  </si>
-  <si>
-    <t>685</t>
-  </si>
-  <si>
-    <t>147.08442</t>
-  </si>
-  <si>
     <t>189.55072</t>
   </si>
   <si>
     <t>190.42571</t>
   </si>
   <si>
-    <t>14048</t>
-  </si>
-  <si>
-    <t>120.68321</t>
-  </si>
-  <si>
     <t>57.048</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>38.334</t>
-  </si>
-  <si>
-    <t>56.89696</t>
   </si>
   <si>
     <t>71.668</t>
@@ -646,130 +622,7 @@
     <t>56.96721</t>
   </si>
   <si>
-    <t>14050</t>
-  </si>
-  <si>
-    <t>120.70622</t>
-  </si>
-  <si>
-    <t>14052</t>
-  </si>
-  <si>
-    <t>120.72922</t>
-  </si>
-  <si>
-    <t>14054</t>
-  </si>
-  <si>
-    <t>120.75222</t>
-  </si>
-  <si>
-    <t>14056</t>
-  </si>
-  <si>
-    <t>120.77521</t>
-  </si>
-  <si>
-    <t>14058</t>
-  </si>
-  <si>
-    <t>120.79819</t>
-  </si>
-  <si>
-    <t>14060</t>
-  </si>
-  <si>
-    <t>120.82117</t>
-  </si>
-  <si>
-    <t>14062</t>
-  </si>
-  <si>
-    <t>120.84414</t>
-  </si>
-  <si>
-    <t>14064</t>
-  </si>
-  <si>
-    <t>120.8671</t>
-  </si>
-  <si>
-    <t>14066</t>
-  </si>
-  <si>
-    <t>120.89006</t>
-  </si>
-  <si>
-    <t>14070</t>
-  </si>
-  <si>
-    <t>120.93595</t>
-  </si>
-  <si>
-    <t>14072</t>
-  </si>
-  <si>
-    <t>120.95889</t>
-  </si>
-  <si>
-    <t>14074</t>
-  </si>
-  <si>
-    <t>120.98182</t>
-  </si>
-  <si>
-    <t>14076</t>
-  </si>
-  <si>
-    <t>121.00475</t>
-  </si>
-  <si>
-    <t>14078</t>
-  </si>
-  <si>
-    <t>121.02767</t>
-  </si>
-  <si>
-    <t>14080</t>
-  </si>
-  <si>
-    <t>121.05058</t>
-  </si>
-  <si>
-    <t>14082</t>
-  </si>
-  <si>
-    <t>121.07349</t>
-  </si>
-  <si>
-    <t>14084</t>
-  </si>
-  <si>
-    <t>121.09639</t>
-  </si>
-  <si>
-    <t>14086</t>
-  </si>
-  <si>
-    <t>121.11928</t>
-  </si>
-  <si>
-    <t>14088</t>
-  </si>
-  <si>
-    <t>121.14217</t>
-  </si>
-  <si>
     <t>14090</t>
-  </si>
-  <si>
-    <t>121.19751</t>
-  </si>
-  <si>
-    <t>689</t>
-  </si>
-  <si>
-    <t>146.93409</t>
   </si>
   <si>
     <t>121.22038</t>
@@ -779,6 +632,15 @@
   </si>
   <si>
     <t>146.85967</t>
+  </si>
+  <si>
+    <t>TVS-SER-10001-PriceList</t>
+  </si>
+  <si>
+    <t>TVS-SER-10001-RateContract</t>
+  </si>
+  <si>
+    <t>TVS-RM-KDK-101</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1427,7 @@
   <dimension ref="A8:BR37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="27.28515625"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:70" ht="15.75" thickBot="1"/>
@@ -1733,10 +1595,10 @@
       <c r="AT9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU9" t="s" s="0">
+      <c r="AU9" t="s">
         <v>127</v>
       </c>
-      <c r="AV9" t="s" s="0">
+      <c r="AV9" t="s">
         <v>143</v>
       </c>
       <c r="AW9" s="48">
@@ -1777,10 +1639,10 @@
       <c r="BL9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" t="s" s="0">
+      <c r="BM9" t="s">
         <v>146</v>
       </c>
-      <c r="BN9" t="s" s="0">
+      <c r="BN9" t="s">
         <v>147</v>
       </c>
       <c r="BO9" s="48" t="e">
@@ -1952,20 +1814,20 @@
       <c r="AQ15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR15" t="e" s="0">
+      <c r="AR15" t="e">
         <f>ROUND(AN15+AO15+AP15,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS15" t="s" s="0">
+      <c r="AS15" t="s">
         <v>107</v>
       </c>
       <c r="AT15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU15" t="s" s="0">
+      <c r="AU15" t="s">
         <v>131</v>
       </c>
-      <c r="AV15" t="s" s="0">
+      <c r="AV15" t="s">
         <v>149</v>
       </c>
       <c r="AW15" s="48">
@@ -2004,10 +1866,10 @@
       <c r="BL15" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM15" t="s" s="0">
+      <c r="BM15" t="s">
         <v>149</v>
       </c>
-      <c r="BN15" t="s" s="0">
+      <c r="BN15" t="s">
         <v>150</v>
       </c>
       <c r="BO15" s="48" t="e">
@@ -2177,20 +2039,20 @@
       <c r="AQ16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR16" s="0">
+      <c r="AR16">
         <f>ROUND(AN16+AO16+AP16,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS16" t="s" s="0">
+      <c r="AS16" t="s">
         <v>107</v>
       </c>
       <c r="AT16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU16" t="s" s="0">
+      <c r="AU16" t="s">
         <v>135</v>
       </c>
-      <c r="AV16" t="s" s="0">
+      <c r="AV16" t="s">
         <v>136</v>
       </c>
       <c r="AW16" s="48">
@@ -2229,10 +2091,10 @@
       <c r="BL16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM16" t="s" s="0">
+      <c r="BM16" t="s">
         <v>134</v>
       </c>
-      <c r="BN16" t="s" s="0">
+      <c r="BN16" t="s">
         <v>133</v>
       </c>
       <c r="BO16" s="48">
@@ -2402,20 +2264,20 @@
       <c r="AQ17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR17" s="0">
+      <c r="AR17">
         <f>ROUND(AN17+AO17+AP17,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS17" t="s" s="0">
+      <c r="AS17" t="s">
         <v>107</v>
       </c>
       <c r="AT17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU17" t="s" s="0">
+      <c r="AU17" t="s">
         <v>108</v>
       </c>
-      <c r="AV17" t="s" s="0">
+      <c r="AV17" t="s">
         <v>132</v>
       </c>
       <c r="AW17" s="48">
@@ -2621,20 +2483,20 @@
       <c r="AQ18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR18" s="0">
+      <c r="AR18">
         <f>ROUND(AN18+AO18+AP18,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS18" t="s" s="0">
+      <c r="AS18" t="s">
         <v>107</v>
       </c>
       <c r="AT18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU18" t="s" s="0">
+      <c r="AU18" t="s">
         <v>130</v>
       </c>
-      <c r="AV18" t="s" s="0">
+      <c r="AV18" t="s">
         <v>137</v>
       </c>
       <c r="AW18" s="48">
@@ -2673,10 +2535,10 @@
       <c r="BL18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM18" t="s" s="0">
+      <c r="BM18" t="s">
         <v>153</v>
       </c>
-      <c r="BN18" t="s" s="0">
+      <c r="BN18" t="s">
         <v>152</v>
       </c>
       <c r="BO18" s="48">
@@ -2847,20 +2709,20 @@
       <c r="AQ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR20" t="e" s="0">
+      <c r="AR20" t="e">
         <f>ROUND(AN20+AO20+AP20,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS20" t="s" s="0">
+      <c r="AS20" t="s">
         <v>107</v>
       </c>
       <c r="AT20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU20" t="s" s="0">
+      <c r="AU20" t="s">
         <v>155</v>
       </c>
-      <c r="AV20" t="s" s="0">
+      <c r="AV20" t="s">
         <v>156</v>
       </c>
       <c r="AW20" s="48">
@@ -2899,10 +2761,10 @@
       <c r="BL20" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM20" t="s" s="0">
+      <c r="BM20" t="s">
         <v>156</v>
       </c>
-      <c r="BN20" t="s" s="0">
+      <c r="BN20" t="s">
         <v>127</v>
       </c>
       <c r="BO20" s="48" t="e">
@@ -3072,20 +2934,20 @@
       <c r="AQ21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" t="e" s="0">
+      <c r="AR21" t="e">
         <f t="shared" ref="AR21:AR23" si="30">ROUND(AN21+AO21+AP21,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS21" t="s" s="0">
+      <c r="AS21" t="s">
         <v>107</v>
       </c>
       <c r="AT21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU21" t="s" s="0">
+      <c r="AU21" t="s">
         <v>131</v>
       </c>
-      <c r="AV21" t="s" s="0">
+      <c r="AV21" t="s">
         <v>157</v>
       </c>
       <c r="AW21" s="48">
@@ -3124,10 +2986,10 @@
       <c r="BL21" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM21" t="s" s="0">
+      <c r="BM21" t="s">
         <v>108</v>
       </c>
-      <c r="BN21" t="s" s="0">
+      <c r="BN21" t="s">
         <v>108</v>
       </c>
       <c r="BO21" s="48" t="e">
@@ -3297,20 +3159,20 @@
       <c r="AQ22" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR22" t="e" s="0">
+      <c r="AR22" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS22" t="s" s="0">
+      <c r="AS22" t="s">
         <v>107</v>
       </c>
       <c r="AT22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU22" t="s" s="0">
+      <c r="AU22" t="s">
         <v>158</v>
       </c>
-      <c r="AV22" t="s" s="0">
+      <c r="AV22" t="s">
         <v>159</v>
       </c>
       <c r="AW22" s="48">
@@ -3349,10 +3211,10 @@
       <c r="BL22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM22" t="s" s="0">
+      <c r="BM22" t="s">
         <v>108</v>
       </c>
-      <c r="BN22" t="s" s="0">
+      <c r="BN22" t="s">
         <v>108</v>
       </c>
       <c r="BO22" s="48" t="e">
@@ -3522,20 +3384,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" t="e" s="0">
+      <c r="AR23" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>160</v>
       </c>
       <c r="AW23" s="48">
@@ -3574,10 +3436,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48" t="e">
@@ -3634,14 +3496,14 @@
       <c r="F31" s="46">
         <v>2</v>
       </c>
-      <c r="G31" t="s" s="0">
+      <c r="G31" t="s">
         <v>128</v>
       </c>
       <c r="H31" s="46">
         <f>F31*G31</f>
         <v>600</v>
       </c>
-      <c r="I31" t="s" s="0">
+      <c r="I31" t="s">
         <v>127</v>
       </c>
       <c r="J31" s="46">
@@ -3769,20 +3631,20 @@
       <c r="AQ31" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR31" s="0">
+      <c r="AR31">
         <f>ROUND(AN31+AO31+AP31,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS31" t="s" s="0">
+      <c r="AS31" t="s">
         <v>107</v>
       </c>
       <c r="AT31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU31" t="s" s="0">
+      <c r="AU31" t="s">
         <v>162</v>
       </c>
-      <c r="AV31" t="s" s="0">
+      <c r="AV31" t="s">
         <v>170</v>
       </c>
       <c r="AW31" s="48">
@@ -3821,10 +3683,10 @@
       <c r="BL31" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM31" t="s" s="0">
+      <c r="BM31" t="s">
         <v>108</v>
       </c>
-      <c r="BN31" t="s" s="0">
+      <c r="BN31" t="s">
         <v>108</v>
       </c>
       <c r="BO31" s="48">
@@ -3859,14 +3721,14 @@
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" t="s" s="0">
+      <c r="G32" t="s">
         <v>129</v>
       </c>
       <c r="H32" s="46">
         <f>F32*G32</f>
         <v>800</v>
       </c>
-      <c r="I32" t="s" s="0">
+      <c r="I32" t="s">
         <v>127</v>
       </c>
       <c r="J32" s="46">
@@ -3994,20 +3856,20 @@
       <c r="AQ32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR32" s="0">
+      <c r="AR32">
         <f>ROUND(AN32+AO32+AP32,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS32" t="s" s="0">
+      <c r="AS32" t="s">
         <v>107</v>
       </c>
       <c r="AT32" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU32" t="s" s="0">
+      <c r="AU32" t="s">
         <v>171</v>
       </c>
-      <c r="AV32" t="s" s="0">
+      <c r="AV32" t="s">
         <v>172</v>
       </c>
       <c r="AW32" s="48">
@@ -4046,10 +3908,10 @@
       <c r="BL32" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM32" t="s" s="0">
+      <c r="BM32" t="s">
         <v>108</v>
       </c>
-      <c r="BN32" t="s" s="0">
+      <c r="BN32" t="s">
         <v>108</v>
       </c>
       <c r="BO32" s="48">
@@ -4084,14 +3946,14 @@
       <c r="F33" s="46">
         <v>2</v>
       </c>
-      <c r="G33" t="s" s="0">
+      <c r="G33" t="s">
         <v>161</v>
       </c>
       <c r="H33" s="46">
         <f>F33*G33</f>
         <v>1000</v>
       </c>
-      <c r="I33" t="s" s="0">
+      <c r="I33" t="s">
         <v>127</v>
       </c>
       <c r="J33" s="46">
@@ -4219,20 +4081,20 @@
       <c r="AQ33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR33" s="0">
+      <c r="AR33">
         <f>ROUND(AN33+AO33+AP33,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS33" t="s" s="0">
+      <c r="AS33" t="s">
         <v>107</v>
       </c>
       <c r="AT33" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU33" t="s" s="0">
+      <c r="AU33" t="s">
         <v>108</v>
       </c>
-      <c r="AV33" t="s" s="0">
+      <c r="AV33" t="s">
         <v>173</v>
       </c>
       <c r="AW33" s="48">
@@ -4271,10 +4133,10 @@
       <c r="BL33" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM33" t="s" s="0">
+      <c r="BM33" t="s">
         <v>108</v>
       </c>
-      <c r="BN33" t="s" s="0">
+      <c r="BN33" t="s">
         <v>108</v>
       </c>
       <c r="BO33" s="48">
@@ -4310,14 +4172,14 @@
       <c r="F35" s="46">
         <v>2</v>
       </c>
-      <c r="G35" t="s" s="0">
+      <c r="G35" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="46">
         <f>F35*G35</f>
         <v>600</v>
       </c>
-      <c r="I35" t="s" s="0">
+      <c r="I35" t="s">
         <v>127</v>
       </c>
       <c r="J35" s="46">
@@ -4445,20 +4307,20 @@
       <c r="AQ35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR35" s="0">
+      <c r="AR35">
         <f>ROUND(AN35+AO35+AP35,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS35" t="s" s="0">
+      <c r="AS35" t="s">
         <v>107</v>
       </c>
       <c r="AT35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU35" t="s" s="0">
+      <c r="AU35" t="s">
         <v>174</v>
       </c>
-      <c r="AV35" t="s" s="0">
+      <c r="AV35" t="s">
         <v>175</v>
       </c>
       <c r="AW35" s="48">
@@ -4497,10 +4359,10 @@
       <c r="BL35" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM35" t="s" s="0">
+      <c r="BM35" t="s">
         <v>108</v>
       </c>
-      <c r="BN35" t="s" s="0">
+      <c r="BN35" t="s">
         <v>108</v>
       </c>
       <c r="BO35" s="48">
@@ -4535,14 +4397,14 @@
       <c r="F36" s="46">
         <v>2</v>
       </c>
-      <c r="G36" t="s" s="0">
+      <c r="G36" t="s">
         <v>129</v>
       </c>
       <c r="H36" s="46">
         <f>F36*G36</f>
         <v>800</v>
       </c>
-      <c r="I36" t="s" s="0">
+      <c r="I36" t="s">
         <v>127</v>
       </c>
       <c r="J36" s="46">
@@ -4670,20 +4532,20 @@
       <c r="AQ36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR36" s="0">
+      <c r="AR36">
         <f>ROUND(AN36+AO36+AP36,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS36" t="s" s="0">
+      <c r="AS36" t="s">
         <v>107</v>
       </c>
       <c r="AT36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU36" t="s" s="0">
+      <c r="AU36" t="s">
         <v>176</v>
       </c>
-      <c r="AV36" t="s" s="0">
+      <c r="AV36" t="s">
         <v>177</v>
       </c>
       <c r="AW36" s="48">
@@ -4722,10 +4584,10 @@
       <c r="BL36" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM36" t="s" s="0">
+      <c r="BM36" t="s">
         <v>108</v>
       </c>
-      <c r="BN36" t="s" s="0">
+      <c r="BN36" t="s">
         <v>108</v>
       </c>
       <c r="BO36" s="48">
@@ -4760,14 +4622,14 @@
       <c r="F37" s="46">
         <v>2</v>
       </c>
-      <c r="G37" t="s" s="0">
+      <c r="G37" t="s">
         <v>161</v>
       </c>
       <c r="H37" s="46">
         <f>F37*G37</f>
         <v>1000</v>
       </c>
-      <c r="I37" t="s" s="0">
+      <c r="I37" t="s">
         <v>127</v>
       </c>
       <c r="J37" s="46">
@@ -4895,20 +4757,20 @@
       <c r="AQ37" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR37" s="0">
+      <c r="AR37">
         <f>ROUND(AN37+AO37+AP37,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS37" t="s" s="0">
+      <c r="AS37" t="s">
         <v>107</v>
       </c>
       <c r="AT37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU37" t="s" s="0">
+      <c r="AU37" t="s">
         <v>108</v>
       </c>
-      <c r="AV37" t="s" s="0">
+      <c r="AV37" t="s">
         <v>173</v>
       </c>
       <c r="AW37" s="48">
@@ -4947,10 +4809,10 @@
       <c r="BL37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM37" t="s" s="0">
+      <c r="BM37" t="s">
         <v>108</v>
       </c>
-      <c r="BN37" t="s" s="0">
+      <c r="BN37" t="s">
         <v>108</v>
       </c>
       <c r="BO37" s="48">
@@ -4976,34 +4838,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -6515,10 +6377,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -6529,14 +6391,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -6664,20 +6526,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -6716,10 +6578,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -6894,32 +6756,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -8445,14 +8307,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -8580,11 +8442,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -8795,34 +8657,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -10334,10 +10196,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -10348,14 +10210,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -10483,20 +10345,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -10535,10 +10397,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -10713,32 +10575,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -12250,10 +12112,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -12264,14 +12126,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -12399,11 +12261,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -12614,34 +12476,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -14153,10 +14015,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -14167,14 +14029,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -14302,20 +14164,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -14354,10 +14216,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -14532,32 +14394,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -16069,10 +15931,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -16083,14 +15945,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -16218,11 +16080,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -16433,34 +16295,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -18121,20 +17983,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>178</v>
       </c>
       <c r="AW23" s="48">
@@ -18173,10 +18035,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>178</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>179</v>
       </c>
       <c r="BO23" s="48">
@@ -18348,34 +18210,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -20036,20 +19898,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>131</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -20088,10 +19950,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>149</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -20263,32 +20125,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -21814,14 +21676,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -21949,11 +21811,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -22164,34 +22026,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -23717,14 +23579,14 @@
       <c r="F23" s="46">
         <v>50</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>1000</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -23852,21 +23714,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>57.048000000000002</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
-        <v>192</v>
+      <c r="AV23" t="s">
+        <v>187</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -23904,11 +23766,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="BN23" t="s" s="0">
-        <v>196</v>
+      <c r="BM23" t="s">
+        <v>189</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>188</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -24079,34 +23941,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -25618,10 +25480,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -25767,21 +25629,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
-        <v>236</v>
-      </c>
-      <c r="AV23" t="s" s="0">
-        <v>240</v>
+      <c r="AU23" t="s">
+        <v>190</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>191</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -25819,11 +25681,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
-        <v>242</v>
-      </c>
-      <c r="BN23" t="s" s="0">
-        <v>241</v>
+      <c r="BM23" t="s">
+        <v>193</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>192</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -25995,34 +25857,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -27548,14 +27410,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -27683,20 +27545,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>55.89</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>180</v>
       </c>
       <c r="AW23" s="48">
@@ -27735,10 +27597,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>180</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>130</v>
       </c>
       <c r="BO23" s="48">
@@ -27910,32 +27772,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -29461,14 +29323,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -29596,11 +29458,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -29811,34 +29673,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -31364,14 +31226,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -31499,20 +31361,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>55.89</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>181</v>
       </c>
       <c r="AW23" s="48">
@@ -31551,10 +31413,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>181</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -31729,34 +31591,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -33282,14 +33144,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -33417,20 +33279,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>56.46</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>181</v>
       </c>
       <c r="AW23" s="48">
@@ -33469,10 +33331,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>181</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>158</v>
       </c>
       <c r="BO23" s="48">
@@ -33647,32 +33509,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -35198,14 +35060,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -35333,11 +35195,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -35548,32 +35410,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -37085,10 +36947,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -37234,20 +37096,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>131</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -37286,10 +37148,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>149</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>182</v>
       </c>
       <c r="BO23" s="48">
@@ -37464,32 +37326,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -39150,11 +39012,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -39365,34 +39227,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -40918,14 +40780,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -41053,21 +40915,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>155</v>
       </c>
-      <c r="AV23" t="s" s="0">
-        <v>188</v>
+      <c r="AV23" t="s">
+        <v>185</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -41105,10 +40967,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
-        <v>189</v>
-      </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BM23" t="s">
+        <v>186</v>
+      </c>
+      <c r="BN23" t="s">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -41280,32 +41142,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -42817,10 +42679,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -42831,14 +42693,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -42966,11 +42828,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -43181,34 +43043,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -44734,14 +44596,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -44869,20 +44731,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>158</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>183</v>
       </c>
       <c r="AW23" s="48">
@@ -44921,10 +44783,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>184</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>131</v>
       </c>
       <c r="BO23" s="48">
@@ -45100,32 +44962,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -46637,10 +46499,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -46651,14 +46513,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -46786,11 +46648,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -46993,6 +46855,7 @@
     <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -47001,34 +46864,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -48540,10 +48403,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -48554,14 +48417,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -48689,20 +48552,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>132</v>
       </c>
       <c r="AW23" s="48">
@@ -48741,10 +48604,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48">

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="15" activeTab="18"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4118" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="196">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -550,16 +550,7 @@
     <t>183.52817</t>
   </si>
   <si>
-    <t>KD-DISS-UOM-10001</t>
-  </si>
-  <si>
-    <t>KD-DISS-UOM-10001-Rate Contract</t>
-  </si>
-  <si>
     <t>KGS</t>
-  </si>
-  <si>
-    <t>KD-DISS-UOM-10001-PriceList</t>
   </si>
   <si>
     <t>274.35</t>
@@ -598,19 +589,10 @@
     <t>56.46</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>185.02695</t>
   </si>
   <si>
     <t>184.24408</t>
-  </si>
-  <si>
-    <t>189.55072</t>
-  </si>
-  <si>
-    <t>190.42571</t>
   </si>
   <si>
     <t>57.048</t>
@@ -622,25 +604,40 @@
     <t>56.96721</t>
   </si>
   <si>
-    <t>14090</t>
+    <t>TVS-RM-KDK-101</t>
   </si>
   <si>
-    <t>121.22038</t>
+    <t>ROAU-RM-KDK-01</t>
   </si>
   <si>
-    <t>691</t>
+    <t>ROAU-KDK-SERVICE-01</t>
   </si>
   <si>
-    <t>146.85967</t>
+    <t>ROAU-KDK-SERVICE-RATECONTRACT-01</t>
   </si>
   <si>
-    <t>TVS-SER-10001-PriceList</t>
+    <t>ROAU-RM-KDK-01 RateContract</t>
   </si>
   <si>
-    <t>TVS-SER-10001-RateContract</t>
+    <t>ROAU-RM-KDK-01 PriceList</t>
   </si>
   <si>
-    <t>TVS-RM-KDK-101</t>
+    <t>ROAU-KDK-SERVICE-PRICELIST-01</t>
+  </si>
+  <si>
+    <t>ROAU-RM-KDK-DIS-01</t>
+  </si>
+  <si>
+    <t>ROAU-RM-KDK-DIS-01 RateContract</t>
+  </si>
+  <si>
+    <t>ROAU-RM-KDK-DIS-01 PriceList</t>
+  </si>
+  <si>
+    <t>INS</t>
+  </si>
+  <si>
+    <t>186.32</t>
   </si>
 </sst>
 </file>
@@ -677,14 +674,14 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
@@ -692,14 +689,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1109,10 +1106,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1427,7 +1424,7 @@
   <dimension ref="A8:BR37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="27.28515625"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:70" ht="15.75" thickBot="1"/>
@@ -1595,10 +1592,10 @@
       <c r="AT9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU9" t="s">
+      <c r="AU9" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AV9" t="s" s="0">
         <v>143</v>
       </c>
       <c r="AW9" s="48">
@@ -1639,10 +1636,10 @@
       <c r="BL9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" t="s">
+      <c r="BM9" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BN9" t="s" s="0">
         <v>147</v>
       </c>
       <c r="BO9" s="48" t="e">
@@ -1814,20 +1811,20 @@
       <c r="AQ15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR15" t="e">
+      <c r="AR15" t="e" s="0">
         <f>ROUND(AN15+AO15+AP15,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS15" t="s">
+      <c r="AS15" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU15" t="s">
+      <c r="AU15" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV15" t="s">
+      <c r="AV15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW15" s="48">
@@ -1866,10 +1863,10 @@
       <c r="BL15" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM15" t="s">
+      <c r="BM15" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN15" t="s">
+      <c r="BN15" t="s" s="0">
         <v>150</v>
       </c>
       <c r="BO15" s="48" t="e">
@@ -2039,20 +2036,20 @@
       <c r="AQ16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="0">
         <f>ROUND(AN16+AO16+AP16,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS16" t="s">
+      <c r="AS16" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU16" t="s">
+      <c r="AU16" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="AV16" t="s">
+      <c r="AV16" t="s" s="0">
         <v>136</v>
       </c>
       <c r="AW16" s="48">
@@ -2091,10 +2088,10 @@
       <c r="BL16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM16" t="s">
+      <c r="BM16" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="BN16" t="s">
+      <c r="BN16" t="s" s="0">
         <v>133</v>
       </c>
       <c r="BO16" s="48">
@@ -2264,20 +2261,20 @@
       <c r="AQ17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR17">
+      <c r="AR17" s="0">
         <f>ROUND(AN17+AO17+AP17,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS17" t="s">
+      <c r="AS17" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU17" t="s">
+      <c r="AU17" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AV17" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW17" s="48">
@@ -2483,20 +2480,20 @@
       <c r="AQ18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR18">
+      <c r="AR18" s="0">
         <f>ROUND(AN18+AO18+AP18,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS18" t="s">
+      <c r="AS18" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU18" t="s">
+      <c r="AU18" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="AV18" t="s">
+      <c r="AV18" t="s" s="0">
         <v>137</v>
       </c>
       <c r="AW18" s="48">
@@ -2535,10 +2532,10 @@
       <c r="BL18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM18" t="s">
+      <c r="BM18" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="BN18" t="s">
+      <c r="BN18" t="s" s="0">
         <v>152</v>
       </c>
       <c r="BO18" s="48">
@@ -2709,20 +2706,20 @@
       <c r="AQ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR20" t="e">
+      <c r="AR20" t="e" s="0">
         <f>ROUND(AN20+AO20+AP20,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS20" t="s">
+      <c r="AS20" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU20" t="s">
+      <c r="AU20" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="AV20" t="s">
+      <c r="AV20" t="s" s="0">
         <v>156</v>
       </c>
       <c r="AW20" s="48">
@@ -2761,10 +2758,10 @@
       <c r="BL20" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM20" t="s">
+      <c r="BM20" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="BN20" t="s">
+      <c r="BN20" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO20" s="48" t="e">
@@ -2934,20 +2931,20 @@
       <c r="AQ21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" t="e">
+      <c r="AR21" t="e" s="0">
         <f t="shared" ref="AR21:AR23" si="30">ROUND(AN21+AO21+AP21,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS21" t="s">
+      <c r="AS21" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU21" t="s">
+      <c r="AU21" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV21" t="s">
+      <c r="AV21" t="s" s="0">
         <v>157</v>
       </c>
       <c r="AW21" s="48">
@@ -2986,10 +2983,10 @@
       <c r="BL21" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM21" t="s">
+      <c r="BM21" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN21" t="s">
+      <c r="BN21" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO21" s="48" t="e">
@@ -3159,20 +3156,20 @@
       <c r="AQ22" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR22" t="e">
+      <c r="AR22" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS22" t="s">
+      <c r="AS22" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU22" t="s">
+      <c r="AU22" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV22" t="s">
+      <c r="AV22" t="s" s="0">
         <v>159</v>
       </c>
       <c r="AW22" s="48">
@@ -3211,10 +3208,10 @@
       <c r="BL22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM22" t="s">
+      <c r="BM22" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN22" t="s">
+      <c r="BN22" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO22" s="48" t="e">
@@ -3384,20 +3381,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" t="e">
+      <c r="AR23" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>160</v>
       </c>
       <c r="AW23" s="48">
@@ -3436,10 +3433,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48" t="e">
@@ -3496,14 +3493,14 @@
       <c r="F31" s="46">
         <v>2</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H31" s="46">
         <f>F31*G31</f>
         <v>600</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J31" s="46">
@@ -3631,21 +3628,21 @@
       <c r="AQ31" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR31">
+      <c r="AR31" s="0">
         <f>ROUND(AN31+AO31+AP31,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS31" t="s">
+      <c r="AS31" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU31" t="s">
+      <c r="AU31" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="AV31" t="s">
-        <v>170</v>
+      <c r="AV31" t="s" s="0">
+        <v>167</v>
       </c>
       <c r="AW31" s="48">
         <f>AM31</f>
@@ -3683,10 +3680,10 @@
       <c r="BL31" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM31" t="s">
+      <c r="BM31" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN31" t="s">
+      <c r="BN31" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO31" s="48">
@@ -3721,14 +3718,14 @@
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H32" s="46">
         <f>F32*G32</f>
         <v>800</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J32" s="46">
@@ -3856,21 +3853,21 @@
       <c r="AQ32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR32">
+      <c r="AR32" s="0">
         <f>ROUND(AN32+AO32+AP32,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS32" t="s">
+      <c r="AS32" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT32" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU32" t="s">
-        <v>171</v>
-      </c>
-      <c r="AV32" t="s">
-        <v>172</v>
+      <c r="AU32" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="AV32" t="s" s="0">
+        <v>169</v>
       </c>
       <c r="AW32" s="48">
         <f>AM32</f>
@@ -3908,10 +3905,10 @@
       <c r="BL32" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM32" t="s">
+      <c r="BM32" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN32" t="s">
+      <c r="BN32" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO32" s="48">
@@ -3946,14 +3943,14 @@
       <c r="F33" s="46">
         <v>2</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H33" s="46">
         <f>F33*G33</f>
         <v>1000</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J33" s="46">
@@ -4081,21 +4078,21 @@
       <c r="AQ33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR33">
+      <c r="AR33" s="0">
         <f>ROUND(AN33+AO33+AP33,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS33" t="s">
+      <c r="AS33" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT33" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU33" t="s">
+      <c r="AU33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV33" t="s">
-        <v>173</v>
+      <c r="AV33" t="s" s="0">
+        <v>170</v>
       </c>
       <c r="AW33" s="48">
         <f>AM33</f>
@@ -4133,10 +4130,10 @@
       <c r="BL33" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM33" t="s">
+      <c r="BM33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN33" t="s">
+      <c r="BN33" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO33" s="48">
@@ -4172,14 +4169,14 @@
       <c r="F35" s="46">
         <v>2</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H35" s="46">
         <f>F35*G35</f>
         <v>600</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J35" s="46">
@@ -4307,21 +4304,21 @@
       <c r="AQ35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR35">
+      <c r="AR35" s="0">
         <f>ROUND(AN35+AO35+AP35,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS35" t="s">
+      <c r="AS35" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU35" t="s">
-        <v>174</v>
-      </c>
-      <c r="AV35" t="s">
-        <v>175</v>
+      <c r="AU35" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="AV35" t="s" s="0">
+        <v>172</v>
       </c>
       <c r="AW35" s="48">
         <f>AM35</f>
@@ -4359,10 +4356,10 @@
       <c r="BL35" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM35" t="s">
+      <c r="BM35" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN35" t="s">
+      <c r="BN35" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO35" s="48">
@@ -4397,14 +4394,14 @@
       <c r="F36" s="46">
         <v>2</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H36" s="46">
         <f>F36*G36</f>
         <v>800</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J36" s="46">
@@ -4532,21 +4529,21 @@
       <c r="AQ36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR36">
+      <c r="AR36" s="0">
         <f>ROUND(AN36+AO36+AP36,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS36" t="s">
+      <c r="AS36" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU36" t="s">
-        <v>176</v>
-      </c>
-      <c r="AV36" t="s">
-        <v>177</v>
+      <c r="AU36" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="AV36" t="s" s="0">
+        <v>174</v>
       </c>
       <c r="AW36" s="48">
         <f>AM36</f>
@@ -4584,10 +4581,10 @@
       <c r="BL36" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM36" t="s">
+      <c r="BM36" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN36" t="s">
+      <c r="BN36" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO36" s="48">
@@ -4622,14 +4619,14 @@
       <c r="F37" s="46">
         <v>2</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H37" s="46">
         <f>F37*G37</f>
         <v>1000</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J37" s="46">
@@ -4757,21 +4754,21 @@
       <c r="AQ37" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR37">
+      <c r="AR37" s="0">
         <f>ROUND(AN37+AO37+AP37,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS37" t="s">
+      <c r="AS37" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU37" t="s">
+      <c r="AU37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV37" t="s">
-        <v>173</v>
+      <c r="AV37" t="s" s="0">
+        <v>170</v>
       </c>
       <c r="AW37" s="48">
         <f>AM37</f>
@@ -4809,10 +4806,10 @@
       <c r="BL37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM37" t="s">
+      <c r="BM37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN37" t="s">
+      <c r="BN37" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO37" s="48">
@@ -4838,34 +4835,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -4900,69 +4897,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -6377,10 +6374,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -6391,14 +6388,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -6526,20 +6523,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -6578,10 +6575,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -6593,7 +6590,7 @@
         <v>4</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -6756,32 +6753,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -6816,69 +6813,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -8293,10 +8290,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -8307,14 +8304,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -8442,11 +8439,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -8497,7 +8494,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -8657,34 +8654,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -8719,69 +8716,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -10195,11 +10192,11 @@
       <c r="A23" s="45">
         <v>1</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>123</v>
+      <c r="B23" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>188</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -10210,14 +10207,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -10345,20 +10342,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -10397,10 +10394,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -10412,7 +10409,7 @@
         <v>4</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -10575,32 +10572,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -10635,69 +10632,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -12112,10 +12109,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -12126,14 +12123,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -12261,11 +12258,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -12316,7 +12313,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -12476,34 +12473,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -12538,69 +12535,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -14015,10 +14012,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -14029,14 +14026,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -14164,20 +14161,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -14216,10 +14213,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -14231,7 +14228,7 @@
         <v>4</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -14394,32 +14391,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -14454,69 +14451,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -15931,10 +15928,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -15945,14 +15942,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -16080,11 +16077,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -16135,7 +16132,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -16295,34 +16292,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -16357,69 +16354,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -17834,16 +17831,16 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="45" t="s">
         <v>166</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>168</v>
       </c>
       <c r="F23" s="46">
         <v>2</v>
@@ -17983,21 +17980,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>178</v>
+      <c r="AV23" t="s" s="0">
+        <v>175</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -18035,22 +18032,22 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>178</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>179</v>
+      <c r="BM23" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>176</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
         <v>846.99</v>
       </c>
-      <c r="BP23" s="62">
+      <c r="BP23" s="61">
         <f>BN23+AW23</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -18210,34 +18207,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -18272,69 +18269,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -19749,16 +19746,16 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="45" t="s">
         <v>166</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>168</v>
       </c>
       <c r="F23" s="46">
         <v>2</v>
@@ -19898,20 +19895,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -19950,10 +19947,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -19965,7 +19962,7 @@
         <v>8</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -20125,32 +20122,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -20185,69 +20182,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -21662,10 +21659,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -21676,14 +21673,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -21811,11 +21808,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -21866,7 +21863,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -22026,34 +22023,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -22088,69 +22085,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -23565,28 +23562,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F23" s="46">
         <v>50</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>1000</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -23714,21 +23711,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>57.048000000000002</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>187</v>
+      <c r="AV23" t="s" s="0">
+        <v>181</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -23766,11 +23763,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>189</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>188</v>
+      <c r="BM23" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>182</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -23781,7 +23778,7 @@
         <v>21.667000000000002</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -23941,34 +23938,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -25480,10 +25477,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -25629,21 +25626,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
-        <v>190</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>191</v>
+      <c r="AU23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="AV23" t="s" s="0">
+        <v>149</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -25659,7 +25656,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>257.23235</v>
+        <v>282.33</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -25681,11 +25678,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>193</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>192</v>
+      <c r="BM23" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>155</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -25696,7 +25693,7 @@
         <v>14</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -25857,34 +25854,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -25919,69 +25916,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -27396,28 +27393,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -27545,21 +27542,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>55.89</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>180</v>
+      <c r="AV23" t="s" s="0">
+        <v>177</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -27597,10 +27594,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>180</v>
-      </c>
-      <c r="BN23" t="s">
+      <c r="BM23" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="BN23" t="s" s="0">
         <v>130</v>
       </c>
       <c r="BO23" s="48">
@@ -27612,7 +27609,7 @@
         <v>4</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -27772,32 +27769,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -27832,69 +27829,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -29323,14 +29320,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -29458,11 +29455,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -29513,7 +29510,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -29673,34 +29670,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -29735,69 +29732,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -31212,28 +31209,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -31361,21 +31358,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>55.89</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>181</v>
+      <c r="AV23" t="s" s="0">
+        <v>178</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -31413,10 +31410,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>181</v>
-      </c>
-      <c r="BN23" t="s">
+      <c r="BM23" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="BN23" t="s" s="0">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -31428,7 +31425,7 @@
         <v>5</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -31591,34 +31588,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -31653,69 +31650,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
-      <c r="AH1" s="63"/>
-      <c r="AI1" s="63"/>
-      <c r="AJ1" s="63"/>
-      <c r="AK1" s="63"/>
-      <c r="AL1" s="63"/>
-      <c r="AM1" s="63"/>
-      <c r="AN1" s="63"/>
-      <c r="AO1" s="63"/>
-      <c r="AP1" s="63"/>
-      <c r="AQ1" s="63"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="63"/>
-      <c r="W2" s="63"/>
-      <c r="X2" s="63"/>
-      <c r="Y2" s="63"/>
-      <c r="Z2" s="63"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
-      <c r="AH2" s="63"/>
-      <c r="AI2" s="63"/>
-      <c r="AJ2" s="63"/>
-      <c r="AK2" s="63"/>
-      <c r="AL2" s="63"/>
-      <c r="AM2" s="63"/>
-      <c r="AN2" s="63"/>
-      <c r="AO2" s="63"/>
-      <c r="AP2" s="63"/>
-      <c r="AQ2" s="63"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="62"/>
+      <c r="AC2" s="62"/>
+      <c r="AD2" s="62"/>
+      <c r="AE2" s="62"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="62"/>
+      <c r="AI2" s="62"/>
+      <c r="AJ2" s="62"/>
+      <c r="AK2" s="62"/>
+      <c r="AL2" s="62"/>
+      <c r="AM2" s="62"/>
+      <c r="AN2" s="62"/>
+      <c r="AO2" s="62"/>
+      <c r="AP2" s="62"/>
+      <c r="AQ2" s="62"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -33130,28 +33127,28 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -33279,21 +33276,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>56.46</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>181</v>
+      <c r="AV23" t="s" s="0">
+        <v>178</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -33331,10 +33328,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>181</v>
-      </c>
-      <c r="BN23" t="s">
+      <c r="BM23" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="BN23" t="s" s="0">
         <v>158</v>
       </c>
       <c r="BO23" s="48">
@@ -33346,7 +33343,7 @@
         <v>7</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -33509,32 +33506,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -33569,69 +33566,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -35060,14 +35057,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -35195,11 +35192,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -35250,7 +35247,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -35410,32 +35407,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -36947,10 +36944,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -37096,20 +37093,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV23" t="s">
+      <c r="AU23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -37148,11 +37145,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
-        <v>182</v>
+      <c r="BN23" t="s" s="0">
+        <v>164</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -37163,7 +37160,7 @@
         <v>16</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -37326,32 +37323,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -38863,10 +38860,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -39012,11 +39009,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -39067,7 +39064,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -39227,34 +39224,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -39289,69 +39286,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="58"/>
-      <c r="AE1" s="58"/>
-      <c r="AF1" s="58"/>
-      <c r="AG1" s="58"/>
-      <c r="AH1" s="58"/>
-      <c r="AI1" s="58"/>
-      <c r="AJ1" s="58"/>
-      <c r="AK1" s="58"/>
-      <c r="AL1" s="58"/>
-      <c r="AM1" s="58"/>
-      <c r="AN1" s="58"/>
-      <c r="AO1" s="58"/>
-      <c r="AP1" s="58"/>
-      <c r="AQ1" s="58"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="58"/>
-      <c r="AB2" s="58"/>
-      <c r="AC2" s="58"/>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="58"/>
-      <c r="AH2" s="58"/>
-      <c r="AI2" s="58"/>
-      <c r="AJ2" s="58"/>
-      <c r="AK2" s="58"/>
-      <c r="AL2" s="58"/>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="58"/>
-      <c r="AO2" s="58"/>
-      <c r="AP2" s="58"/>
-      <c r="AQ2" s="58"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="63"/>
+      <c r="Y2" s="63"/>
+      <c r="Z2" s="63"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
+      <c r="AH2" s="63"/>
+      <c r="AI2" s="63"/>
+      <c r="AJ2" s="63"/>
+      <c r="AK2" s="63"/>
+      <c r="AL2" s="63"/>
+      <c r="AM2" s="63"/>
+      <c r="AN2" s="63"/>
+      <c r="AO2" s="63"/>
+      <c r="AP2" s="63"/>
+      <c r="AQ2" s="63"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -39441,7 +39438,7 @@
         <v>257.63</v>
       </c>
       <c r="H4" s="18">
-        <f>F4*G4</f>
+        <f t="shared" ref="H4:H18" si="0">F4*G4</f>
         <v>6440.75</v>
       </c>
       <c r="I4" s="19"/>
@@ -39505,7 +39502,7 @@
         <v>125.45</v>
       </c>
       <c r="H5" s="18">
-        <f>F5*G5</f>
+        <f t="shared" si="0"/>
         <v>4390.75</v>
       </c>
       <c r="I5" s="19"/>
@@ -39569,7 +39566,7 @@
         <v>125.36</v>
       </c>
       <c r="H6" s="18">
-        <f>F6*G6</f>
+        <f t="shared" si="0"/>
         <v>5641.2</v>
       </c>
       <c r="I6" s="19"/>
@@ -39633,7 +39630,7 @@
         <v>45.25</v>
       </c>
       <c r="H7" s="18">
-        <f t="shared" ref="H7:H18" si="0">F7*G7</f>
+        <f t="shared" si="0"/>
         <v>2488.75</v>
       </c>
       <c r="I7" s="19"/>
@@ -40766,10 +40763,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -40780,14 +40777,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>400</v>
-      </c>
-      <c r="I23" t="s">
+        <v>600</v>
+      </c>
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -40798,35 +40795,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>392</v>
+        <v>594</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>7.84</v>
+        <v>11.88</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>384.16</v>
+        <v>582.12</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>11.52</v>
+        <v>17.46</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>27.36</v>
+        <v>35.340000000000003</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>372.64</v>
+        <v>564.66</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -40836,11 +40833,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>33.54</v>
+        <v>50.82</v>
       </c>
       <c r="W23" s="46">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>33.54</v>
+        <v>50.82</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -40851,19 +40848,19 @@
         <v>0</v>
       </c>
       <c r="Z23" s="47">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="46">
         <f>IF($C21=3,0,S23*Z23)</f>
-        <v>22.3584</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>89.438400000000001</v>
+        <v>101.64</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>462.07839999999999</v>
+        <v>666.3</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -40883,7 +40880,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>372.64</v>
+        <v>564.66</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -40902,7 +40899,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>186.32</v>
+        <v>282.33</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -40915,21 +40912,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>186.32</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>107</v>
+        <v>282.33</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
-        <v>155</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>185</v>
+      <c r="AU23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="AV23" t="s" s="0">
+        <v>195</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -40937,15 +40934,15 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>186.32</v>
+        <v>282.33</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>190.35839999999999</v>
+        <v>282.33</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -40967,22 +40964,22 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>186</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>150</v>
+      <c r="BM23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>108</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>190.86320000000001</v>
+        <v>282.33</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -40998,7 +40995,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -41011,21 +41008,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>27.36</v>
+        <v>35.340000000000003</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>372.64</v>
+        <v>564.66</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>33.54</v>
+        <v>50.82</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>33.54</v>
+        <v>50.82</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -41036,11 +41033,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>89.438400000000001</v>
+        <v>101.64</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>462.07839999999999</v>
+        <v>666.3</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -41061,7 +41058,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>372.64</v>
+        <v>564.66</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -41134,6 +41131,7 @@
     <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -41142,32 +41140,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -41202,69 +41200,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="59"/>
-      <c r="AE1" s="59"/>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="59"/>
-      <c r="AI1" s="59"/>
-      <c r="AJ1" s="59"/>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="59"/>
-      <c r="AM1" s="59"/>
-      <c r="AN1" s="59"/>
-      <c r="AO1" s="59"/>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="59"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
+      <c r="AH1" s="58"/>
+      <c r="AI1" s="58"/>
+      <c r="AJ1" s="58"/>
+      <c r="AK1" s="58"/>
+      <c r="AL1" s="58"/>
+      <c r="AM1" s="58"/>
+      <c r="AN1" s="58"/>
+      <c r="AO1" s="58"/>
+      <c r="AP1" s="58"/>
+      <c r="AQ1" s="58"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="59"/>
-      <c r="AP2" s="59"/>
-      <c r="AQ2" s="59"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+      <c r="Y2" s="58"/>
+      <c r="Z2" s="58"/>
+      <c r="AA2" s="58"/>
+      <c r="AB2" s="58"/>
+      <c r="AC2" s="58"/>
+      <c r="AD2" s="58"/>
+      <c r="AE2" s="58"/>
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="58"/>
+      <c r="AH2" s="58"/>
+      <c r="AI2" s="58"/>
+      <c r="AJ2" s="58"/>
+      <c r="AK2" s="58"/>
+      <c r="AL2" s="58"/>
+      <c r="AM2" s="58"/>
+      <c r="AN2" s="58"/>
+      <c r="AO2" s="58"/>
+      <c r="AP2" s="58"/>
+      <c r="AQ2" s="58"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -42679,10 +42677,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -42693,14 +42691,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -42828,11 +42826,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -42883,7 +42881,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -43043,34 +43041,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -43105,69 +43103,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="60"/>
-      <c r="AF1" s="60"/>
-      <c r="AG1" s="60"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="60"/>
-      <c r="AK1" s="60"/>
-      <c r="AL1" s="60"/>
-      <c r="AM1" s="60"/>
-      <c r="AN1" s="60"/>
-      <c r="AO1" s="60"/>
-      <c r="AP1" s="60"/>
-      <c r="AQ1" s="60"/>
+      <c r="AD1" s="59"/>
+      <c r="AE1" s="59"/>
+      <c r="AF1" s="59"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="59"/>
+      <c r="AI1" s="59"/>
+      <c r="AJ1" s="59"/>
+      <c r="AK1" s="59"/>
+      <c r="AL1" s="59"/>
+      <c r="AM1" s="59"/>
+      <c r="AN1" s="59"/>
+      <c r="AO1" s="59"/>
+      <c r="AP1" s="59"/>
+      <c r="AQ1" s="59"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="60"/>
-      <c r="AI2" s="60"/>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="60"/>
-      <c r="AL2" s="60"/>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="60"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
+      <c r="AM2" s="59"/>
+      <c r="AN2" s="59"/>
+      <c r="AO2" s="59"/>
+      <c r="AP2" s="59"/>
+      <c r="AQ2" s="59"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -44582,10 +44580,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -44596,14 +44594,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -44731,21 +44729,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV23" t="s">
-        <v>183</v>
+      <c r="AV23" t="s" s="0">
+        <v>179</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -44783,10 +44781,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>184</v>
-      </c>
-      <c r="BN23" t="s">
+      <c r="BM23" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="BN23" t="s" s="0">
         <v>131</v>
       </c>
       <c r="BO23" s="48">
@@ -44798,7 +44796,7 @@
         <v>10</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -44962,32 +44960,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -45022,69 +45020,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -46499,10 +46497,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -46513,14 +46511,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -46648,11 +46646,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -46703,7 +46701,7 @@
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>
@@ -46864,34 +46862,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -46926,69 +46924,69 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
       <c r="AC1" s="66"/>
-      <c r="AD1" s="61"/>
-      <c r="AE1" s="61"/>
-      <c r="AF1" s="61"/>
-      <c r="AG1" s="61"/>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="61"/>
-      <c r="AL1" s="61"/>
-      <c r="AM1" s="61"/>
-      <c r="AN1" s="61"/>
-      <c r="AO1" s="61"/>
-      <c r="AP1" s="61"/>
-      <c r="AQ1" s="61"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
     </row>
     <row r="2" spans="1:45" ht="18.75" thickBot="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
     </row>
@@ -48403,10 +48401,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -48417,14 +48415,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -48552,20 +48550,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW23" s="48">
@@ -48604,10 +48602,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -48619,7 +48617,7 @@
         <v>4</v>
       </c>
       <c r="BQ23" s="50">
-        <v>123562</v>
+        <v>88363222</v>
       </c>
       <c r="BR23" s="4"/>
     </row>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="21" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4118" uniqueCount="196">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -1424,7 +1424,7 @@
   <dimension ref="A8:BR37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="27.28515625"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:70" ht="15.75" thickBot="1"/>
@@ -1592,10 +1592,10 @@
       <c r="AT9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU9" t="s" s="0">
+      <c r="AU9" t="s">
         <v>127</v>
       </c>
-      <c r="AV9" t="s" s="0">
+      <c r="AV9" t="s">
         <v>143</v>
       </c>
       <c r="AW9" s="48">
@@ -1636,10 +1636,10 @@
       <c r="BL9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" t="s" s="0">
+      <c r="BM9" t="s">
         <v>146</v>
       </c>
-      <c r="BN9" t="s" s="0">
+      <c r="BN9" t="s">
         <v>147</v>
       </c>
       <c r="BO9" s="48" t="e">
@@ -1811,20 +1811,20 @@
       <c r="AQ15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR15" t="e" s="0">
+      <c r="AR15" t="e">
         <f>ROUND(AN15+AO15+AP15,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS15" t="s" s="0">
+      <c r="AS15" t="s">
         <v>107</v>
       </c>
       <c r="AT15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU15" t="s" s="0">
+      <c r="AU15" t="s">
         <v>131</v>
       </c>
-      <c r="AV15" t="s" s="0">
+      <c r="AV15" t="s">
         <v>149</v>
       </c>
       <c r="AW15" s="48">
@@ -1863,10 +1863,10 @@
       <c r="BL15" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM15" t="s" s="0">
+      <c r="BM15" t="s">
         <v>149</v>
       </c>
-      <c r="BN15" t="s" s="0">
+      <c r="BN15" t="s">
         <v>150</v>
       </c>
       <c r="BO15" s="48" t="e">
@@ -2036,20 +2036,20 @@
       <c r="AQ16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR16" s="0">
+      <c r="AR16">
         <f>ROUND(AN16+AO16+AP16,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS16" t="s" s="0">
+      <c r="AS16" t="s">
         <v>107</v>
       </c>
       <c r="AT16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU16" t="s" s="0">
+      <c r="AU16" t="s">
         <v>135</v>
       </c>
-      <c r="AV16" t="s" s="0">
+      <c r="AV16" t="s">
         <v>136</v>
       </c>
       <c r="AW16" s="48">
@@ -2088,10 +2088,10 @@
       <c r="BL16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM16" t="s" s="0">
+      <c r="BM16" t="s">
         <v>134</v>
       </c>
-      <c r="BN16" t="s" s="0">
+      <c r="BN16" t="s">
         <v>133</v>
       </c>
       <c r="BO16" s="48">
@@ -2261,20 +2261,20 @@
       <c r="AQ17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR17" s="0">
+      <c r="AR17">
         <f>ROUND(AN17+AO17+AP17,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS17" t="s" s="0">
+      <c r="AS17" t="s">
         <v>107</v>
       </c>
       <c r="AT17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU17" t="s" s="0">
+      <c r="AU17" t="s">
         <v>108</v>
       </c>
-      <c r="AV17" t="s" s="0">
+      <c r="AV17" t="s">
         <v>132</v>
       </c>
       <c r="AW17" s="48">
@@ -2480,20 +2480,20 @@
       <c r="AQ18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR18" s="0">
+      <c r="AR18">
         <f>ROUND(AN18+AO18+AP18,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS18" t="s" s="0">
+      <c r="AS18" t="s">
         <v>107</v>
       </c>
       <c r="AT18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU18" t="s" s="0">
+      <c r="AU18" t="s">
         <v>130</v>
       </c>
-      <c r="AV18" t="s" s="0">
+      <c r="AV18" t="s">
         <v>137</v>
       </c>
       <c r="AW18" s="48">
@@ -2532,10 +2532,10 @@
       <c r="BL18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM18" t="s" s="0">
+      <c r="BM18" t="s">
         <v>153</v>
       </c>
-      <c r="BN18" t="s" s="0">
+      <c r="BN18" t="s">
         <v>152</v>
       </c>
       <c r="BO18" s="48">
@@ -2706,20 +2706,20 @@
       <c r="AQ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR20" t="e" s="0">
+      <c r="AR20" t="e">
         <f>ROUND(AN20+AO20+AP20,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS20" t="s" s="0">
+      <c r="AS20" t="s">
         <v>107</v>
       </c>
       <c r="AT20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU20" t="s" s="0">
+      <c r="AU20" t="s">
         <v>155</v>
       </c>
-      <c r="AV20" t="s" s="0">
+      <c r="AV20" t="s">
         <v>156</v>
       </c>
       <c r="AW20" s="48">
@@ -2758,10 +2758,10 @@
       <c r="BL20" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM20" t="s" s="0">
+      <c r="BM20" t="s">
         <v>156</v>
       </c>
-      <c r="BN20" t="s" s="0">
+      <c r="BN20" t="s">
         <v>127</v>
       </c>
       <c r="BO20" s="48" t="e">
@@ -2931,20 +2931,20 @@
       <c r="AQ21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" t="e" s="0">
+      <c r="AR21" t="e">
         <f t="shared" ref="AR21:AR23" si="30">ROUND(AN21+AO21+AP21,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS21" t="s" s="0">
+      <c r="AS21" t="s">
         <v>107</v>
       </c>
       <c r="AT21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU21" t="s" s="0">
+      <c r="AU21" t="s">
         <v>131</v>
       </c>
-      <c r="AV21" t="s" s="0">
+      <c r="AV21" t="s">
         <v>157</v>
       </c>
       <c r="AW21" s="48">
@@ -2983,10 +2983,10 @@
       <c r="BL21" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM21" t="s" s="0">
+      <c r="BM21" t="s">
         <v>108</v>
       </c>
-      <c r="BN21" t="s" s="0">
+      <c r="BN21" t="s">
         <v>108</v>
       </c>
       <c r="BO21" s="48" t="e">
@@ -3156,20 +3156,20 @@
       <c r="AQ22" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR22" t="e" s="0">
+      <c r="AR22" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS22" t="s" s="0">
+      <c r="AS22" t="s">
         <v>107</v>
       </c>
       <c r="AT22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU22" t="s" s="0">
+      <c r="AU22" t="s">
         <v>158</v>
       </c>
-      <c r="AV22" t="s" s="0">
+      <c r="AV22" t="s">
         <v>159</v>
       </c>
       <c r="AW22" s="48">
@@ -3208,10 +3208,10 @@
       <c r="BL22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM22" t="s" s="0">
+      <c r="BM22" t="s">
         <v>108</v>
       </c>
-      <c r="BN22" t="s" s="0">
+      <c r="BN22" t="s">
         <v>108</v>
       </c>
       <c r="BO22" s="48" t="e">
@@ -3381,20 +3381,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" t="e" s="0">
+      <c r="AR23" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>160</v>
       </c>
       <c r="AW23" s="48">
@@ -3433,10 +3433,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48" t="e">
@@ -3493,14 +3493,14 @@
       <c r="F31" s="46">
         <v>2</v>
       </c>
-      <c r="G31" t="s" s="0">
+      <c r="G31" t="s">
         <v>128</v>
       </c>
       <c r="H31" s="46">
         <f>F31*G31</f>
         <v>600</v>
       </c>
-      <c r="I31" t="s" s="0">
+      <c r="I31" t="s">
         <v>127</v>
       </c>
       <c r="J31" s="46">
@@ -3628,20 +3628,20 @@
       <c r="AQ31" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR31" s="0">
+      <c r="AR31">
         <f>ROUND(AN31+AO31+AP31,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS31" t="s" s="0">
+      <c r="AS31" t="s">
         <v>107</v>
       </c>
       <c r="AT31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU31" t="s" s="0">
+      <c r="AU31" t="s">
         <v>162</v>
       </c>
-      <c r="AV31" t="s" s="0">
+      <c r="AV31" t="s">
         <v>167</v>
       </c>
       <c r="AW31" s="48">
@@ -3680,10 +3680,10 @@
       <c r="BL31" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM31" t="s" s="0">
+      <c r="BM31" t="s">
         <v>108</v>
       </c>
-      <c r="BN31" t="s" s="0">
+      <c r="BN31" t="s">
         <v>108</v>
       </c>
       <c r="BO31" s="48">
@@ -3718,14 +3718,14 @@
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" t="s" s="0">
+      <c r="G32" t="s">
         <v>129</v>
       </c>
       <c r="H32" s="46">
         <f>F32*G32</f>
         <v>800</v>
       </c>
-      <c r="I32" t="s" s="0">
+      <c r="I32" t="s">
         <v>127</v>
       </c>
       <c r="J32" s="46">
@@ -3853,20 +3853,20 @@
       <c r="AQ32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR32" s="0">
+      <c r="AR32">
         <f>ROUND(AN32+AO32+AP32,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS32" t="s" s="0">
+      <c r="AS32" t="s">
         <v>107</v>
       </c>
       <c r="AT32" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU32" t="s" s="0">
+      <c r="AU32" t="s">
         <v>168</v>
       </c>
-      <c r="AV32" t="s" s="0">
+      <c r="AV32" t="s">
         <v>169</v>
       </c>
       <c r="AW32" s="48">
@@ -3905,10 +3905,10 @@
       <c r="BL32" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM32" t="s" s="0">
+      <c r="BM32" t="s">
         <v>108</v>
       </c>
-      <c r="BN32" t="s" s="0">
+      <c r="BN32" t="s">
         <v>108</v>
       </c>
       <c r="BO32" s="48">
@@ -3943,14 +3943,14 @@
       <c r="F33" s="46">
         <v>2</v>
       </c>
-      <c r="G33" t="s" s="0">
+      <c r="G33" t="s">
         <v>161</v>
       </c>
       <c r="H33" s="46">
         <f>F33*G33</f>
         <v>1000</v>
       </c>
-      <c r="I33" t="s" s="0">
+      <c r="I33" t="s">
         <v>127</v>
       </c>
       <c r="J33" s="46">
@@ -4078,20 +4078,20 @@
       <c r="AQ33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR33" s="0">
+      <c r="AR33">
         <f>ROUND(AN33+AO33+AP33,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS33" t="s" s="0">
+      <c r="AS33" t="s">
         <v>107</v>
       </c>
       <c r="AT33" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU33" t="s" s="0">
+      <c r="AU33" t="s">
         <v>108</v>
       </c>
-      <c r="AV33" t="s" s="0">
+      <c r="AV33" t="s">
         <v>170</v>
       </c>
       <c r="AW33" s="48">
@@ -4130,10 +4130,10 @@
       <c r="BL33" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM33" t="s" s="0">
+      <c r="BM33" t="s">
         <v>108</v>
       </c>
-      <c r="BN33" t="s" s="0">
+      <c r="BN33" t="s">
         <v>108</v>
       </c>
       <c r="BO33" s="48">
@@ -4169,14 +4169,14 @@
       <c r="F35" s="46">
         <v>2</v>
       </c>
-      <c r="G35" t="s" s="0">
+      <c r="G35" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="46">
         <f>F35*G35</f>
         <v>600</v>
       </c>
-      <c r="I35" t="s" s="0">
+      <c r="I35" t="s">
         <v>127</v>
       </c>
       <c r="J35" s="46">
@@ -4304,20 +4304,20 @@
       <c r="AQ35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR35" s="0">
+      <c r="AR35">
         <f>ROUND(AN35+AO35+AP35,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS35" t="s" s="0">
+      <c r="AS35" t="s">
         <v>107</v>
       </c>
       <c r="AT35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU35" t="s" s="0">
+      <c r="AU35" t="s">
         <v>171</v>
       </c>
-      <c r="AV35" t="s" s="0">
+      <c r="AV35" t="s">
         <v>172</v>
       </c>
       <c r="AW35" s="48">
@@ -4356,10 +4356,10 @@
       <c r="BL35" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM35" t="s" s="0">
+      <c r="BM35" t="s">
         <v>108</v>
       </c>
-      <c r="BN35" t="s" s="0">
+      <c r="BN35" t="s">
         <v>108</v>
       </c>
       <c r="BO35" s="48">
@@ -4394,14 +4394,14 @@
       <c r="F36" s="46">
         <v>2</v>
       </c>
-      <c r="G36" t="s" s="0">
+      <c r="G36" t="s">
         <v>129</v>
       </c>
       <c r="H36" s="46">
         <f>F36*G36</f>
         <v>800</v>
       </c>
-      <c r="I36" t="s" s="0">
+      <c r="I36" t="s">
         <v>127</v>
       </c>
       <c r="J36" s="46">
@@ -4529,20 +4529,20 @@
       <c r="AQ36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR36" s="0">
+      <c r="AR36">
         <f>ROUND(AN36+AO36+AP36,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS36" t="s" s="0">
+      <c r="AS36" t="s">
         <v>107</v>
       </c>
       <c r="AT36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU36" t="s" s="0">
+      <c r="AU36" t="s">
         <v>173</v>
       </c>
-      <c r="AV36" t="s" s="0">
+      <c r="AV36" t="s">
         <v>174</v>
       </c>
       <c r="AW36" s="48">
@@ -4581,10 +4581,10 @@
       <c r="BL36" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM36" t="s" s="0">
+      <c r="BM36" t="s">
         <v>108</v>
       </c>
-      <c r="BN36" t="s" s="0">
+      <c r="BN36" t="s">
         <v>108</v>
       </c>
       <c r="BO36" s="48">
@@ -4619,14 +4619,14 @@
       <c r="F37" s="46">
         <v>2</v>
       </c>
-      <c r="G37" t="s" s="0">
+      <c r="G37" t="s">
         <v>161</v>
       </c>
       <c r="H37" s="46">
         <f>F37*G37</f>
         <v>1000</v>
       </c>
-      <c r="I37" t="s" s="0">
+      <c r="I37" t="s">
         <v>127</v>
       </c>
       <c r="J37" s="46">
@@ -4754,20 +4754,20 @@
       <c r="AQ37" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR37" s="0">
+      <c r="AR37">
         <f>ROUND(AN37+AO37+AP37,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS37" t="s" s="0">
+      <c r="AS37" t="s">
         <v>107</v>
       </c>
       <c r="AT37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU37" t="s" s="0">
+      <c r="AU37" t="s">
         <v>108</v>
       </c>
-      <c r="AV37" t="s" s="0">
+      <c r="AV37" t="s">
         <v>170</v>
       </c>
       <c r="AW37" s="48">
@@ -4806,10 +4806,10 @@
       <c r="BL37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM37" t="s" s="0">
+      <c r="BM37" t="s">
         <v>108</v>
       </c>
-      <c r="BN37" t="s" s="0">
+      <c r="BN37" t="s">
         <v>108</v>
       </c>
       <c r="BO37" s="48">
@@ -4835,34 +4835,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -6388,14 +6388,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -6523,20 +6523,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -6575,10 +6575,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -6753,32 +6753,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -8304,14 +8304,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -8439,12 +8439,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -8654,34 +8654,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -10207,14 +10207,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -10342,20 +10342,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -10394,10 +10394,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -10572,32 +10572,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -12123,14 +12123,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -12258,12 +12258,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -12473,34 +12473,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -14026,14 +14026,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -14161,20 +14161,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -14213,10 +14213,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -14391,32 +14391,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -15942,14 +15942,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -16077,12 +16077,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -16292,34 +16292,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -17980,20 +17980,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -18032,10 +18032,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>175</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>176</v>
       </c>
       <c r="BO23" s="48">
@@ -18207,34 +18207,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -19895,20 +19895,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>131</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -19947,10 +19947,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>149</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -20122,32 +20122,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -21673,14 +21673,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -21808,12 +21808,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -22023,34 +22023,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -23576,14 +23576,14 @@
       <c r="F23" s="46">
         <v>50</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>1000</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -23711,20 +23711,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>57.048000000000002</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>181</v>
       </c>
       <c r="AW23" s="48">
@@ -23763,10 +23763,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>183</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>182</v>
       </c>
       <c r="BO23" s="48">
@@ -23938,34 +23938,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -25626,20 +25626,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -25678,10 +25678,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>149</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>155</v>
       </c>
       <c r="BO23" s="48">
@@ -25854,34 +25854,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -27407,14 +27407,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -27542,20 +27542,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>55.89</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>177</v>
       </c>
       <c r="AW23" s="48">
@@ -27594,10 +27594,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>177</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>130</v>
       </c>
       <c r="BO23" s="48">
@@ -27769,32 +27769,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -29320,14 +29320,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -29455,12 +29455,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -29670,34 +29670,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -31223,14 +31223,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -31358,20 +31358,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>55.89</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>178</v>
       </c>
       <c r="AW23" s="48">
@@ -31410,10 +31410,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>178</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -31588,34 +31588,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -33141,14 +33141,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>60</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -33276,20 +33276,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>56.46</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>178</v>
       </c>
       <c r="AW23" s="48">
@@ -33328,10 +33328,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>178</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>158</v>
       </c>
       <c r="BO23" s="48">
@@ -33506,32 +33506,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -35057,14 +35057,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -35192,12 +35192,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -35407,32 +35407,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -37093,20 +37093,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -37145,10 +37145,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>149</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>164</v>
       </c>
       <c r="BO23" s="48">
@@ -37323,32 +37323,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -39009,12 +39009,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -39224,34 +39224,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -40777,14 +40777,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -40912,20 +40912,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>195</v>
       </c>
       <c r="AW23" s="48">
@@ -40964,10 +40964,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -41140,32 +41140,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -42691,14 +42691,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -42826,12 +42826,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -43041,34 +43041,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -44594,14 +44594,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -44729,20 +44729,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>158</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>179</v>
       </c>
       <c r="AW23" s="48">
@@ -44781,10 +44781,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>180</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>131</v>
       </c>
       <c r="BO23" s="48">
@@ -44960,32 +44960,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -46511,14 +46511,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -46646,12 +46646,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -46862,34 +46862,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -48415,14 +48415,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -48550,20 +48550,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
-        <v>107</v>
+      <c r="AS23" t="s">
+        <v>194</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>132</v>
       </c>
       <c r="AW23" s="48">
@@ -48602,10 +48602,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48">

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4118" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4118" uniqueCount="195">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -602,9 +602,6 @@
   </si>
   <si>
     <t>56.96721</t>
-  </si>
-  <si>
-    <t>TVS-RM-KDK-101</t>
   </si>
   <si>
     <t>ROAU-RM-KDK-01</t>
@@ -6528,7 +6525,7 @@
         <v>186.32</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -8290,10 +8287,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -8444,7 +8441,7 @@
         <v>18.824999999999999</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -10193,10 +10190,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -10347,7 +10344,7 @@
         <v>186.32</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -12109,10 +12106,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -12263,7 +12260,7 @@
         <v>18.824999999999999</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -14012,10 +14009,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -14166,7 +14163,7 @@
         <v>186.32</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -15928,10 +15925,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -16082,7 +16079,7 @@
         <v>18.824999999999999</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -17831,10 +17828,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -17985,7 +17982,7 @@
         <v>846.99</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -19746,10 +19743,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -19900,7 +19897,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -21659,10 +21656,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -21813,7 +21810,7 @@
         <v>18.824999999999999</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -23562,10 +23559,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -23716,7 +23713,7 @@
         <v>57.048000000000002</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -25477,10 +25474,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -25631,7 +25628,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -27393,10 +27390,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -27547,7 +27544,7 @@
         <v>55.89</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -29306,10 +29303,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -29460,7 +29457,7 @@
         <v>18.824999999999999</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -31209,10 +31206,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -31363,7 +31360,7 @@
         <v>55.89</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -33127,10 +33124,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -33281,7 +33278,7 @@
         <v>56.46</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -35043,10 +35040,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -35197,7 +35194,7 @@
         <v>18.824999999999999</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -36944,10 +36941,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -37098,7 +37095,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -38860,10 +38857,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -39014,7 +39011,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -40763,10 +40760,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -40917,7 +40914,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -40926,7 +40923,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -42677,10 +42674,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -42831,7 +42828,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -44580,10 +44577,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -44734,7 +44731,7 @@
         <v>186.32</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -46497,10 +46494,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -46651,7 +46648,7 @@
         <v>18.824999999999999</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -48401,10 +48398,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -48555,7 +48552,7 @@
         <v>186.32</v>
       </c>
       <c r="AS23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="21" activeTab="23"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="18" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4118" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4113" uniqueCount="196">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -635,6 +635,9 @@
   </si>
   <si>
     <t>186.32</t>
+  </si>
+  <si>
+    <t>ROAU-KDK-DIS-SERVICE-01</t>
   </si>
 </sst>
 </file>
@@ -21655,11 +21658,11 @@
       <c r="A23" s="45">
         <v>1</v>
       </c>
-      <c r="B23" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>185</v>
+      <c r="B23" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -23571,14 +23574,14 @@
         <v>166</v>
       </c>
       <c r="F23" s="46">
-        <v>50</v>
-      </c>
-      <c r="G23" t="s">
-        <v>162</v>
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>200</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="I23" t="s">
         <v>127</v>
@@ -23591,35 +23594,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>980</v>
+        <v>392</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>19.600000000000001</v>
+        <v>7.84</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>960.4</v>
+        <v>384.16</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>9.6</v>
+        <v>3.84</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>49.2</v>
+        <v>19.68</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>950.8</v>
+        <v>380.32</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -23629,11 +23632,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>85.57</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="W23" s="46">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>85.57</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -23652,11 +23655,11 @@
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>171.14</v>
+        <v>68.459999999999994</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>1121.94</v>
+        <v>448.78</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -23676,7 +23679,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>950.8</v>
+        <v>380.32</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -23691,11 +23694,11 @@
       </c>
       <c r="AM23" s="46">
         <f>F23/AL23</f>
-        <v>16.666666666666668</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>57.047999999999995</v>
+        <v>570.48</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -23710,7 +23713,7 @@
       </c>
       <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>57.048000000000002</v>
+        <v>570.48</v>
       </c>
       <c r="AS23" t="s">
         <v>193</v>
@@ -23724,21 +23727,21 @@
       <c r="AV23" t="s">
         <v>181</v>
       </c>
-      <c r="AW23" s="48">
+      <c r="AW23" s="16">
         <f>AM23</f>
-        <v>16.666666666666668</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>57.048000000000002</v>
-      </c>
-      <c r="AY23" s="48">
+        <v>570.48</v>
+      </c>
+      <c r="AY23" s="16">
         <f>AU23+AW23</f>
-        <v>16.666666666666668</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>57.048000000000002</v>
+        <v>570.48</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -23767,12 +23770,12 @@
         <v>182</v>
       </c>
       <c r="BO23" s="48">
-        <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>56.780769999999997</v>
+        <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),3)</f>
+        <v>61.7</v>
       </c>
       <c r="BP23" s="4">
         <f>ROUND(BN23+AW23,3)</f>
-        <v>21.667000000000002</v>
+        <v>72.334999999999994</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -23791,7 +23794,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -23804,21 +23807,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>49.2</v>
+        <v>19.68</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>950.8</v>
+        <v>380.32</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>85.57</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>85.57</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -23829,11 +23832,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>171.14</v>
+        <v>68.459999999999994</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>1121.94</v>
+        <v>448.78</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -23854,7 +23857,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>950.8</v>
+        <v>380.32</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -27402,14 +27405,14 @@
         <v>166</v>
       </c>
       <c r="F23" s="46">
-        <v>3</v>
-      </c>
-      <c r="G23" t="s">
-        <v>162</v>
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>200</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="I23" t="s">
         <v>127</v>
@@ -27422,35 +27425,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>58.8</v>
+        <v>392</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>1.18</v>
+        <v>7.84</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>57.62</v>
+        <v>384.16</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>1.73</v>
+        <v>11.52</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>4.1099999999999994</v>
+        <v>27.36</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>55.89</v>
+        <v>372.64</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -27460,11 +27463,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>5.03</v>
+        <v>33.54</v>
       </c>
       <c r="W23" s="46">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>5.03</v>
+        <v>33.54</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -27479,15 +27482,15 @@
       </c>
       <c r="AA23" s="46">
         <f>IF($C21=3,0,S23*Z23)</f>
-        <v>3.3533999999999997</v>
+        <v>22.3584</v>
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>13.413399999999999</v>
+        <v>89.438400000000001</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>69.303399999999996</v>
+        <v>462.07839999999999</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -27507,7 +27510,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>55.89</v>
+        <v>372.64</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -27522,11 +27525,11 @@
       </c>
       <c r="AM23" s="46">
         <f>F23/AL23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>55.89</v>
+        <v>558.96</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -27541,7 +27544,7 @@
       </c>
       <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>55.89</v>
+        <v>558.96</v>
       </c>
       <c r="AS23" t="s">
         <v>193</v>
@@ -27557,19 +27560,19 @@
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>55.89</v>
+        <v>558.96</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>55.89</v>
+        <v>558.96</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -27599,11 +27602,11 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>55.89</v>
+        <v>127.75714000000001</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
-        <v>4</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -27622,7 +27625,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -27635,21 +27638,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>4.1099999999999994</v>
+        <v>27.36</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>55.89</v>
+        <v>372.64</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>5.03</v>
+        <v>33.54</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>5.03</v>
+        <v>33.54</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -27660,11 +27663,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>13.413399999999999</v>
+        <v>89.438400000000001</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>69.303399999999996</v>
+        <v>462.07839999999999</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -27685,7 +27688,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>55.89</v>
+        <v>372.64</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -29302,11 +29305,11 @@
       <c r="A23" s="45">
         <v>1</v>
       </c>
-      <c r="B23" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>185</v>
+      <c r="B23" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -29317,12 +29320,12 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
-        <v>162</v>
+      <c r="G23">
+        <v>200</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="I23" t="s">
         <v>115</v>
@@ -29335,35 +29338,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>39.6</v>
+        <v>396</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>0.79</v>
+        <v>7.92</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>38.81</v>
+        <v>388.08</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>1.1599999999999999</v>
+        <v>11.64</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>2.3499999999999996</v>
+        <v>23.560000000000002</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>37.65</v>
+        <v>376.44</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>151</v>
@@ -29373,11 +29376,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>3.39</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="W23" s="46">
         <f>IF(DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>3.39</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="X23" s="46">
         <f>IF(DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -29392,15 +29395,15 @@
       </c>
       <c r="AA23" s="46">
         <f>IF(DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
-        <v>2.2589999999999999</v>
+        <v>22.586399999999998</v>
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>9.0389999999999997</v>
+        <v>90.346400000000003</v>
       </c>
       <c r="AC23" s="46">
         <f>IF(DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
-        <v>37.65</v>
+        <v>376.44</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -29420,7 +29423,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*DirectGrnGenUD!$M$21</f>
-        <v>37.65</v>
+        <v>376.44</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF(DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
@@ -29439,7 +29442,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>18.824999999999999</v>
+        <v>188.22</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -29454,7 +29457,7 @@
       </c>
       <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>18.824999999999999</v>
+        <v>188.22</v>
       </c>
       <c r="AS23" t="s">
         <v>193</v>
@@ -29468,7 +29471,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>18.824999999999999</v>
+        <v>188.22</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -29476,7 +29479,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>18.824999999999999</v>
+        <v>188.22</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -29500,7 +29503,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>18.824999999999999</v>
+        <v>188.22</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -29523,7 +29526,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -29536,21 +29539,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>2.3499999999999996</v>
+        <v>23.560000000000002</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>37.65</v>
+        <v>376.44</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f t="shared" ref="V24:AE24" si="1">SUM(V23:V23)</f>
-        <v>3.39</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="W24" s="55">
         <f t="shared" si="1"/>
-        <v>3.39</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="X24" s="55">
         <f t="shared" si="1"/>
@@ -29561,11 +29564,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f t="shared" si="1"/>
-        <v>9.0389999999999997</v>
+        <v>90.346400000000003</v>
       </c>
       <c r="AC24" s="56">
         <f t="shared" si="1"/>
-        <v>37.65</v>
+        <v>376.44</v>
       </c>
       <c r="AD24" s="57">
         <f t="shared" si="1"/>
@@ -29586,7 +29589,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>37.65</v>
+        <v>376.44</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -31218,14 +31221,14 @@
         <v>166</v>
       </c>
       <c r="F23" s="46">
-        <v>3</v>
-      </c>
-      <c r="G23" t="s">
-        <v>162</v>
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>200</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="I23" t="s">
         <v>115</v>
@@ -31238,35 +31241,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>58.8</v>
+        <v>396</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>1.18</v>
+        <v>7.92</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>57.62</v>
+        <v>388.08</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>1.73</v>
+        <v>11.64</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>4.1099999999999994</v>
+        <v>23.560000000000002</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>55.89</v>
+        <v>376.44</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -31276,11 +31279,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>5.03</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="W23" s="46">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>5.03</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -31295,15 +31298,15 @@
       </c>
       <c r="AA23" s="46">
         <f>IF($C21=3,0,S23*Z23)</f>
-        <v>3.3533999999999997</v>
+        <v>22.586399999999998</v>
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>13.413399999999999</v>
+        <v>90.346400000000003</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>69.303399999999996</v>
+        <v>466.78640000000001</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -31323,7 +31326,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>55.89</v>
+        <v>376.44</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -31338,11 +31341,11 @@
       </c>
       <c r="AM23" s="46">
         <f>F23/AL23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>55.89</v>
+        <v>564.66000000000008</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -31357,7 +31360,7 @@
       </c>
       <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>55.89</v>
+        <v>564.66</v>
       </c>
       <c r="AS23" t="s">
         <v>193</v>
@@ -31371,21 +31374,21 @@
       <c r="AV23" t="s">
         <v>178</v>
       </c>
-      <c r="AW23" s="48">
+      <c r="AW23" s="16">
         <f>AM23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>55.89</v>
-      </c>
-      <c r="AY23" s="48">
+        <v>564.66</v>
+      </c>
+      <c r="AY23" s="16">
         <f>AU23+AW23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>55.89</v>
+        <v>564.66</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -31415,11 +31418,11 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>55.89</v>
+        <v>107.28</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
-        <v>5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -31438,7 +31441,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -31451,21 +31454,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>4.1099999999999994</v>
+        <v>23.560000000000002</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>55.89</v>
+        <v>376.44</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>5.03</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>5.03</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -31476,11 +31479,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>13.413399999999999</v>
+        <v>90.346400000000003</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>69.303399999999996</v>
+        <v>466.78640000000001</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -31501,7 +31504,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>55.89</v>
+        <v>376.44</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -33136,14 +33139,14 @@
         <v>166</v>
       </c>
       <c r="F23" s="46">
-        <v>3</v>
-      </c>
-      <c r="G23" t="s">
-        <v>162</v>
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>200</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="I23" t="s">
         <v>115</v>
@@ -33156,35 +33159,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>59.4</v>
+        <v>396</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>1.19</v>
+        <v>7.92</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>58.21</v>
+        <v>388.08</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>1.75</v>
+        <v>11.64</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>3.54</v>
+        <v>23.560000000000002</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>56.46</v>
+        <v>376.44</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -33194,11 +33197,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>5.08</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="W23" s="46">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>5.08</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -33213,15 +33216,15 @@
       </c>
       <c r="AA23" s="46">
         <f>IF($C21=3,0,S23*Z23)</f>
-        <v>3.3875999999999999</v>
+        <v>22.586399999999998</v>
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>13.547599999999999</v>
+        <v>90.346400000000003</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>70.007599999999996</v>
+        <v>466.78640000000001</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -33241,7 +33244,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>56.46</v>
+        <v>376.44</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -33256,11 +33259,11 @@
       </c>
       <c r="AM23" s="46">
         <f>F23/AL23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>56.46</v>
+        <v>564.66000000000008</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -33275,7 +33278,7 @@
       </c>
       <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>56.46</v>
+        <v>564.66</v>
       </c>
       <c r="AS23" t="s">
         <v>193</v>
@@ -33289,21 +33292,21 @@
       <c r="AV23" t="s">
         <v>178</v>
       </c>
-      <c r="AW23" s="48">
+      <c r="AW23" s="16">
         <f>AM23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>56.46</v>
-      </c>
-      <c r="AY23" s="48">
+        <v>564.66</v>
+      </c>
+      <c r="AY23" s="16">
         <f>AU23+AW23</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>56.46</v>
+        <v>564.66</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -33333,11 +33336,11 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>56.46</v>
+        <v>76.787999999999997</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
-        <v>7</v>
+        <v>16.666666666666668</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -33356,7 +33359,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -33369,21 +33372,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>3.54</v>
+        <v>23.560000000000002</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>56.46</v>
+        <v>376.44</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>5.08</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>5.08</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -33394,11 +33397,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>13.547599999999999</v>
+        <v>90.346400000000003</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>70.007599999999996</v>
+        <v>466.78640000000001</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -33419,7 +33422,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>56.46</v>
+        <v>376.44</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -35039,11 +35042,11 @@
       <c r="A23" s="45">
         <v>1</v>
       </c>
-      <c r="B23" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>185</v>
+      <c r="B23" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="18" activeTab="18"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="19" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4113" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4154" uniqueCount="205">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -583,12 +583,6 @@
     <t>1.334</t>
   </si>
   <si>
-    <t>55.89</t>
-  </si>
-  <si>
-    <t>56.46</t>
-  </si>
-  <si>
     <t>185.02695</t>
   </si>
   <si>
@@ -638,6 +632,39 @@
   </si>
   <si>
     <t>ROAU-KDK-DIS-SERVICE-01</t>
+  </si>
+  <si>
+    <t>558.96</t>
+  </si>
+  <si>
+    <t>8.671</t>
+  </si>
+  <si>
+    <t>9.338</t>
+  </si>
+  <si>
+    <t>566.36571</t>
+  </si>
+  <si>
+    <t>10.005</t>
+  </si>
+  <si>
+    <t>565.872</t>
+  </si>
+  <si>
+    <t>570.48</t>
+  </si>
+  <si>
+    <t>11.339</t>
+  </si>
+  <si>
+    <t>565.73647</t>
+  </si>
+  <si>
+    <t>12.006</t>
+  </si>
+  <si>
+    <t>566</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1451,7 @@
   <dimension ref="A8:BR37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="27.28515625"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:70" ht="15.75" thickBot="1"/>
@@ -1592,10 +1619,10 @@
       <c r="AT9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU9" t="s">
+      <c r="AU9" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AV9" t="s" s="0">
         <v>143</v>
       </c>
       <c r="AW9" s="48">
@@ -1636,10 +1663,10 @@
       <c r="BL9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" t="s">
+      <c r="BM9" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BN9" t="s" s="0">
         <v>147</v>
       </c>
       <c r="BO9" s="48" t="e">
@@ -1811,20 +1838,20 @@
       <c r="AQ15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR15" t="e">
+      <c r="AR15" t="e" s="0">
         <f>ROUND(AN15+AO15+AP15,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS15" t="s">
+      <c r="AS15" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU15" t="s">
+      <c r="AU15" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV15" t="s">
+      <c r="AV15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW15" s="48">
@@ -1863,10 +1890,10 @@
       <c r="BL15" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM15" t="s">
+      <c r="BM15" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN15" t="s">
+      <c r="BN15" t="s" s="0">
         <v>150</v>
       </c>
       <c r="BO15" s="48" t="e">
@@ -2036,20 +2063,20 @@
       <c r="AQ16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="0">
         <f>ROUND(AN16+AO16+AP16,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS16" t="s">
+      <c r="AS16" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU16" t="s">
+      <c r="AU16" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="AV16" t="s">
+      <c r="AV16" t="s" s="0">
         <v>136</v>
       </c>
       <c r="AW16" s="48">
@@ -2088,10 +2115,10 @@
       <c r="BL16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM16" t="s">
+      <c r="BM16" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="BN16" t="s">
+      <c r="BN16" t="s" s="0">
         <v>133</v>
       </c>
       <c r="BO16" s="48">
@@ -2261,20 +2288,20 @@
       <c r="AQ17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR17">
+      <c r="AR17" s="0">
         <f>ROUND(AN17+AO17+AP17,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS17" t="s">
+      <c r="AS17" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU17" t="s">
+      <c r="AU17" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AV17" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW17" s="48">
@@ -2480,20 +2507,20 @@
       <c r="AQ18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR18">
+      <c r="AR18" s="0">
         <f>ROUND(AN18+AO18+AP18,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS18" t="s">
+      <c r="AS18" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU18" t="s">
+      <c r="AU18" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="AV18" t="s">
+      <c r="AV18" t="s" s="0">
         <v>137</v>
       </c>
       <c r="AW18" s="48">
@@ -2532,10 +2559,10 @@
       <c r="BL18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM18" t="s">
+      <c r="BM18" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="BN18" t="s">
+      <c r="BN18" t="s" s="0">
         <v>152</v>
       </c>
       <c r="BO18" s="48">
@@ -2706,20 +2733,20 @@
       <c r="AQ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR20" t="e">
+      <c r="AR20" t="e" s="0">
         <f>ROUND(AN20+AO20+AP20,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS20" t="s">
+      <c r="AS20" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU20" t="s">
+      <c r="AU20" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="AV20" t="s">
+      <c r="AV20" t="s" s="0">
         <v>156</v>
       </c>
       <c r="AW20" s="48">
@@ -2758,10 +2785,10 @@
       <c r="BL20" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM20" t="s">
+      <c r="BM20" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="BN20" t="s">
+      <c r="BN20" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO20" s="48" t="e">
@@ -2931,20 +2958,20 @@
       <c r="AQ21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" t="e">
+      <c r="AR21" t="e" s="0">
         <f t="shared" ref="AR21:AR23" si="30">ROUND(AN21+AO21+AP21,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS21" t="s">
+      <c r="AS21" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU21" t="s">
+      <c r="AU21" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV21" t="s">
+      <c r="AV21" t="s" s="0">
         <v>157</v>
       </c>
       <c r="AW21" s="48">
@@ -2983,10 +3010,10 @@
       <c r="BL21" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM21" t="s">
+      <c r="BM21" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN21" t="s">
+      <c r="BN21" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO21" s="48" t="e">
@@ -3156,20 +3183,20 @@
       <c r="AQ22" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR22" t="e">
+      <c r="AR22" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS22" t="s">
+      <c r="AS22" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU22" t="s">
+      <c r="AU22" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV22" t="s">
+      <c r="AV22" t="s" s="0">
         <v>159</v>
       </c>
       <c r="AW22" s="48">
@@ -3208,10 +3235,10 @@
       <c r="BL22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM22" t="s">
+      <c r="BM22" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN22" t="s">
+      <c r="BN22" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO22" s="48" t="e">
@@ -3381,20 +3408,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" t="e">
+      <c r="AR23" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>160</v>
       </c>
       <c r="AW23" s="48">
@@ -3433,10 +3460,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48" t="e">
@@ -3493,14 +3520,14 @@
       <c r="F31" s="46">
         <v>2</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H31" s="46">
         <f>F31*G31</f>
         <v>600</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J31" s="46">
@@ -3628,20 +3655,20 @@
       <c r="AQ31" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR31">
+      <c r="AR31" s="0">
         <f>ROUND(AN31+AO31+AP31,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS31" t="s">
+      <c r="AS31" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU31" t="s">
+      <c r="AU31" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="AV31" t="s">
+      <c r="AV31" t="s" s="0">
         <v>167</v>
       </c>
       <c r="AW31" s="48">
@@ -3680,10 +3707,10 @@
       <c r="BL31" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM31" t="s">
+      <c r="BM31" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN31" t="s">
+      <c r="BN31" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO31" s="48">
@@ -3718,14 +3745,14 @@
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H32" s="46">
         <f>F32*G32</f>
         <v>800</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J32" s="46">
@@ -3853,20 +3880,20 @@
       <c r="AQ32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR32">
+      <c r="AR32" s="0">
         <f>ROUND(AN32+AO32+AP32,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS32" t="s">
+      <c r="AS32" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT32" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU32" t="s">
+      <c r="AU32" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="AV32" t="s">
+      <c r="AV32" t="s" s="0">
         <v>169</v>
       </c>
       <c r="AW32" s="48">
@@ -3905,10 +3932,10 @@
       <c r="BL32" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM32" t="s">
+      <c r="BM32" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN32" t="s">
+      <c r="BN32" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO32" s="48">
@@ -3943,14 +3970,14 @@
       <c r="F33" s="46">
         <v>2</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H33" s="46">
         <f>F33*G33</f>
         <v>1000</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J33" s="46">
@@ -4078,20 +4105,20 @@
       <c r="AQ33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR33">
+      <c r="AR33" s="0">
         <f>ROUND(AN33+AO33+AP33,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS33" t="s">
+      <c r="AS33" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT33" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU33" t="s">
+      <c r="AU33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV33" t="s">
+      <c r="AV33" t="s" s="0">
         <v>170</v>
       </c>
       <c r="AW33" s="48">
@@ -4130,10 +4157,10 @@
       <c r="BL33" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM33" t="s">
+      <c r="BM33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN33" t="s">
+      <c r="BN33" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO33" s="48">
@@ -4169,14 +4196,14 @@
       <c r="F35" s="46">
         <v>2</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H35" s="46">
         <f>F35*G35</f>
         <v>600</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J35" s="46">
@@ -4304,20 +4331,20 @@
       <c r="AQ35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR35">
+      <c r="AR35" s="0">
         <f>ROUND(AN35+AO35+AP35,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS35" t="s">
+      <c r="AS35" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU35" t="s">
+      <c r="AU35" t="s" s="0">
         <v>171</v>
       </c>
-      <c r="AV35" t="s">
+      <c r="AV35" t="s" s="0">
         <v>172</v>
       </c>
       <c r="AW35" s="48">
@@ -4356,10 +4383,10 @@
       <c r="BL35" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM35" t="s">
+      <c r="BM35" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN35" t="s">
+      <c r="BN35" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO35" s="48">
@@ -4394,14 +4421,14 @@
       <c r="F36" s="46">
         <v>2</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H36" s="46">
         <f>F36*G36</f>
         <v>800</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J36" s="46">
@@ -4529,20 +4556,20 @@
       <c r="AQ36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR36">
+      <c r="AR36" s="0">
         <f>ROUND(AN36+AO36+AP36,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS36" t="s">
+      <c r="AS36" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU36" t="s">
+      <c r="AU36" t="s" s="0">
         <v>173</v>
       </c>
-      <c r="AV36" t="s">
+      <c r="AV36" t="s" s="0">
         <v>174</v>
       </c>
       <c r="AW36" s="48">
@@ -4581,10 +4608,10 @@
       <c r="BL36" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM36" t="s">
+      <c r="BM36" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN36" t="s">
+      <c r="BN36" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO36" s="48">
@@ -4619,14 +4646,14 @@
       <c r="F37" s="46">
         <v>2</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H37" s="46">
         <f>F37*G37</f>
         <v>1000</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J37" s="46">
@@ -4754,20 +4781,20 @@
       <c r="AQ37" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR37">
+      <c r="AR37" s="0">
         <f>ROUND(AN37+AO37+AP37,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS37" t="s">
+      <c r="AS37" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU37" t="s">
+      <c r="AU37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV37" t="s">
+      <c r="AV37" t="s" s="0">
         <v>170</v>
       </c>
       <c r="AW37" s="48">
@@ -4806,10 +4833,10 @@
       <c r="BL37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM37" t="s">
+      <c r="BM37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN37" t="s">
+      <c r="BN37" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO37" s="48">
@@ -4835,34 +4862,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -6374,10 +6401,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -6388,14 +6415,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -6523,20 +6550,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -6575,10 +6602,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -6753,32 +6780,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -8290,10 +8317,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -8304,14 +8331,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -8439,12 +8466,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -8654,34 +8681,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -10193,10 +10220,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -10207,14 +10234,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -10342,20 +10369,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -10394,10 +10421,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -10572,32 +10599,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -12109,10 +12136,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -12123,14 +12150,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -12258,12 +12285,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -12473,34 +12500,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -14012,10 +14039,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -14026,14 +14053,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -14161,20 +14188,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -14213,10 +14240,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -14391,32 +14418,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -15928,10 +15955,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -15942,14 +15969,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -16077,12 +16104,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -16292,34 +16319,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -17831,10 +17858,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -17980,20 +18007,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -18032,10 +18059,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>176</v>
       </c>
       <c r="BO23" s="48">
@@ -18043,8 +18070,8 @@
         <v>846.99</v>
       </c>
       <c r="BP23" s="61">
-        <f>BN23+AW23</f>
-        <v>0.66666666666666663</v>
+        <f>ROUND((BN23+AW23),3)</f>
+        <v>2.0009999999999999</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -18207,34 +18234,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -19746,10 +19773,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -19895,20 +19922,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -19947,10 +19974,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>150</v>
       </c>
       <c r="BO23" s="48">
@@ -19958,7 +19985,7 @@
         <v>282.33</v>
       </c>
       <c r="BP23" s="4">
-        <f>BN23+AW23</f>
+        <f>ROUND((BN23+AW23),3)</f>
         <v>8</v>
       </c>
       <c r="BQ23" s="50">
@@ -20122,32 +20149,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -21659,10 +21686,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -21673,14 +21700,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -21808,12 +21835,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -22023,34 +22050,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -23562,10 +23589,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -23576,14 +23603,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23">
-        <v>200</v>
+      <c r="G23" t="s" s="0">
+        <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -23711,21 +23738,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>570.48</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>181</v>
+      <c r="AV23" t="s" s="0">
+        <v>200</v>
       </c>
       <c r="AW23" s="16">
         <f>AM23</f>
@@ -23763,11 +23790,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>182</v>
+      <c r="BM23" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>203</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),3)</f>
@@ -23938,34 +23965,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -25477,10 +25504,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -25626,20 +25653,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -25678,10 +25705,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>155</v>
       </c>
       <c r="BO23" s="48">
@@ -25854,34 +25881,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -27393,10 +27420,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -27407,14 +27434,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23">
-        <v>200</v>
+      <c r="G23" t="s" s="0">
+        <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -27542,21 +27569,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>558.96</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>177</v>
+      <c r="AV23" t="s" s="0">
+        <v>194</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -27594,19 +27621,19 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>130</v>
+      <c r="BM23" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>198</v>
       </c>
       <c r="BO23" s="48">
-        <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>127.75714000000001</v>
+        <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),3)</f>
+        <v>566.36599999999999</v>
       </c>
       <c r="BP23" s="4">
-        <f>BN23+AW23</f>
-        <v>4.666666666666667</v>
+        <f>ROUND((BN23+AW23),3)</f>
+        <v>9.3379999999999992</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -27769,32 +27796,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -29306,10 +29333,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -29320,14 +29347,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="0">
         <v>200</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -29455,12 +29482,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>188.22</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -29506,7 +29533,7 @@
         <v>188.22</v>
       </c>
       <c r="BP23" s="4">
-        <f>BN23+AW23</f>
+        <f>ROUND((BN23+AW23),3)</f>
         <v>2</v>
       </c>
       <c r="BQ23" s="50">
@@ -29670,34 +29697,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -31209,10 +31236,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -31223,15 +31250,15 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23">
-        <v>200</v>
+      <c r="G23" t="s" s="0">
+        <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
-        <v>115</v>
+      <c r="I23" t="s" s="0">
+        <v>127</v>
       </c>
       <c r="J23" s="46">
         <v>2</v>
@@ -31358,21 +31385,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>178</v>
+      <c r="AV23" t="s" s="0">
+        <v>194</v>
       </c>
       <c r="AW23" s="16">
         <f>AM23</f>
@@ -31410,19 +31437,19 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>178</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>150</v>
+      <c r="BM23" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>196</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
         <v>107.28</v>
       </c>
-      <c r="BP23" s="4">
-        <f>BN23+AW23</f>
-        <v>6.666666666666667</v>
+      <c r="BP23" s="61">
+        <f>ROUND((BN23+AW23),3)</f>
+        <v>6.6669999999999998</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -31588,34 +31615,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -33127,10 +33154,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -33141,15 +33168,15 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23">
-        <v>200</v>
+      <c r="G23" t="s" s="0">
+        <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
-        <v>115</v>
+      <c r="I23" t="s" s="0">
+        <v>127</v>
       </c>
       <c r="J23" s="46">
         <v>2</v>
@@ -33276,21 +33303,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>178</v>
+      <c r="AV23" t="s" s="0">
+        <v>194</v>
       </c>
       <c r="AW23" s="16">
         <f>AM23</f>
@@ -33328,19 +33355,19 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>178</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>158</v>
+      <c r="BM23" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>195</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
         <v>76.787999999999997</v>
       </c>
-      <c r="BP23" s="4">
-        <f>BN23+AW23</f>
-        <v>16.666666666666668</v>
+      <c r="BP23" s="61">
+        <f>ROUND((BN23+AW23),3)</f>
+        <v>8.6709999999999994</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -33506,32 +33533,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -35043,10 +35070,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -35057,14 +35084,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -35192,12 +35219,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -35407,32 +35434,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -36944,10 +36971,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -37093,20 +37120,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -37145,10 +37172,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>164</v>
       </c>
       <c r="BO23" s="48">
@@ -37323,32 +37350,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -38860,10 +38887,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -39009,12 +39036,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -39224,34 +39251,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -40763,10 +40790,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -40777,14 +40804,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -40912,21 +40939,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>194</v>
+      <c r="AV23" t="s" s="0">
+        <v>192</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -40964,10 +40991,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -41140,32 +41167,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -42677,10 +42704,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -42691,14 +42718,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -42826,12 +42853,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -43041,34 +43068,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -44580,10 +44607,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -44594,14 +44621,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -44729,21 +44756,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV23" t="s">
-        <v>179</v>
+      <c r="AV23" t="s" s="0">
+        <v>177</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -44781,10 +44808,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>180</v>
-      </c>
-      <c r="BN23" t="s">
+      <c r="BM23" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="BN23" t="s" s="0">
         <v>131</v>
       </c>
       <c r="BO23" s="48">
@@ -44960,32 +44987,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -46497,10 +46524,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -46511,14 +46538,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -46646,12 +46673,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -46862,34 +46889,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -48401,10 +48428,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -48415,14 +48442,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -48550,20 +48577,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>193</v>
+      <c r="AS23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW23" s="48">
@@ -48602,10 +48629,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48">

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="16" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -21799,15 +21799,15 @@
         <v>0</v>
       </c>
       <c r="AL23" s="46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM23" s="46">
         <f>F23/AL23</f>
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>282.33</v>
+        <v>846.99</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -21822,7 +21822,7 @@
       </c>
       <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>282.33</v>
+        <v>846.99</v>
       </c>
       <c r="AS23" t="s">
         <v>188</v>
@@ -21838,19 +21838,19 @@
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
-        <v>2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>282.33</v>
+        <v>846.99</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
-        <v>14</v>
+        <v>12.666666666666666</v>
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>282.33</v>
+        <v>312.04894999999999</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -21880,11 +21880,11 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>282.33</v>
+        <v>285.30189999999999</v>
       </c>
       <c r="BP23" s="4">
         <f>ROUND((BN23+AW23),3)</f>
-        <v>8</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5528" uniqueCount="230">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -727,6 +727,27 @@
   </si>
   <si>
     <t>294</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>880.96853</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>879.88404</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>878.80347</t>
+  </si>
+  <si>
+    <t>1810.39779</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1595,7 @@
   <dimension ref="A8:BR37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="27.28515625"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:70" ht="15.75" thickBot="1"/>
@@ -1742,10 +1763,10 @@
       <c r="AT9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU9" t="s">
+      <c r="AU9" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AV9" t="s" s="0">
         <v>143</v>
       </c>
       <c r="AW9" s="48">
@@ -1786,10 +1807,10 @@
       <c r="BL9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" t="s">
+      <c r="BM9" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BN9" t="s" s="0">
         <v>147</v>
       </c>
       <c r="BO9" s="48" t="e">
@@ -1961,20 +1982,20 @@
       <c r="AQ15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR15" t="e">
+      <c r="AR15" t="e" s="0">
         <f>ROUND(AN15+AO15+AP15,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS15" t="s">
+      <c r="AS15" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU15" t="s">
+      <c r="AU15" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV15" t="s">
+      <c r="AV15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW15" s="48">
@@ -2013,10 +2034,10 @@
       <c r="BL15" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM15" t="s">
+      <c r="BM15" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN15" t="s">
+      <c r="BN15" t="s" s="0">
         <v>150</v>
       </c>
       <c r="BO15" s="48" t="e">
@@ -2186,20 +2207,20 @@
       <c r="AQ16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="0">
         <f>ROUND(AN16+AO16+AP16,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS16" t="s">
+      <c r="AS16" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU16" t="s">
+      <c r="AU16" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="AV16" t="s">
+      <c r="AV16" t="s" s="0">
         <v>136</v>
       </c>
       <c r="AW16" s="48">
@@ -2238,10 +2259,10 @@
       <c r="BL16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM16" t="s">
+      <c r="BM16" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="BN16" t="s">
+      <c r="BN16" t="s" s="0">
         <v>133</v>
       </c>
       <c r="BO16" s="48">
@@ -2411,20 +2432,20 @@
       <c r="AQ17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR17">
+      <c r="AR17" s="0">
         <f>ROUND(AN17+AO17+AP17,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS17" t="s">
+      <c r="AS17" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU17" t="s">
+      <c r="AU17" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AV17" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW17" s="48">
@@ -2630,20 +2651,20 @@
       <c r="AQ18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR18">
+      <c r="AR18" s="0">
         <f>ROUND(AN18+AO18+AP18,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS18" t="s">
+      <c r="AS18" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU18" t="s">
+      <c r="AU18" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="AV18" t="s">
+      <c r="AV18" t="s" s="0">
         <v>137</v>
       </c>
       <c r="AW18" s="48">
@@ -2682,10 +2703,10 @@
       <c r="BL18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM18" t="s">
+      <c r="BM18" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="BN18" t="s">
+      <c r="BN18" t="s" s="0">
         <v>152</v>
       </c>
       <c r="BO18" s="48">
@@ -2856,20 +2877,20 @@
       <c r="AQ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR20" t="e">
+      <c r="AR20" t="e" s="0">
         <f>ROUND(AN20+AO20+AP20,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS20" t="s">
+      <c r="AS20" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU20" t="s">
+      <c r="AU20" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="AV20" t="s">
+      <c r="AV20" t="s" s="0">
         <v>156</v>
       </c>
       <c r="AW20" s="48">
@@ -2908,10 +2929,10 @@
       <c r="BL20" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM20" t="s">
+      <c r="BM20" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="BN20" t="s">
+      <c r="BN20" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO20" s="48" t="e">
@@ -3081,20 +3102,20 @@
       <c r="AQ21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" t="e">
+      <c r="AR21" t="e" s="0">
         <f t="shared" ref="AR21:AR23" si="30">ROUND(AN21+AO21+AP21,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS21" t="s">
+      <c r="AS21" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU21" t="s">
+      <c r="AU21" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV21" t="s">
+      <c r="AV21" t="s" s="0">
         <v>157</v>
       </c>
       <c r="AW21" s="48">
@@ -3133,10 +3154,10 @@
       <c r="BL21" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM21" t="s">
+      <c r="BM21" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN21" t="s">
+      <c r="BN21" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO21" s="48" t="e">
@@ -3306,20 +3327,20 @@
       <c r="AQ22" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR22" t="e">
+      <c r="AR22" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS22" t="s">
+      <c r="AS22" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU22" t="s">
+      <c r="AU22" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV22" t="s">
+      <c r="AV22" t="s" s="0">
         <v>159</v>
       </c>
       <c r="AW22" s="48">
@@ -3358,10 +3379,10 @@
       <c r="BL22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM22" t="s">
+      <c r="BM22" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN22" t="s">
+      <c r="BN22" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO22" s="48" t="e">
@@ -3531,20 +3552,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" t="e">
+      <c r="AR23" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>160</v>
       </c>
       <c r="AW23" s="48">
@@ -3583,10 +3604,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48" t="e">
@@ -3643,14 +3664,14 @@
       <c r="F31" s="46">
         <v>2</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H31" s="46">
         <f>F31*G31</f>
         <v>600</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J31" s="46">
@@ -3778,20 +3799,20 @@
       <c r="AQ31" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR31">
+      <c r="AR31" s="0">
         <f>ROUND(AN31+AO31+AP31,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS31" t="s">
+      <c r="AS31" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU31" t="s">
+      <c r="AU31" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="AV31" t="s">
+      <c r="AV31" t="s" s="0">
         <v>167</v>
       </c>
       <c r="AW31" s="48">
@@ -3830,10 +3851,10 @@
       <c r="BL31" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM31" t="s">
+      <c r="BM31" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN31" t="s">
+      <c r="BN31" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO31" s="48">
@@ -3868,14 +3889,14 @@
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H32" s="46">
         <f>F32*G32</f>
         <v>800</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J32" s="46">
@@ -4003,20 +4024,20 @@
       <c r="AQ32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR32">
+      <c r="AR32" s="0">
         <f>ROUND(AN32+AO32+AP32,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS32" t="s">
+      <c r="AS32" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT32" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU32" t="s">
+      <c r="AU32" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="AV32" t="s">
+      <c r="AV32" t="s" s="0">
         <v>169</v>
       </c>
       <c r="AW32" s="48">
@@ -4055,10 +4076,10 @@
       <c r="BL32" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM32" t="s">
+      <c r="BM32" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN32" t="s">
+      <c r="BN32" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO32" s="48">
@@ -4093,14 +4114,14 @@
       <c r="F33" s="46">
         <v>2</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H33" s="46">
         <f>F33*G33</f>
         <v>1000</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J33" s="46">
@@ -4228,20 +4249,20 @@
       <c r="AQ33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR33">
+      <c r="AR33" s="0">
         <f>ROUND(AN33+AO33+AP33,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS33" t="s">
+      <c r="AS33" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT33" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU33" t="s">
+      <c r="AU33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV33" t="s">
+      <c r="AV33" t="s" s="0">
         <v>170</v>
       </c>
       <c r="AW33" s="48">
@@ -4280,10 +4301,10 @@
       <c r="BL33" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM33" t="s">
+      <c r="BM33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN33" t="s">
+      <c r="BN33" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO33" s="48">
@@ -4319,14 +4340,14 @@
       <c r="F35" s="46">
         <v>2</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H35" s="46">
         <f>F35*G35</f>
         <v>600</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J35" s="46">
@@ -4454,20 +4475,20 @@
       <c r="AQ35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR35">
+      <c r="AR35" s="0">
         <f>ROUND(AN35+AO35+AP35,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS35" t="s">
+      <c r="AS35" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU35" t="s">
+      <c r="AU35" t="s" s="0">
         <v>171</v>
       </c>
-      <c r="AV35" t="s">
+      <c r="AV35" t="s" s="0">
         <v>172</v>
       </c>
       <c r="AW35" s="48">
@@ -4506,10 +4527,10 @@
       <c r="BL35" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM35" t="s">
+      <c r="BM35" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN35" t="s">
+      <c r="BN35" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO35" s="48">
@@ -4544,14 +4565,14 @@
       <c r="F36" s="46">
         <v>2</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H36" s="46">
         <f>F36*G36</f>
         <v>800</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J36" s="46">
@@ -4679,20 +4700,20 @@
       <c r="AQ36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR36">
+      <c r="AR36" s="0">
         <f>ROUND(AN36+AO36+AP36,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS36" t="s">
+      <c r="AS36" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU36" t="s">
+      <c r="AU36" t="s" s="0">
         <v>173</v>
       </c>
-      <c r="AV36" t="s">
+      <c r="AV36" t="s" s="0">
         <v>174</v>
       </c>
       <c r="AW36" s="48">
@@ -4731,10 +4752,10 @@
       <c r="BL36" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM36" t="s">
+      <c r="BM36" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN36" t="s">
+      <c r="BN36" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO36" s="48">
@@ -4769,14 +4790,14 @@
       <c r="F37" s="46">
         <v>2</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H37" s="46">
         <f>F37*G37</f>
         <v>1000</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J37" s="46">
@@ -4904,20 +4925,20 @@
       <c r="AQ37" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR37">
+      <c r="AR37" s="0">
         <f>ROUND(AN37+AO37+AP37,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS37" t="s">
+      <c r="AS37" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU37" t="s">
+      <c r="AU37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV37" t="s">
+      <c r="AV37" t="s" s="0">
         <v>170</v>
       </c>
       <c r="AW37" s="48">
@@ -4956,10 +4977,10 @@
       <c r="BL37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM37" t="s">
+      <c r="BM37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN37" t="s">
+      <c r="BN37" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO37" s="48">
@@ -4985,34 +5006,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -6538,14 +6559,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -6673,20 +6694,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>177</v>
       </c>
       <c r="AW23" s="48">
@@ -6725,10 +6746,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>131</v>
       </c>
       <c r="BO23" s="48">
@@ -6904,32 +6925,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -8455,14 +8476,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -8590,11 +8611,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -8806,34 +8827,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -10359,14 +10380,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -10494,20 +10515,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW23" s="48">
@@ -10546,10 +10567,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -10724,34 +10745,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -12277,14 +12298,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -12412,20 +12433,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -12464,10 +12485,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -12642,32 +12663,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -14193,14 +14214,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -14328,11 +14349,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -14543,34 +14564,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -16096,14 +16117,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -16231,20 +16252,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -16283,10 +16304,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -16461,32 +16482,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -18012,14 +18033,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -18147,11 +18168,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -18362,34 +18383,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -19915,14 +19936,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -20050,20 +20071,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>189</v>
       </c>
       <c r="AW23" s="48">
@@ -20102,10 +20123,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>195</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>194</v>
       </c>
       <c r="BO23" s="48">
@@ -20280,32 +20301,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -21831,14 +21852,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -21966,11 +21987,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -22181,34 +22202,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -23869,20 +23890,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -23921,10 +23942,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>176</v>
       </c>
       <c r="BO23" s="48">
@@ -24096,34 +24117,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -25784,20 +25805,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -25836,10 +25857,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>155</v>
       </c>
       <c r="BO23" s="48">
@@ -26012,34 +26033,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -27700,20 +27721,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -27752,10 +27773,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>196</v>
       </c>
       <c r="BO23" s="48">
@@ -27927,32 +27948,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -29478,14 +29499,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -29613,11 +29634,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -29828,34 +29849,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -31381,14 +31402,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -31516,20 +31537,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>570.48</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>191</v>
       </c>
       <c r="AW23" s="16">
@@ -31568,10 +31589,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>197</v>
       </c>
       <c r="BO23" s="48">
@@ -31743,34 +31764,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -33296,14 +33317,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -33431,20 +33452,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>558.96</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>191</v>
       </c>
       <c r="AW23" s="48">
@@ -33483,10 +33504,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>199</v>
       </c>
       <c r="BO23" s="48">
@@ -33658,32 +33679,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -35209,14 +35230,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -35344,11 +35365,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>188.22</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -35559,34 +35580,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -37112,14 +37133,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -37247,20 +37268,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>191</v>
       </c>
       <c r="AW23" s="16">
@@ -37299,10 +37320,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>193</v>
       </c>
       <c r="BO23" s="48">
@@ -37477,34 +37498,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -39030,14 +39051,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -39165,20 +39186,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>191</v>
       </c>
       <c r="AW23" s="16">
@@ -39217,10 +39238,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>192</v>
       </c>
       <c r="BO23" s="48">
@@ -39395,32 +39416,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -40946,14 +40967,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -41081,11 +41102,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -41296,34 +41317,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -42984,20 +43005,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>28.23</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>209</v>
       </c>
       <c r="AW23" s="66">
@@ -43036,10 +43057,10 @@
       <c r="BL23" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>211</v>
       </c>
       <c r="BO23" s="66">
@@ -43211,34 +43232,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -44899,20 +44920,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="66">
@@ -44951,10 +44972,10 @@
       <c r="BL23" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>213</v>
       </c>
       <c r="BO23" s="66">
@@ -45124,20 +45145,20 @@
       <c r="AQ24" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR24">
+      <c r="AR24" s="0">
         <f>ROUND(AN24+AO24+AP24,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS24" t="s">
+      <c r="AS24" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT24" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU24" t="s">
+      <c r="AU24" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV24" t="s">
+      <c r="AV24" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW24" s="66">
@@ -45176,10 +45197,10 @@
       <c r="BL24" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BM24" t="s">
+      <c r="BM24" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="BN24" t="s">
+      <c r="BN24" t="s" s="0">
         <v>216</v>
       </c>
       <c r="BO24" s="66">
@@ -45351,36 +45372,36 @@
   <dimension ref="A1:BU25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
-    <col min="71" max="71" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="18" max="18" customWidth="true" width="14.85546875"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="71" max="71" customWidth="true" width="22.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -47051,20 +47072,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -47103,10 +47124,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23">
+      <c r="BM23" s="0">
         <v>292.60462000000001</v>
       </c>
-      <c r="BN23">
+      <c r="BN23" s="0">
         <v>682</v>
       </c>
       <c r="BO23" s="48">
@@ -47288,35 +47309,35 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -48977,20 +48998,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="66">
@@ -49029,10 +49050,10 @@
       <c r="BL23" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>173</v>
       </c>
       <c r="BO23" s="66">
@@ -49204,35 +49225,35 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -50893,20 +50914,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="66">
@@ -50945,10 +50966,10 @@
       <c r="BL23" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>219</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>220</v>
       </c>
       <c r="BO23" s="66">
@@ -51118,20 +51139,20 @@
       <c r="AQ24" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR24">
+      <c r="AR24" s="0">
         <f>ROUND(AN24+AO24+AP24,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS24" t="s">
+      <c r="AS24" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT24" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU24" t="s">
+      <c r="AU24" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV24" t="s">
+      <c r="AV24" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW24" s="66">
@@ -51170,10 +51191,10 @@
       <c r="BL24" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="BM24" t="s">
+      <c r="BM24" t="s" s="0">
         <v>221</v>
       </c>
-      <c r="BN24" t="s">
+      <c r="BN24" t="s" s="0">
         <v>222</v>
       </c>
       <c r="BO24" s="66">
@@ -51345,34 +51366,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -53033,20 +53054,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="66">
@@ -53085,11 +53106,11 @@
       <c r="BL23" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>219</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>220</v>
+      <c r="BM23" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>227</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -53258,20 +53279,20 @@
       <c r="AQ24" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR24">
+      <c r="AR24" s="0">
         <f>ROUND(AN24+AO24+AP24,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS24" t="s">
+      <c r="AS24" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT24" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU24" t="s">
+      <c r="AU24" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV24" t="s">
+      <c r="AV24" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW24" s="66">
@@ -53310,11 +53331,11 @@
       <c r="BL24" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BM24" t="s">
-        <v>221</v>
-      </c>
-      <c r="BN24" t="s">
-        <v>222</v>
+      <c r="BM24" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="BN24" t="s" s="0">
+        <v>213</v>
       </c>
       <c r="BO24" s="66">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -53485,37 +53506,37 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="18" max="18" width="11.28515625" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="23.85546875" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="50" max="50" width="11" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="18" max="18" customWidth="true" width="11.28515625"/>
+    <col min="19" max="19" customWidth="true" width="11.140625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="23.85546875"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="50" max="50" customWidth="true" width="11.0"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -55044,14 +55065,14 @@
       <c r="F23" s="46">
         <v>5</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>1000</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -55179,20 +55200,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.31800000000001</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>189</v>
       </c>
       <c r="AW23" s="48">
@@ -55231,10 +55252,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>207</v>
       </c>
       <c r="BO23" s="48">
@@ -55410,34 +55431,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -56966,7 +56987,7 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="0">
         <v>300</v>
       </c>
       <c r="H23" s="46">
@@ -57101,20 +57122,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -57153,11 +57174,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>206</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>205</v>
+      <c r="BM23" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>225</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -57332,32 +57353,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -59018,20 +59039,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -59070,10 +59091,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>164</v>
       </c>
       <c r="BO23" s="48">
@@ -59248,32 +59269,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -60934,11 +60955,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -61149,34 +61170,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -62702,14 +62723,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -62837,20 +62858,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>189</v>
       </c>
       <c r="AW23" s="48">
@@ -62889,10 +62910,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -63065,32 +63086,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -64616,14 +64637,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -64751,11 +64772,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5528" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5570" uniqueCount="240">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -748,6 +748,36 @@
   </si>
   <si>
     <t>1810.39779</t>
+  </si>
+  <si>
+    <t>1225</t>
+  </si>
+  <si>
+    <t>186.65529</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>186.65393</t>
+  </si>
+  <si>
+    <t>1235</t>
+  </si>
+  <si>
+    <t>186.65258</t>
+  </si>
+  <si>
+    <t>1240</t>
+  </si>
+  <si>
+    <t>186.65124</t>
+  </si>
+  <si>
+    <t>1245</t>
+  </si>
+  <si>
+    <t>186.64991</t>
   </si>
 </sst>
 </file>
@@ -55253,10 +55283,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5570" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5588" uniqueCount="244">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -778,6 +778,18 @@
   </si>
   <si>
     <t>186.64991</t>
+  </si>
+  <si>
+    <t>1250</t>
+  </si>
+  <si>
+    <t>186.64859</t>
+  </si>
+  <si>
+    <t>1255</t>
+  </si>
+  <si>
+    <t>186.64728</t>
   </si>
 </sst>
 </file>
@@ -55283,10 +55295,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6009" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5903" uniqueCount="245">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -659,12 +659,6 @@
     <t>565.52002</t>
   </si>
   <si>
-    <t>51.359</t>
-  </si>
-  <si>
-    <t>565.24365</t>
-  </si>
-  <si>
     <t>Cost</t>
   </si>
   <si>
@@ -734,162 +728,82 @@
     <t>1810.39779</t>
   </si>
   <si>
-    <t>5563</t>
-  </si>
-  <si>
-    <t>186.43777</t>
-  </si>
-  <si>
-    <t>5628</t>
-  </si>
-  <si>
-    <t>186.43643</t>
-  </si>
-  <si>
     <t>TDS</t>
   </si>
   <si>
     <t>194Q</t>
   </si>
   <si>
-    <t>5633</t>
+    <t>Matched Amt</t>
   </si>
   <si>
-    <t>186.43633</t>
+    <t>GRN Amt</t>
   </si>
   <si>
-    <t>5638</t>
+    <t>Proc.Qty</t>
   </si>
   <si>
-    <t>186.43623</t>
+    <t>UnitCost</t>
   </si>
   <si>
-    <t>5643</t>
+    <t>Curr.Matched Amt</t>
   </si>
   <si>
-    <t>186.43613</t>
+    <t>Deviation Amt</t>
   </si>
   <si>
-    <t>5648</t>
+    <t>375.00</t>
   </si>
   <si>
-    <t>186.43603</t>
+    <t>558.95</t>
   </si>
   <si>
-    <t>5653</t>
+    <t>234.783</t>
   </si>
   <si>
-    <t>186.43593</t>
+    <t>564.71998</t>
   </si>
   <si>
-    <t>5658</t>
+    <t>186.318</t>
   </si>
   <si>
-    <t>186.43583</t>
+    <t>931.59</t>
   </si>
   <si>
-    <t>5663</t>
+    <t>5.000</t>
   </si>
   <si>
-    <t>186.43573</t>
+    <t>Expense Amnt</t>
   </si>
   <si>
-    <t>5668</t>
+    <t>ServiceItem Amnt</t>
   </si>
   <si>
-    <t>186.43563</t>
+    <t>7134</t>
   </si>
   <si>
-    <t>5673</t>
+    <t>186.49443</t>
   </si>
   <si>
-    <t>186.43553</t>
+    <t>7209</t>
   </si>
   <si>
-    <t>5678</t>
+    <t>186.49927</t>
   </si>
   <si>
-    <t>186.43543</t>
+    <t>7214</t>
   </si>
   <si>
-    <t>5683</t>
-  </si>
-  <si>
-    <t>186.43533</t>
-  </si>
-  <si>
-    <t>5688</t>
-  </si>
-  <si>
-    <t>186.43523</t>
-  </si>
-  <si>
-    <t>5693</t>
-  </si>
-  <si>
-    <t>186.43513</t>
-  </si>
-  <si>
-    <t>5698</t>
-  </si>
-  <si>
-    <t>186.43503</t>
-  </si>
-  <si>
-    <t>5703</t>
-  </si>
-  <si>
-    <t>186.43493</t>
-  </si>
-  <si>
-    <t>5720</t>
-  </si>
-  <si>
-    <t>186.43555</t>
-  </si>
-  <si>
-    <t>5725</t>
-  </si>
-  <si>
-    <t>186.43545</t>
-  </si>
-  <si>
-    <t>5730</t>
-  </si>
-  <si>
-    <t>186.43535</t>
-  </si>
-  <si>
-    <t>5735</t>
-  </si>
-  <si>
-    <t>186.43525</t>
-  </si>
-  <si>
-    <t>5740</t>
-  </si>
-  <si>
-    <t>186.43515</t>
-  </si>
-  <si>
-    <t>5745</t>
-  </si>
-  <si>
-    <t>186.43505</t>
-  </si>
-  <si>
-    <t>5750</t>
-  </si>
-  <si>
-    <t>186.43495</t>
+    <t>186.49914</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1265,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1429,6 +1343,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1441,7 +1359,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5186,37 +5103,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="63"/>
       <c r="AE1" s="63"/>
       <c r="AF1" s="63"/>
@@ -6310,14 +6227,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -6410,10 +6327,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -7100,37 +7017,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="58"/>
       <c r="AE1" s="58"/>
       <c r="AF1" s="58"/>
@@ -8224,14 +8141,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -8324,10 +8241,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -8623,14 +8540,14 @@
         <v>2</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J23" s="46">
         <v>2</v>
@@ -9003,37 +8920,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="59"/>
       <c r="AE1" s="59"/>
       <c r="AF1" s="59"/>
@@ -10127,14 +10044,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -10227,10 +10144,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -10920,37 +10837,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -12044,14 +11961,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -12144,10 +12061,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -12824,37 +12741,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -13948,14 +13865,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -14048,10 +13965,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -14742,37 +14659,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -15866,14 +15783,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -15966,10 +15883,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -16658,37 +16575,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -17782,14 +17699,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -17882,10 +17799,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -18561,37 +18478,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -19685,14 +19602,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -19785,10 +19702,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -20477,37 +20394,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -21601,14 +21518,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -21701,10 +21618,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -22380,37 +22297,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -23504,14 +23421,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -23604,10 +23521,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -24298,37 +24215,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="64"/>
       <c r="AE1" s="64"/>
       <c r="AF1" s="64"/>
@@ -25422,14 +25339,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -25522,10 +25439,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>2</v>
       </c>
@@ -26212,37 +26129,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -27336,14 +27253,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -27436,10 +27353,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -28115,37 +28032,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -29239,14 +29156,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -29339,10 +29256,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -30030,37 +29947,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -31154,14 +31071,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -31254,10 +31171,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -31943,37 +31860,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -33067,14 +32984,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -33167,10 +33084,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -33846,37 +33763,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -34970,14 +34887,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -35070,10 +34987,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -35761,37 +35678,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -36885,14 +36802,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -36985,10 +36902,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -37281,14 +37198,14 @@
         <v>166</v>
       </c>
       <c r="F23" s="46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>127</v>
@@ -37301,35 +37218,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>392</v>
+        <v>588</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>7.84</v>
+        <v>11.76</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>384.16</v>
+        <v>576.24</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>11.52</v>
+        <v>17.29</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>27.36</v>
+        <v>41.05</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>372.64</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -37339,11 +37256,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>33.54</v>
+        <v>50.31</v>
       </c>
       <c r="W23" s="46">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>33.54</v>
+        <v>50.31</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -37358,15 +37275,15 @@
       </c>
       <c r="AA23" s="46">
         <f>IF($C21=3,0,S23*Z23)</f>
-        <v>22.3584</v>
+        <v>33.536999999999999</v>
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>89.438400000000001</v>
+        <v>134.15700000000001</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>462.07839999999999</v>
+        <v>693.10700000000008</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -37386,7 +37303,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>372.64</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -37401,11 +37318,11 @@
       </c>
       <c r="AM23" s="46">
         <f>F23/AL23</f>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>558.96</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -37419,8 +37336,8 @@
         <v>12</v>
       </c>
       <c r="AR23" s="0">
-        <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>558.96</v>
+        <f>AN23+AO23+AP23</f>
+        <v>558.95000000000005</v>
       </c>
       <c r="AS23" t="s" s="0">
         <v>188</v>
@@ -37432,23 +37349,23 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>558.96</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>558.96</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -37471,18 +37388,18 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>565.49843999999996</v>
+        <v>564.76169000000004</v>
       </c>
       <c r="BP23" s="4">
         <f>ROUND((BN23+AW23),3)</f>
-        <v>49.357999999999997</v>
+        <v>230.44800000000001</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -37501,7 +37418,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -37514,21 +37431,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>27.36</v>
+        <v>41.05</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>372.64</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>33.54</v>
+        <v>50.31</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>33.54</v>
+        <v>50.31</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -37539,11 +37456,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>89.438400000000001</v>
+        <v>134.15700000000001</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>462.07839999999999</v>
+        <v>693.10700000000008</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -37564,7 +37481,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>372.64</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -37674,37 +37591,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -38798,14 +38715,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -38898,10 +38815,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -39577,37 +39494,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -40701,14 +40618,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -40801,10 +40718,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -41495,37 +41412,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
       <c r="AF1" s="62"/>
@@ -42619,14 +42536,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -42719,10 +42636,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -43411,37 +43328,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="60"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="60"/>
@@ -44535,14 +44452,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -44635,10 +44552,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -45316,37 +45233,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="96"/>
       <c r="AE1" s="96"/>
       <c r="AF1" s="96"/>
@@ -46440,14 +46357,14 @@
     </row>
     <row r="19" spans="1:73" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -46540,10 +46457,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:73" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>2</v>
       </c>
@@ -46819,16 +46736,16 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="BS22" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="BT22" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="BS22" s="69" t="s">
-        <v>202</v>
-      </c>
-      <c r="BT22" s="69" t="s">
-        <v>203</v>
-      </c>
-      <c r="BU22" s="101" t="s">
-        <v>228</v>
+      <c r="BU22" s="97" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:73" ht="15.75" thickBot="1">
@@ -46858,7 +46775,7 @@
         <v>600</v>
       </c>
       <c r="I23" s="46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="46">
         <v>2</v>
@@ -46872,31 +46789,31 @@
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>11.88</v>
+        <v>11.76</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>582.12</v>
+        <v>576.24</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>17.46</v>
+        <v>17.29</v>
       </c>
       <c r="R23" s="72">
         <f>ROUND(M23+O23+Q23,3)</f>
-        <v>35.340000000000003</v>
+        <v>41.05</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -46914,7 +46831,7 @@
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
-        <v>101.64</v>
+        <v>100.61</v>
       </c>
       <c r="Y23" s="46">
         <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
@@ -46929,11 +46846,11 @@
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>101.64</v>
+        <v>100.61</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>666.3</v>
+        <v>659.56000000000006</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -46953,7 +46870,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -46972,7 +46889,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -46987,7 +46904,7 @@
       </c>
       <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="AS23" t="s" s="0">
         <v>188</v>
@@ -47007,7 +46924,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -47015,7 +46932,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -47045,7 +46962,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>292.57458000000003</v>
+        <v>292.56623000000002</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -47059,13 +46976,13 @@
         <v>400</v>
       </c>
       <c r="BS23" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
       <c r="BU23" t="s" s="0">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:73" ht="15.75" thickBot="1">
@@ -47093,11 +47010,11 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>35.340000000000003</v>
+        <v>41.05</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
@@ -47111,18 +47028,18 @@
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
-        <v>101.64</v>
+        <v>100.61</v>
       </c>
       <c r="Y24" s="55"/>
       <c r="Z24" s="55"/>
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>101.64</v>
+        <v>100.61</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>666.3</v>
+        <v>659.56000000000006</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -47143,7 +47060,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -47256,37 +47173,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="73"/>
       <c r="AE1" s="73"/>
       <c r="AF1" s="73"/>
@@ -48380,14 +48297,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="75"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -48480,10 +48397,10 @@
       <c r="AS20" s="75"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="100"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="13">
         <v>3</v>
       </c>
@@ -48927,7 +48844,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AW23" s="66">
         <f>AM23</f>
@@ -48966,10 +48883,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -49171,37 +49088,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="73"/>
       <c r="AE1" s="73"/>
       <c r="AF1" s="73"/>
@@ -50295,14 +50212,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="75"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -50395,10 +50312,10 @@
       <c r="AS20" s="75"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="100"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="13">
         <v>3</v>
       </c>
@@ -50881,10 +50798,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -50904,10 +50821,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>12</v>
@@ -51106,10 +51023,10 @@
         <v>148</v>
       </c>
       <c r="BM24" t="s" s="0">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="BN24" t="s" s="0">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="BO24" s="66">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -51312,37 +51229,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="73"/>
       <c r="AE1" s="73"/>
       <c r="AF1" s="73"/>
@@ -52436,14 +52353,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="75"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -52536,10 +52453,10 @@
       <c r="AS20" s="75"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="100"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -53019,10 +52936,10 @@
       <c r="BH23" s="3"/>
       <c r="BI23" s="66"/>
       <c r="BL23" s="66" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="BN23" t="s" s="0">
         <v>173</v>
@@ -53228,37 +53145,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="73"/>
       <c r="AE1" s="73"/>
       <c r="AF1" s="73"/>
@@ -54352,14 +54269,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="75"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -54452,10 +54369,10 @@
       <c r="AS20" s="75"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="100"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -54935,13 +54852,13 @@
       <c r="BH23" s="3"/>
       <c r="BI23" s="66"/>
       <c r="BL23" s="66" t="s">
+        <v>211</v>
+      </c>
+      <c r="BM23" t="s" s="0">
         <v>213</v>
       </c>
-      <c r="BM23" t="s" s="0">
-        <v>215</v>
-      </c>
       <c r="BN23" t="s" s="0">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -54961,10 +54878,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>12</v>
@@ -55160,13 +55077,13 @@
       <c r="BH24" s="3"/>
       <c r="BI24" s="66"/>
       <c r="BL24" s="66" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="BM24" t="s" s="0">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="BN24" t="s" s="0">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="BO24" s="66">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -55368,37 +55285,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="73"/>
       <c r="AE1" s="73"/>
       <c r="AF1" s="73"/>
@@ -56492,14 +56409,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="75"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -56592,10 +56509,10 @@
       <c r="AS20" s="75"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="100"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -57078,10 +56995,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -57101,10 +57018,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>12</v>
@@ -57303,10 +57220,10 @@
         <v>148</v>
       </c>
       <c r="BM24" t="s" s="0">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BN24" t="s" s="0">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BO24" s="66">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -57510,37 +57427,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="68"/>
       <c r="AE1" s="68"/>
       <c r="AF1" s="68"/>
@@ -58634,14 +58551,14 @@
     </row>
     <row r="19" spans="1:73" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -58734,10 +58651,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:73" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -59013,16 +58930,16 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="BS22" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="BT22" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="BS22" s="69" t="s">
-        <v>202</v>
-      </c>
-      <c r="BT22" s="69" t="s">
-        <v>203</v>
-      </c>
-      <c r="BU22" s="101" t="s">
-        <v>228</v>
+      <c r="BU22" s="97" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:73" ht="15.75" thickBot="1">
@@ -59052,7 +58969,7 @@
         <v>600</v>
       </c>
       <c r="I23" s="46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="46">
         <v>2</v>
@@ -59066,31 +58983,31 @@
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>11.88</v>
+        <v>11.76</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>582.12</v>
+        <v>576.24</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>17.46</v>
+        <v>17.29</v>
       </c>
       <c r="R23" s="72">
         <f>ROUND(M23+O23+Q23,3)</f>
-        <v>35.340000000000003</v>
+        <v>41.05</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>106</v>
@@ -59100,11 +59017,11 @@
       </c>
       <c r="V23" s="46">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>50.82</v>
+        <v>50.31</v>
       </c>
       <c r="W23" s="46">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>50.82</v>
+        <v>50.31</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -59123,11 +59040,11 @@
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>101.64</v>
+        <v>100.62</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>666.3</v>
+        <v>659.57</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -59147,7 +59064,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -59166,7 +59083,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -59181,7 +59098,7 @@
       </c>
       <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="AS23" t="s" s="0">
         <v>188</v>
@@ -59201,7 +59118,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -59209,7 +59126,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>282.33</v>
+        <v>279.47500000000002</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -59239,7 +59156,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>292.57458000000003</v>
+        <v>292.56623000000002</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -59253,13 +59170,13 @@
         <v>400</v>
       </c>
       <c r="BS23" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
       <c r="BU23" t="s" s="0">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:73" ht="15.75" thickBot="1">
@@ -59287,21 +59204,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>35.340000000000003</v>
+        <v>41.05</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>50.82</v>
+        <v>50.31</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>50.82</v>
+        <v>50.31</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -59312,11 +59229,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>101.64</v>
+        <v>100.62</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>666.3</v>
+        <v>659.57</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -59337,7 +59254,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>564.66</v>
+        <v>558.95000000000005</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -59416,7 +59333,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BU25"/>
+  <dimension ref="A1:CC25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="26.85546875"/>
@@ -59450,40 +59367,44 @@
     <col min="66" max="66" customWidth="true" width="37.0"/>
     <col min="67" max="67" customWidth="true" width="18.85546875"/>
     <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="74" max="74" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="75" max="75" bestFit="true" customWidth="true" width="9.140625"/>
+    <col min="78" max="78" bestFit="true" customWidth="true" width="17.5703125"/>
+    <col min="79" max="79" bestFit="true" customWidth="true" width="14.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="74"/>
       <c r="AE1" s="74"/>
       <c r="AF1" s="74"/>
@@ -60445,7 +60366,7 @@
       <c r="AR16" s="82"/>
       <c r="AS16" s="75"/>
     </row>
-    <row r="17" spans="1:73">
+    <row r="17" spans="1:81">
       <c r="A17" s="76">
         <v>14</v>
       </c>
@@ -60511,7 +60432,7 @@
       <c r="AR17" s="82"/>
       <c r="AS17" s="75"/>
     </row>
-    <row r="18" spans="1:73" ht="15.75" thickBot="1">
+    <row r="18" spans="1:81" ht="15.75" thickBot="1">
       <c r="A18" s="83">
         <v>15</v>
       </c>
@@ -60575,16 +60496,16 @@
       <c r="AR18" s="82"/>
       <c r="AS18" s="75"/>
     </row>
-    <row r="19" spans="1:73" ht="15.75" thickTop="1">
+    <row r="19" spans="1:81" ht="15.75" thickTop="1">
       <c r="A19" s="75"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -60627,7 +60548,7 @@
       <c r="AR19" s="29"/>
       <c r="AS19" s="75"/>
     </row>
-    <row r="20" spans="1:73">
+    <row r="20" spans="1:81">
       <c r="A20" s="29" t="s">
         <v>42</v>
       </c>
@@ -60676,11 +60597,11 @@
       <c r="AR20" s="29"/>
       <c r="AS20" s="75"/>
     </row>
-    <row r="21" spans="1:73" ht="15.75" thickBot="1">
-      <c r="A21" s="100" t="s">
+    <row r="21" spans="1:81" ht="15.75" thickBot="1">
+      <c r="A21" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="100"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="13">
         <v>2</v>
       </c>
@@ -60747,7 +60668,7 @@
       <c r="AR21" s="29"/>
       <c r="AS21" s="75"/>
     </row>
-    <row r="22" spans="1:73" ht="58.5" thickTop="1" thickBot="1">
+    <row r="22" spans="1:81" ht="58.5" thickTop="1" thickBot="1">
       <c r="A22" s="33" t="s">
         <v>2</v>
       </c>
@@ -60956,20 +60877,44 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="BS22" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="BT22" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="BS22" s="69" t="s">
-        <v>202</v>
-      </c>
-      <c r="BT22" s="69" t="s">
-        <v>203</v>
-      </c>
-      <c r="BU22" s="101" t="s">
+      <c r="BU22" s="97" t="s">
+        <v>222</v>
+      </c>
+      <c r="BV22" s="90" t="s">
+        <v>224</v>
+      </c>
+      <c r="BW22" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="BX22" s="90" t="s">
+        <v>226</v>
+      </c>
+      <c r="BY22" s="90" t="s">
+        <v>227</v>
+      </c>
+      <c r="BZ22" s="90" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="23" spans="1:73" ht="15.75" thickBot="1">
-      <c r="A23" s="2">
+      <c r="CA22" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="CB22" s="90" t="s">
+        <v>237</v>
+      </c>
+      <c r="CC22" s="90" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:81" ht="15.75" thickBot="1">
+      <c r="A23" s="45">
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -60978,7 +60923,7 @@
       <c r="C23" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="45" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -60992,7 +60937,7 @@
       </c>
       <c r="H23" s="65">
         <f>F23*G23</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>127</v>
@@ -61005,35 +60950,35 @@
       </c>
       <c r="L23" s="65">
         <f>H23</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="M23" s="65">
         <f>ROUND(L23*I23%,2)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N23" s="65">
         <f>H23-M23</f>
-        <v>980</v>
+        <v>1470</v>
       </c>
       <c r="O23" s="65">
         <f>ROUND(N23*J23%,2)</f>
-        <v>19.600000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="P23" s="65">
         <f>ROUND(N23-O23,2)</f>
-        <v>960.4</v>
+        <v>1440.6</v>
       </c>
       <c r="Q23" s="65">
         <f>ROUND(P23*K23%,2)</f>
-        <v>28.81</v>
+        <v>43.22</v>
       </c>
       <c r="R23" s="95">
         <f>ROUND(M23+O23+Q23,3)</f>
-        <v>68.41</v>
+        <v>102.62</v>
       </c>
       <c r="S23" s="95">
         <f>(H23-R23)</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="T23" s="65" t="s">
         <v>106</v>
@@ -61051,7 +60996,7 @@
       </c>
       <c r="X23" s="65">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
-        <v>167.69</v>
+        <v>251.53</v>
       </c>
       <c r="Y23" s="65">
         <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
@@ -61066,11 +61011,11 @@
       </c>
       <c r="AB23" s="65">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>167.69</v>
+        <v>251.53</v>
       </c>
       <c r="AC23" s="65">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>1099.28</v>
+        <v>1648.91</v>
       </c>
       <c r="AD23" s="65">
         <v>120</v>
@@ -61090,7 +61035,7 @@
       </c>
       <c r="AI23" s="65">
         <f>S23*$M$21</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="AJ23" s="65">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -61109,7 +61054,7 @@
       </c>
       <c r="AN23" s="65">
         <f>AI23/AM23</f>
-        <v>186.31800000000001</v>
+        <v>279.476</v>
       </c>
       <c r="AO23" s="65">
         <f>AJ23/AM23</f>
@@ -61123,8 +61068,8 @@
         <v>12</v>
       </c>
       <c r="AR23" s="0">
-        <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>186.31800000000001</v>
+        <f>AN23+AO23+AP23</f>
+        <v>279.476</v>
       </c>
       <c r="AS23" t="s" s="0">
         <v>188</v>
@@ -61136,23 +61081,23 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="AW23" s="66">
         <f>AM23</f>
         <v>5</v>
       </c>
       <c r="AX23" s="66">
-        <f>ROUND(AR23,2)</f>
-        <v>186.32</v>
+        <f>ROUND(AR23,3)</f>
+        <v>279.476</v>
       </c>
       <c r="AY23" s="66">
         <f>AU23+AW23</f>
         <v>5</v>
       </c>
-      <c r="AZ23" s="66">
+      <c r="AZ23" s="78">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>186.32</v>
+        <v>279.476</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -61175,14 +61120,14 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>186.50245000000001</v>
+        <v>186.5607</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -61193,19 +61138,45 @@
       </c>
       <c r="BR23" s="4">
         <f>G23+100</f>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="BS23" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
       <c r="BU23" t="s" s="0">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="24" spans="1:73" ht="15.75" thickBot="1">
+        <v>223</v>
+      </c>
+      <c r="BV23" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="BW23" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="BX23" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="BY23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="BZ23" s="99">
+        <f>S23+CB23+CC23</f>
+        <v>2297.38</v>
+      </c>
+      <c r="CA23" s="99">
+        <f>BZ23-BW23</f>
+        <v>1365.79</v>
+      </c>
+      <c r="CB23" s="98">
+        <v>300</v>
+      </c>
+      <c r="CC23" s="98">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:81" ht="15.75" thickBot="1">
       <c r="A24" s="75"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -61217,7 +61188,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -61230,11 +61201,11 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>68.41</v>
+        <v>102.62</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
@@ -61248,18 +61219,18 @@
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
-        <v>167.69</v>
+        <v>251.53</v>
       </c>
       <c r="Y24" s="55"/>
       <c r="Z24" s="55"/>
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>167.69</v>
+        <v>251.53</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>1099.28</v>
+        <v>1648.91</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -61280,7 +61251,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -61299,7 +61270,7 @@
       <c r="AR24" s="56"/>
       <c r="AS24" s="75"/>
     </row>
-    <row r="25" spans="1:73">
+    <row r="25" spans="1:81">
       <c r="A25" s="75"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -61359,7 +61330,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BR25"/>
+  <dimension ref="A1:CC25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="26.85546875"/>
@@ -61393,40 +61364,43 @@
     <col min="66" max="66" customWidth="true" width="37.0"/>
     <col min="67" max="67" customWidth="true" width="18.85546875"/>
     <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="78" max="78" bestFit="true" customWidth="true" width="17.5703125"/>
+    <col min="79" max="79" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="81" max="81" bestFit="true" customWidth="true" width="17.28515625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="71"/>
       <c r="AE1" s="71"/>
       <c r="AF1" s="71"/>
@@ -62388,7 +62362,7 @@
       <c r="AR16" s="20"/>
       <c r="AS16" s="8"/>
     </row>
-    <row r="17" spans="1:70">
+    <row r="17" spans="1:81">
       <c r="A17" s="14">
         <v>14</v>
       </c>
@@ -62454,7 +62428,7 @@
       <c r="AR17" s="20"/>
       <c r="AS17" s="8"/>
     </row>
-    <row r="18" spans="1:70" ht="15.75" thickBot="1">
+    <row r="18" spans="1:81" ht="15.75" thickBot="1">
       <c r="A18" s="22">
         <v>15</v>
       </c>
@@ -62518,16 +62492,16 @@
       <c r="AR18" s="20"/>
       <c r="AS18" s="8"/>
     </row>
-    <row r="19" spans="1:70" ht="15.75" thickTop="1">
+    <row r="19" spans="1:81" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -62570,7 +62544,7 @@
       <c r="AR19" s="29"/>
       <c r="AS19" s="8"/>
     </row>
-    <row r="20" spans="1:70">
+    <row r="20" spans="1:81">
       <c r="A20" s="29" t="s">
         <v>42</v>
       </c>
@@ -62619,11 +62593,11 @@
       <c r="AR20" s="29"/>
       <c r="AS20" s="8"/>
     </row>
-    <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+    <row r="21" spans="1:81" ht="15.75" thickBot="1">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -62690,7 +62664,7 @@
       <c r="AR21" s="29"/>
       <c r="AS21" s="8"/>
     </row>
-    <row r="22" spans="1:70" ht="58.5" thickTop="1" thickBot="1">
+    <row r="22" spans="1:81" ht="58.5" thickTop="1" thickBot="1">
       <c r="A22" s="33" t="s">
         <v>2</v>
       </c>
@@ -62899,10 +62873,43 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
+        <v>199</v>
+      </c>
+      <c r="BS22" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="BT22" s="69" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="23" spans="1:70" ht="15.75" thickBot="1">
+      <c r="BU22" s="97" t="s">
+        <v>222</v>
+      </c>
+      <c r="BV22" s="90" t="s">
+        <v>224</v>
+      </c>
+      <c r="BW22" s="90" t="s">
+        <v>225</v>
+      </c>
+      <c r="BX22" s="90" t="s">
+        <v>226</v>
+      </c>
+      <c r="BY22" s="90" t="s">
+        <v>227</v>
+      </c>
+      <c r="BZ22" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="CA22" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="CB22" s="90" t="s">
+        <v>237</v>
+      </c>
+      <c r="CC22" s="90" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:81" ht="15.75" thickBot="1">
       <c r="A23" s="45">
         <v>1</v>
       </c>
@@ -62922,11 +62929,11 @@
         <v>5</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>127</v>
@@ -62939,35 +62946,35 @@
       </c>
       <c r="L23" s="46">
         <f>H23</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>980</v>
+        <v>1470</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>19.600000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>960.4</v>
+        <v>1440.6</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>28.81</v>
+        <v>43.22</v>
       </c>
       <c r="R23" s="72">
         <f>ROUND(M23+O23+Q23,3)</f>
-        <v>68.41</v>
+        <v>102.62</v>
       </c>
       <c r="S23" s="72">
         <f>(H23-R23)</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="T23" s="65" t="s">
         <v>106</v>
@@ -62977,11 +62984,11 @@
       </c>
       <c r="V23" s="72">
         <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>83.84</v>
+        <v>125.76</v>
       </c>
       <c r="W23" s="72">
         <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>83.84</v>
+        <v>125.76</v>
       </c>
       <c r="X23" s="46">
         <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
@@ -63000,11 +63007,11 @@
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>167.68</v>
+        <v>251.52</v>
       </c>
       <c r="AC23" s="46">
         <f>IF($V21=1,S23+AB23,S23)</f>
-        <v>1099.27</v>
+        <v>1648.9</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
@@ -63024,7 +63031,7 @@
       </c>
       <c r="AI23" s="46">
         <f>S23*$M$21</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="AJ23" s="46">
         <f>IF($C$21=3,0,AG23+AH23)</f>
@@ -63043,7 +63050,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>186.31800000000001</v>
+        <v>279.476</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -63058,7 +63065,7 @@
       </c>
       <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>186.31800000000001</v>
+        <v>279.476</v>
       </c>
       <c r="AS23" t="s" s="0">
         <v>188</v>
@@ -63070,7 +63077,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -63078,7 +63085,7 @@
       </c>
       <c r="AX23" s="48">
         <f>ROUND(AR23,2)</f>
-        <v>186.32</v>
+        <v>279.48</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -63086,7 +63093,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>186.32</v>
+        <v>279.48</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -63109,18 +63116,18 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>187.06620000000001</v>
+        <v>186.56370999999999</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
-        <v>452</v>
+        <v>7174</v>
       </c>
       <c r="BQ23" s="50">
         <v>88363222</v>
@@ -63129,8 +63136,45 @@
         <f>G23+100</f>
         <v>400</v>
       </c>
-    </row>
-    <row r="24" spans="1:70" ht="15.75" thickBot="1">
+      <c r="BS23" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="BT23" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU23" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="BV23" s="75" t="s">
+        <v>230</v>
+      </c>
+      <c r="BW23" s="75" t="s">
+        <v>230</v>
+      </c>
+      <c r="BX23" s="75">
+        <v>5</v>
+      </c>
+      <c r="BY23" s="75">
+        <v>200</v>
+      </c>
+      <c r="BZ23" s="100">
+        <f>AC23+CB23+CC23</f>
+        <v>2710.9</v>
+      </c>
+      <c r="CA23" s="98">
+        <f>BZ23-BW23</f>
+        <v>2335.9</v>
+      </c>
+      <c r="CB23" s="98">
+        <f>300+CB24</f>
+        <v>354</v>
+      </c>
+      <c r="CC23" s="98">
+        <f>600+CC24</f>
+        <v>708</v>
+      </c>
+    </row>
+    <row r="24" spans="1:81" ht="15.75" thickBot="1">
       <c r="A24" s="8"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -63142,7 +63186,7 @@
       <c r="G24" s="52"/>
       <c r="H24" s="53">
         <f>SUM(H23:H23)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I24" s="45"/>
       <c r="J24" s="45"/>
@@ -63155,21 +63199,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>68.41</v>
+        <v>102.62</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f>SUM(V23:V23)</f>
-        <v>83.84</v>
+        <v>125.76</v>
       </c>
       <c r="W24" s="55">
         <f>SUM(W23:W23)</f>
-        <v>83.84</v>
+        <v>125.76</v>
       </c>
       <c r="X24" s="55">
         <f>SUM(X23:X23)</f>
@@ -63180,11 +63224,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f>SUM(AB23:AB23)</f>
-        <v>167.68</v>
+        <v>251.52</v>
       </c>
       <c r="AC24" s="56">
         <f>SUM(AC23:AC23)</f>
-        <v>1099.27</v>
+        <v>1648.9</v>
       </c>
       <c r="AD24" s="57">
         <f>SUM(AD23:AD23)</f>
@@ -63205,7 +63249,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>931.59</v>
+        <v>1397.38</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -63223,8 +63267,16 @@
       <c r="AQ24" s="56"/>
       <c r="AR24" s="56"/>
       <c r="AS24" s="8"/>
-    </row>
-    <row r="25" spans="1:70">
+      <c r="CB24" s="0">
+        <f>300*U23</f>
+        <v>54</v>
+      </c>
+      <c r="CC24" s="0">
+        <f>600*U23</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:81">
       <c r="A25" s="8"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -63318,37 +63370,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
@@ -64442,14 +64494,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -64542,10 +64594,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -64821,7 +64873,7 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:70" ht="15.75" thickBot="1">
@@ -65031,10 +65083,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -65238,37 +65290,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
@@ -66362,14 +66414,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -66462,10 +66514,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>
@@ -67154,37 +67206,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
-      <c r="A1" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
@@ -68278,14 +68330,14 @@
     </row>
     <row r="19" spans="1:70" ht="15.75" thickTop="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="27">
         <f>SUM(H4:H18)</f>
         <v>71856.759999999995</v>
@@ -68378,10 +68430,10 @@
       <c r="AS20" s="8"/>
     </row>
     <row r="21" spans="1:70" ht="15.75" thickBot="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="99"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="13">
         <v>1</v>
       </c>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="29" activeTab="29"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5903" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6094" uniqueCount="324">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -680,19 +680,10 @@
     <t>712</t>
   </si>
   <si>
-    <t>266.61192</t>
-  </si>
-  <si>
     <t>386</t>
   </si>
   <si>
     <t>ROAU-RM-KDK-02</t>
-  </si>
-  <si>
-    <t>261.53222</t>
-  </si>
-  <si>
-    <t>144</t>
   </si>
   <si>
     <t>RM WH 50</t>
@@ -711,12 +702,6 @@
   </si>
   <si>
     <t>294</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>879.88404</t>
   </si>
   <si>
     <t>1106</t>
@@ -785,16 +770,268 @@
     <t>186.49443</t>
   </si>
   <si>
-    <t>7209</t>
-  </si>
-  <si>
-    <t>186.49927</t>
-  </si>
-  <si>
     <t>7214</t>
   </si>
   <si>
     <t>186.49914</t>
+  </si>
+  <si>
+    <t>23998.05</t>
+  </si>
+  <si>
+    <t>4124</t>
+  </si>
+  <si>
+    <t>1378.33564</t>
+  </si>
+  <si>
+    <t>1354</t>
+  </si>
+  <si>
+    <t>3422.47109</t>
+  </si>
+  <si>
+    <t>2399.55</t>
+  </si>
+  <si>
+    <t>4126</t>
+  </si>
+  <si>
+    <t>1378.83065</t>
+  </si>
+  <si>
+    <t>4128</t>
+  </si>
+  <si>
+    <t>1379.32518</t>
+  </si>
+  <si>
+    <t>4130</t>
+  </si>
+  <si>
+    <t>1379.81924</t>
+  </si>
+  <si>
+    <t>4132</t>
+  </si>
+  <si>
+    <t>1380.31282</t>
+  </si>
+  <si>
+    <t>4134</t>
+  </si>
+  <si>
+    <t>1380.80592</t>
+  </si>
+  <si>
+    <t>4136</t>
+  </si>
+  <si>
+    <t>1381.29854</t>
+  </si>
+  <si>
+    <t>4138</t>
+  </si>
+  <si>
+    <t>1381.79069</t>
+  </si>
+  <si>
+    <t>4142</t>
+  </si>
+  <si>
+    <t>1380.72892</t>
+  </si>
+  <si>
+    <t>4144</t>
+  </si>
+  <si>
+    <t>1381.22063</t>
+  </si>
+  <si>
+    <t>4146</t>
+  </si>
+  <si>
+    <t>1381.71186</t>
+  </si>
+  <si>
+    <t>4148</t>
+  </si>
+  <si>
+    <t>1382.20262</t>
+  </si>
+  <si>
+    <t>4150</t>
+  </si>
+  <si>
+    <t>1382.69291</t>
+  </si>
+  <si>
+    <t>4152</t>
+  </si>
+  <si>
+    <t>1383.18273</t>
+  </si>
+  <si>
+    <t>4156</t>
+  </si>
+  <si>
+    <t>1383.09587</t>
+  </si>
+  <si>
+    <t>4160</t>
+  </si>
+  <si>
+    <t>1383.00918</t>
+  </si>
+  <si>
+    <t>4166</t>
+  </si>
+  <si>
+    <t>1382.3482</t>
+  </si>
+  <si>
+    <t>4168</t>
+  </si>
+  <si>
+    <t>1382.8363</t>
+  </si>
+  <si>
+    <t>4170</t>
+  </si>
+  <si>
+    <t>1383.32393</t>
+  </si>
+  <si>
+    <t>4172</t>
+  </si>
+  <si>
+    <t>1383.81109</t>
+  </si>
+  <si>
+    <t>4174</t>
+  </si>
+  <si>
+    <t>1384.29779</t>
+  </si>
+  <si>
+    <t>4176</t>
+  </si>
+  <si>
+    <t>1384.78402</t>
+  </si>
+  <si>
+    <t>4178</t>
+  </si>
+  <si>
+    <t>1385.26979</t>
+  </si>
+  <si>
+    <t>4180</t>
+  </si>
+  <si>
+    <t>1385.75509</t>
+  </si>
+  <si>
+    <t>4182</t>
+  </si>
+  <si>
+    <t>1386.23993</t>
+  </si>
+  <si>
+    <t>4184</t>
+  </si>
+  <si>
+    <t>1386.7243</t>
+  </si>
+  <si>
+    <t>4186</t>
+  </si>
+  <si>
+    <t>1387.20821</t>
+  </si>
+  <si>
+    <t>4188</t>
+  </si>
+  <si>
+    <t>1387.69166</t>
+  </si>
+  <si>
+    <t>4190</t>
+  </si>
+  <si>
+    <t>1388.17465</t>
+  </si>
+  <si>
+    <t>4192</t>
+  </si>
+  <si>
+    <t>1387.64705</t>
+  </si>
+  <si>
+    <t>4194</t>
+  </si>
+  <si>
+    <t>1388.1296</t>
+  </si>
+  <si>
+    <t>4196</t>
+  </si>
+  <si>
+    <t>1388.61169</t>
+  </si>
+  <si>
+    <t>4198</t>
+  </si>
+  <si>
+    <t>1389.09332</t>
+  </si>
+  <si>
+    <t>4200</t>
+  </si>
+  <si>
+    <t>1389.57449</t>
+  </si>
+  <si>
+    <t>4202</t>
+  </si>
+  <si>
+    <t>1390.0552</t>
+  </si>
+  <si>
+    <t>4204</t>
+  </si>
+  <si>
+    <t>1390.53545</t>
+  </si>
+  <si>
+    <t>4206</t>
+  </si>
+  <si>
+    <t>1391.01525</t>
+  </si>
+  <si>
+    <t>4208</t>
+  </si>
+  <si>
+    <t>1391.49459</t>
+  </si>
+  <si>
+    <t>4210</t>
+  </si>
+  <si>
+    <t>1390.96767</t>
+  </si>
+  <si>
+    <t>4212</t>
+  </si>
+  <si>
+    <t>1390.44125</t>
+  </si>
+  <si>
+    <t>4216</t>
+  </si>
+  <si>
+    <t>1391.39866</t>
   </si>
 </sst>
 </file>
@@ -37349,7 +37586,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -37388,10 +37625,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -46745,7 +46982,7 @@
         <v>201</v>
       </c>
       <c r="BU22" s="97" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:73" ht="15.75" thickBot="1">
@@ -46982,7 +47219,7 @@
         <v>3</v>
       </c>
       <c r="BU23" t="s" s="0">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:73" ht="15.75" thickBot="1">
@@ -48844,7 +49081,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="AW23" s="66">
         <f>AM23</f>
@@ -48883,10 +49120,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>204</v>
+        <v>323</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>205</v>
+        <v>322</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -50759,7 +50996,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="AW23" s="66">
         <f>AM23</f>
@@ -50798,10 +51035,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>206</v>
+        <v>283</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>207</v>
+        <v>282</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -50821,10 +51058,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>12</v>
@@ -50984,7 +51221,7 @@
         <v>108</v>
       </c>
       <c r="AV24" t="s" s="0">
-        <v>149</v>
+        <v>238</v>
       </c>
       <c r="AW24" s="66">
         <f>AM24</f>
@@ -51023,10 +51260,10 @@
         <v>148</v>
       </c>
       <c r="BM24" t="s" s="0">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="BN24" t="s" s="0">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="BO24" s="66">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -52936,10 +53173,10 @@
       <c r="BH23" s="3"/>
       <c r="BI23" s="66"/>
       <c r="BL23" s="66" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="BN23" t="s" s="0">
         <v>173</v>
@@ -54852,13 +55089,13 @@
       <c r="BH23" s="3"/>
       <c r="BI23" s="66"/>
       <c r="BL23" s="66" t="s">
+        <v>208</v>
+      </c>
+      <c r="BM23" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="BN23" t="s" s="0">
         <v>211</v>
-      </c>
-      <c r="BM23" t="s" s="0">
-        <v>213</v>
-      </c>
-      <c r="BN23" t="s" s="0">
-        <v>214</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -54878,10 +55115,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>12</v>
@@ -55077,13 +55314,13 @@
       <c r="BH24" s="3"/>
       <c r="BI24" s="66"/>
       <c r="BL24" s="66" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="BM24" t="s" s="0">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="BN24" t="s" s="0">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="BO24" s="66">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -56995,10 +57232,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -57018,10 +57255,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>12</v>
@@ -57220,10 +57457,10 @@
         <v>148</v>
       </c>
       <c r="BM24" t="s" s="0">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="BN24" t="s" s="0">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BO24" s="66">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -58939,7 +59176,7 @@
         <v>201</v>
       </c>
       <c r="BU22" s="97" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:73" ht="15.75" thickBot="1">
@@ -59176,7 +59413,7 @@
         <v>3</v>
       </c>
       <c r="BU23" t="s" s="0">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:73" ht="15.75" thickBot="1">
@@ -60886,31 +61123,31 @@
         <v>201</v>
       </c>
       <c r="BU22" s="97" t="s">
+        <v>217</v>
+      </c>
+      <c r="BV22" s="90" t="s">
+        <v>219</v>
+      </c>
+      <c r="BW22" s="90" t="s">
+        <v>220</v>
+      </c>
+      <c r="BX22" s="90" t="s">
+        <v>221</v>
+      </c>
+      <c r="BY22" s="90" t="s">
         <v>222</v>
       </c>
-      <c r="BV22" s="90" t="s">
+      <c r="BZ22" s="90" t="s">
+        <v>223</v>
+      </c>
+      <c r="CA22" s="90" t="s">
         <v>224</v>
       </c>
-      <c r="BW22" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="BX22" s="90" t="s">
-        <v>226</v>
-      </c>
-      <c r="BY22" s="90" t="s">
-        <v>227</v>
-      </c>
-      <c r="BZ22" s="90" t="s">
-        <v>228</v>
-      </c>
-      <c r="CA22" s="90" t="s">
-        <v>229</v>
-      </c>
       <c r="CB22" s="90" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="CC22" s="90" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:81" ht="15.75" thickBot="1">
@@ -61081,7 +61318,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AW23" s="66">
         <f>AM23</f>
@@ -61120,10 +61357,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -61147,16 +61384,16 @@
         <v>3</v>
       </c>
       <c r="BU23" t="s" s="0">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="BV23" t="s" s="0">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="BW23" t="s" s="0">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="BX23" t="s" s="0">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="BY23" t="s" s="0">
         <v>109</v>
@@ -62882,31 +63119,31 @@
         <v>201</v>
       </c>
       <c r="BU22" s="97" t="s">
+        <v>217</v>
+      </c>
+      <c r="BV22" s="90" t="s">
+        <v>219</v>
+      </c>
+      <c r="BW22" s="90" t="s">
+        <v>220</v>
+      </c>
+      <c r="BX22" s="90" t="s">
+        <v>221</v>
+      </c>
+      <c r="BY22" s="90" t="s">
         <v>222</v>
       </c>
-      <c r="BV22" s="90" t="s">
+      <c r="BZ22" s="90" t="s">
+        <v>223</v>
+      </c>
+      <c r="CA22" s="90" t="s">
         <v>224</v>
       </c>
-      <c r="BW22" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="BX22" s="90" t="s">
-        <v>226</v>
-      </c>
-      <c r="BY22" s="90" t="s">
-        <v>227</v>
-      </c>
-      <c r="BZ22" s="90" t="s">
-        <v>228</v>
-      </c>
-      <c r="CA22" s="90" t="s">
-        <v>229</v>
-      </c>
       <c r="CB22" s="90" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="CC22" s="90" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:81" ht="15.75" thickBot="1">
@@ -63077,7 +63314,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -63116,10 +63353,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -63143,13 +63380,13 @@
         <v>3</v>
       </c>
       <c r="BU23" t="s" s="0">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="BV23" s="75" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="BW23" s="75" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="BX23" s="75">
         <v>5</v>
@@ -65083,10 +65320,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>218</v>
+        <v>319</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>217</v>
+        <v>318</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915"/>
   </bookViews>
   <sheets>
     <sheet name="DirectGrnGenUD" sheetId="38" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5922" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="245">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -737,12 +737,6 @@
     <t>186.49914</t>
   </si>
   <si>
-    <t>4270</t>
-  </si>
-  <si>
-    <t>1382.06151</t>
-  </si>
-  <si>
     <t>386</t>
   </si>
   <si>
@@ -794,34 +788,16 @@
     <t>2399.55</t>
   </si>
   <si>
-    <t>4224</t>
-  </si>
-  <si>
-    <t>1393.30804</t>
-  </si>
-  <si>
-    <t>4272</t>
-  </si>
-  <si>
-    <t>1382.53786</t>
-  </si>
-  <si>
-    <t>4274</t>
-  </si>
-  <si>
-    <t>1383.01377</t>
-  </si>
-  <si>
     <t>4276</t>
   </si>
   <si>
     <t>1383.48923</t>
   </si>
   <si>
-    <t>4278</t>
+    <t>4282</t>
   </si>
   <si>
-    <t>1383.96425</t>
+    <t>1382.93517</t>
   </si>
 </sst>
 </file>
@@ -1862,44 +1838,44 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="99" width="9.0"/>
-    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
-    <col min="9" max="10" style="99" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
-    <col min="12" max="28" style="99" width="9.0"/>
-    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
-    <col min="32" max="34" style="99" width="9.0"/>
-    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
-    <col min="36" max="42" style="99" width="9.0"/>
-    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
-    <col min="45" max="45" style="99" width="9.0"/>
-    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
-    <col min="50" max="50" style="99" width="9.0"/>
-    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
-    <col min="54" max="59" style="99" width="9.0"/>
-    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
-    <col min="64" max="64" style="99" width="9.0"/>
-    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
-    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
-    <col min="69" max="16384" style="99" width="9.0"/>
+    <col min="1" max="1" width="9" style="99"/>
+    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
+    <col min="9" max="10" width="9" style="99"/>
+    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
+    <col min="12" max="28" width="9" style="99"/>
+    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
+    <col min="32" max="34" width="9" style="99"/>
+    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
+    <col min="36" max="42" width="9" style="99"/>
+    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
+    <col min="45" max="45" width="9" style="99"/>
+    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
+    <col min="50" max="50" width="9" style="99"/>
+    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
+    <col min="54" max="59" width="9" style="99"/>
+    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
+    <col min="64" max="64" width="9" style="99"/>
+    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
+    <col min="66" max="66" width="37" style="99" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
+    <col min="69" max="16384" width="9" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -3573,11 +3549,11 @@
       <c r="AT23" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="99">
+      <c r="AU23" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="99">
-        <v>242</v>
+      <c r="AV23" s="99" t="s">
+        <v>149</v>
       </c>
       <c r="AW23" s="112">
         <f>AM23</f>
@@ -3615,11 +3591,11 @@
       <c r="BL23" s="112" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="99">
-        <v>252</v>
-      </c>
-      <c r="BN23" t="s" s="99">
-        <v>251</v>
+      <c r="BM23" s="99" t="s">
+        <v>244</v>
+      </c>
+      <c r="BN23" s="99" t="s">
+        <v>243</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -3794,36 +3770,36 @@
   <dimension ref="A1:BU25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="18" max="18" customWidth="true" width="14.85546875"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
-    <col min="71" max="71" customWidth="true" width="22.140625"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="71" max="71" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -5496,20 +5472,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -5548,10 +5524,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" s="0">
+      <c r="BM23">
         <v>292.60462000000001</v>
       </c>
-      <c r="BN23" s="0">
+      <c r="BN23">
         <v>682</v>
       </c>
       <c r="BO23" s="48">
@@ -5575,7 +5551,7 @@
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s" s="0">
+      <c r="BU23" t="s">
         <v>204</v>
       </c>
     </row>
@@ -5736,41 +5712,41 @@
   <dimension ref="A1:CC25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="18" max="18" customWidth="true" width="11.28515625"/>
-    <col min="19" max="19" customWidth="true" width="11.140625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="23.85546875"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="50" max="50" customWidth="true" width="11.0"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
-    <col min="74" max="74" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="75" max="75" bestFit="true" customWidth="true" width="9.140625"/>
-    <col min="78" max="78" bestFit="true" customWidth="true" width="17.5703125"/>
-    <col min="79" max="79" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="18" max="18" width="11.28515625" customWidth="1"/>
+    <col min="19" max="19" width="11.140625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="23.85546875" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="50" max="50" width="11" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="74" max="74" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -7332,14 +7308,14 @@
       <c r="F23" s="65">
         <v>5</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>128</v>
       </c>
       <c r="H23" s="65">
         <f>F23*G23</f>
         <v>1500</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="65">
@@ -7467,20 +7443,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>AN23+AO23+AP23</f>
         <v>279.476</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>215</v>
       </c>
       <c r="AW23" s="66">
@@ -7519,10 +7495,10 @@
       <c r="BL23" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>221</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>220</v>
       </c>
       <c r="BO23" s="66">
@@ -7546,19 +7522,19 @@
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s" s="0">
+      <c r="BU23" t="s">
         <v>204</v>
       </c>
-      <c r="BV23" t="s" s="0">
+      <c r="BV23" t="s">
         <v>216</v>
       </c>
-      <c r="BW23" t="s" s="0">
+      <c r="BW23" t="s">
         <v>216</v>
       </c>
-      <c r="BX23" t="s" s="0">
+      <c r="BX23" t="s">
         <v>217</v>
       </c>
-      <c r="BY23" t="s" s="0">
+      <c r="BY23" t="s">
         <v>109</v>
       </c>
       <c r="BZ23" s="97">
@@ -7733,40 +7709,40 @@
   <dimension ref="A1:CC25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="18" max="18" customWidth="true" width="11.28515625"/>
-    <col min="19" max="19" customWidth="true" width="11.140625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="23.85546875"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="50" max="50" customWidth="true" width="11.0"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
-    <col min="78" max="78" bestFit="true" customWidth="true" width="17.5703125"/>
-    <col min="79" max="79" bestFit="true" customWidth="true" width="14.0"/>
-    <col min="81" max="81" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="18" max="18" width="11.28515625" customWidth="1"/>
+    <col min="19" max="19" width="11.140625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="23.85546875" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="50" max="50" width="11" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="78" max="78" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="14" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -9328,14 +9304,14 @@
       <c r="F23" s="46">
         <v>5</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>128</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>1500</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -9463,20 +9439,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>279.476</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>215</v>
       </c>
       <c r="AW23" s="48">
@@ -9515,10 +9491,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>223</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>222</v>
       </c>
       <c r="BO23" s="48">
@@ -9542,7 +9518,7 @@
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s" s="0">
+      <c r="BU23" t="s">
         <v>204</v>
       </c>
       <c r="BV23" s="74" t="s">
@@ -9667,11 +9643,11 @@
       <c r="AQ24" s="56"/>
       <c r="AR24" s="56"/>
       <c r="AS24" s="8"/>
-      <c r="CB24" s="0">
+      <c r="CB24">
         <f>300*U23</f>
         <v>54</v>
       </c>
-      <c r="CC24" s="0">
+      <c r="CC24">
         <f>600*U23</f>
         <v>108</v>
       </c>
@@ -9739,32 +9715,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -11425,20 +11401,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -11477,10 +11453,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>149</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>164</v>
       </c>
       <c r="BO23" s="48">
@@ -11655,32 +11631,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -13341,11 +13317,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -13556,34 +13532,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -15109,14 +15085,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -15244,20 +15220,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>189</v>
       </c>
       <c r="AW23" s="48">
@@ -15296,10 +15272,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -15472,32 +15448,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -17023,14 +16999,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -17158,11 +17134,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -17373,34 +17349,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -18926,14 +18902,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -19061,20 +19037,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>158</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>177</v>
       </c>
       <c r="AW23" s="48">
@@ -19113,10 +19089,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>178</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>131</v>
       </c>
       <c r="BO23" s="48">
@@ -19292,32 +19268,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -20843,14 +20819,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -20978,11 +20954,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -21194,34 +21170,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -22747,14 +22723,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -22882,20 +22858,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>132</v>
       </c>
       <c r="AW23" s="48">
@@ -22934,10 +22910,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -23112,44 +23088,44 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="99" width="9.0"/>
-    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
-    <col min="9" max="10" style="99" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
-    <col min="12" max="28" style="99" width="9.0"/>
-    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
-    <col min="32" max="34" style="99" width="9.0"/>
-    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
-    <col min="36" max="42" style="99" width="9.0"/>
-    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
-    <col min="45" max="45" style="99" width="9.0"/>
-    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
-    <col min="50" max="50" style="99" width="9.0"/>
-    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
-    <col min="54" max="59" style="99" width="9.0"/>
-    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
-    <col min="64" max="64" style="99" width="9.0"/>
-    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
-    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
-    <col min="69" max="16384" style="99" width="9.0"/>
+    <col min="1" max="1" width="9" style="99"/>
+    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
+    <col min="9" max="10" width="9" style="99"/>
+    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
+    <col min="12" max="28" width="9" style="99"/>
+    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
+    <col min="32" max="34" width="9" style="99"/>
+    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
+    <col min="36" max="42" width="9" style="99"/>
+    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
+    <col min="45" max="45" width="9" style="99"/>
+    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
+    <col min="50" max="50" width="9" style="99"/>
+    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
+    <col min="54" max="59" width="9" style="99"/>
+    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
+    <col min="64" max="64" width="9" style="99"/>
+    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
+    <col min="66" max="66" width="37" style="99" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
+    <col min="69" max="16384" width="9" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -24863,10 +24839,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -24886,10 +24862,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -25088,10 +25064,10 @@
         <v>148</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -25262,34 +25238,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -26815,14 +26791,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -26950,20 +26926,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -27002,10 +26978,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -27180,32 +27156,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -28731,14 +28707,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -28866,11 +28842,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -29081,34 +29057,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -30634,14 +30610,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -30769,20 +30745,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>164</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -30821,10 +30797,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>163</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -30999,32 +30975,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -32550,14 +32526,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -32685,11 +32661,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -32900,34 +32876,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -34453,14 +34429,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -34588,20 +34564,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>189</v>
       </c>
       <c r="AW23" s="48">
@@ -34640,10 +34616,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>195</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>194</v>
       </c>
       <c r="BO23" s="48">
@@ -34818,32 +34794,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -36369,14 +36345,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -36504,11 +36480,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -36719,34 +36695,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -38407,20 +38383,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -38459,10 +38435,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>175</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>176</v>
       </c>
       <c r="BO23" s="48">
@@ -38634,34 +38610,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -40322,20 +40298,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -40374,10 +40350,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>175</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>196</v>
       </c>
       <c r="BO23" s="48">
@@ -40549,32 +40525,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -42100,14 +42076,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -42235,11 +42211,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -42450,34 +42426,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -44003,14 +43979,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -44138,20 +44114,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>570.48</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>191</v>
       </c>
       <c r="AW23" s="16">
@@ -44190,10 +44166,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>198</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>197</v>
       </c>
       <c r="BO23" s="48">
@@ -44365,44 +44341,44 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="99" width="9.0"/>
-    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
-    <col min="9" max="10" style="99" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
-    <col min="12" max="28" style="99" width="9.0"/>
-    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
-    <col min="32" max="34" style="99" width="9.0"/>
-    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
-    <col min="36" max="42" style="99" width="9.0"/>
-    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
-    <col min="45" max="45" style="99" width="9.0"/>
-    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
-    <col min="50" max="50" style="99" width="9.0"/>
-    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
-    <col min="54" max="59" style="99" width="9.0"/>
-    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="99" width="10.5703125"/>
-    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
-    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
-    <col min="69" max="16384" style="99" width="9.0"/>
+    <col min="1" max="1" width="9" style="99"/>
+    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
+    <col min="9" max="10" width="9" style="99"/>
+    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
+    <col min="12" max="28" width="9" style="99"/>
+    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
+    <col min="32" max="34" width="9" style="99"/>
+    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
+    <col min="36" max="42" width="9" style="99"/>
+    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
+    <col min="45" max="45" width="9" style="99"/>
+    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
+    <col min="50" max="50" width="9" style="99"/>
+    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
+    <col min="54" max="59" width="9" style="99"/>
+    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="99" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
+    <col min="66" max="66" width="37" style="99" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
+    <col min="69" max="16384" width="9" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -46113,13 +46089,13 @@
       <c r="BH23" s="113"/>
       <c r="BI23" s="112"/>
       <c r="BL23" s="112" t="s">
+        <v>231</v>
+      </c>
+      <c r="BM23" s="99" t="s">
         <v>233</v>
       </c>
-      <c r="BM23" s="99" t="s">
-        <v>235</v>
-      </c>
       <c r="BN23" s="99" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -46139,10 +46115,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -46338,13 +46314,13 @@
       <c r="BH24" s="113"/>
       <c r="BI24" s="112"/>
       <c r="BL24" s="112" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -46515,34 +46491,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -48068,14 +48044,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -48203,20 +48179,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>AN23+AO23+AP23</f>
         <v>558.95000000000005</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>212</v>
       </c>
       <c r="AW23" s="48">
@@ -48255,10 +48231,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>214</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>213</v>
       </c>
       <c r="BO23" s="48">
@@ -48430,32 +48406,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -49981,14 +49957,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -50116,11 +50092,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>188.22</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -50331,34 +50307,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -51884,14 +51860,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -52019,20 +51995,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>191</v>
       </c>
       <c r="AW23" s="16">
@@ -52071,10 +52047,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>191</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>193</v>
       </c>
       <c r="BO23" s="48">
@@ -52249,34 +52225,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -53802,14 +53778,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -53937,20 +53913,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>191</v>
       </c>
       <c r="AW23" s="16">
@@ -53989,10 +53965,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>191</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>192</v>
       </c>
       <c r="BO23" s="48">
@@ -54167,32 +54143,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -55718,14 +55694,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s" s="0">
+      <c r="G23" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s" s="0">
+      <c r="I23" t="s">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -55853,11 +55829,11 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>18.824999999999999</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
@@ -56068,44 +56044,44 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="99" width="9.0"/>
-    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
-    <col min="9" max="10" style="99" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
-    <col min="12" max="28" style="99" width="9.0"/>
-    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
-    <col min="32" max="34" style="99" width="9.0"/>
-    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
-    <col min="36" max="42" style="99" width="9.0"/>
-    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
-    <col min="45" max="45" style="99" width="9.0"/>
-    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
-    <col min="50" max="50" style="99" width="9.0"/>
-    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
-    <col min="54" max="59" style="99" width="9.0"/>
-    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="99" width="10.5703125"/>
-    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
-    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
-    <col min="69" max="16384" style="99" width="9.0"/>
+    <col min="1" max="1" width="9" style="99"/>
+    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
+    <col min="9" max="10" width="9" style="99"/>
+    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
+    <col min="12" max="28" width="9" style="99"/>
+    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
+    <col min="32" max="34" width="9" style="99"/>
+    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
+    <col min="36" max="42" width="9" style="99"/>
+    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
+    <col min="45" max="45" width="9" style="99"/>
+    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
+    <col min="50" max="50" width="9" style="99"/>
+    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
+    <col min="54" max="59" width="9" style="99"/>
+    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="99" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
+    <col min="66" max="66" width="37" style="99" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
+    <col min="69" max="16384" width="9" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -57816,10 +57792,10 @@
       <c r="BH23" s="113"/>
       <c r="BI23" s="112"/>
       <c r="BL23" s="112" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="BN23" s="99" t="s">
         <v>173</v>
@@ -57993,44 +57969,44 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="99" width="9.0"/>
-    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
-    <col min="9" max="10" style="99" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
-    <col min="12" max="28" style="99" width="9.0"/>
-    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
-    <col min="32" max="34" style="99" width="9.0"/>
-    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
-    <col min="36" max="42" style="99" width="9.0"/>
-    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
-    <col min="45" max="45" style="99" width="9.0"/>
-    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
-    <col min="50" max="50" style="99" width="9.0"/>
-    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
-    <col min="54" max="59" style="99" width="9.0"/>
-    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
-    <col min="64" max="64" style="99" width="9.0"/>
-    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
-    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
-    <col min="69" max="16384" style="99" width="9.0"/>
+    <col min="1" max="1" width="9" style="99"/>
+    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
+    <col min="9" max="10" width="9" style="99"/>
+    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
+    <col min="12" max="28" width="9" style="99"/>
+    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
+    <col min="32" max="34" width="9" style="99"/>
+    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
+    <col min="36" max="42" width="9" style="99"/>
+    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
+    <col min="45" max="45" width="9" style="99"/>
+    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
+    <col min="50" max="50" width="9" style="99"/>
+    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
+    <col min="54" max="59" width="9" style="99"/>
+    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
+    <col min="64" max="64" width="9" style="99"/>
+    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
+    <col min="66" max="66" width="37" style="99" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
+    <col min="69" max="16384" width="9" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -59705,7 +59681,7 @@
         <v>108</v>
       </c>
       <c r="AV23" s="99" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AW23" s="112">
         <f>AM23</f>
@@ -59744,10 +59720,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -59767,10 +59743,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -59930,7 +59906,7 @@
         <v>108</v>
       </c>
       <c r="AV24" s="99" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AW24" s="112">
         <f>AM24</f>
@@ -59969,10 +59945,10 @@
         <v>148</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -60143,44 +60119,44 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="99" width="9.0"/>
-    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
-    <col min="9" max="10" style="99" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
-    <col min="12" max="28" style="99" width="9.0"/>
-    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
-    <col min="32" max="34" style="99" width="9.0"/>
-    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
-    <col min="36" max="42" style="99" width="9.0"/>
-    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
-    <col min="45" max="45" style="99" width="9.0"/>
-    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
-    <col min="50" max="50" style="99" width="9.0"/>
-    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
-    <col min="54" max="59" style="99" width="9.0"/>
-    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
-    <col min="64" max="64" style="99" width="9.0"/>
-    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
-    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
-    <col min="69" max="16384" style="99" width="9.0"/>
+    <col min="1" max="1" width="9" style="99"/>
+    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
+    <col min="9" max="10" width="9" style="99"/>
+    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
+    <col min="12" max="28" width="9" style="99"/>
+    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
+    <col min="32" max="34" width="9" style="99"/>
+    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
+    <col min="36" max="42" width="9" style="99"/>
+    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
+    <col min="45" max="45" width="9" style="99"/>
+    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
+    <col min="50" max="50" width="9" style="99"/>
+    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
+    <col min="54" max="59" width="9" style="99"/>
+    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
+    <col min="64" max="64" width="9" style="99"/>
+    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
+    <col min="66" max="66" width="37" style="99" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
+    <col min="69" max="16384" width="9" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -61851,11 +61827,11 @@
       <c r="AT23" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="99">
+      <c r="AU23" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="99">
-        <v>242</v>
+      <c r="AV23" s="99" t="s">
+        <v>240</v>
       </c>
       <c r="AW23" s="112">
         <f>AM23</f>
@@ -61893,11 +61869,11 @@
       <c r="BL23" s="112" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="99">
-        <v>250</v>
-      </c>
-      <c r="BN23" t="s" s="99">
-        <v>249</v>
+      <c r="BM23" s="99" t="s">
+        <v>242</v>
+      </c>
+      <c r="BN23" s="99" t="s">
+        <v>241</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -62068,7 +62044,7 @@
   <dimension ref="A8:BR37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="27.28515625"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:70" ht="15.75" thickBot="1"/>
@@ -62236,10 +62212,10 @@
       <c r="AT9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU9" t="s" s="0">
+      <c r="AU9" t="s">
         <v>127</v>
       </c>
-      <c r="AV9" t="s" s="0">
+      <c r="AV9" t="s">
         <v>143</v>
       </c>
       <c r="AW9" s="48">
@@ -62280,10 +62256,10 @@
       <c r="BL9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" t="s" s="0">
+      <c r="BM9" t="s">
         <v>146</v>
       </c>
-      <c r="BN9" t="s" s="0">
+      <c r="BN9" t="s">
         <v>147</v>
       </c>
       <c r="BO9" s="48" t="e">
@@ -62455,20 +62431,20 @@
       <c r="AQ15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR15" t="e" s="0">
+      <c r="AR15" t="e">
         <f>ROUND(AN15+AO15+AP15,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS15" t="s" s="0">
+      <c r="AS15" t="s">
         <v>107</v>
       </c>
       <c r="AT15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU15" t="s" s="0">
+      <c r="AU15" t="s">
         <v>131</v>
       </c>
-      <c r="AV15" t="s" s="0">
+      <c r="AV15" t="s">
         <v>149</v>
       </c>
       <c r="AW15" s="48">
@@ -62507,10 +62483,10 @@
       <c r="BL15" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM15" t="s" s="0">
+      <c r="BM15" t="s">
         <v>149</v>
       </c>
-      <c r="BN15" t="s" s="0">
+      <c r="BN15" t="s">
         <v>150</v>
       </c>
       <c r="BO15" s="48" t="e">
@@ -62680,20 +62656,20 @@
       <c r="AQ16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR16" s="0">
+      <c r="AR16">
         <f>ROUND(AN16+AO16+AP16,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS16" t="s" s="0">
+      <c r="AS16" t="s">
         <v>107</v>
       </c>
       <c r="AT16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU16" t="s" s="0">
+      <c r="AU16" t="s">
         <v>135</v>
       </c>
-      <c r="AV16" t="s" s="0">
+      <c r="AV16" t="s">
         <v>136</v>
       </c>
       <c r="AW16" s="48">
@@ -62732,10 +62708,10 @@
       <c r="BL16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM16" t="s" s="0">
+      <c r="BM16" t="s">
         <v>134</v>
       </c>
-      <c r="BN16" t="s" s="0">
+      <c r="BN16" t="s">
         <v>133</v>
       </c>
       <c r="BO16" s="48">
@@ -62905,20 +62881,20 @@
       <c r="AQ17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR17" s="0">
+      <c r="AR17">
         <f>ROUND(AN17+AO17+AP17,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS17" t="s" s="0">
+      <c r="AS17" t="s">
         <v>107</v>
       </c>
       <c r="AT17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU17" t="s" s="0">
+      <c r="AU17" t="s">
         <v>108</v>
       </c>
-      <c r="AV17" t="s" s="0">
+      <c r="AV17" t="s">
         <v>132</v>
       </c>
       <c r="AW17" s="48">
@@ -63124,20 +63100,20 @@
       <c r="AQ18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR18" s="0">
+      <c r="AR18">
         <f>ROUND(AN18+AO18+AP18,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS18" t="s" s="0">
+      <c r="AS18" t="s">
         <v>107</v>
       </c>
       <c r="AT18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU18" t="s" s="0">
+      <c r="AU18" t="s">
         <v>130</v>
       </c>
-      <c r="AV18" t="s" s="0">
+      <c r="AV18" t="s">
         <v>137</v>
       </c>
       <c r="AW18" s="48">
@@ -63176,10 +63152,10 @@
       <c r="BL18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM18" t="s" s="0">
+      <c r="BM18" t="s">
         <v>153</v>
       </c>
-      <c r="BN18" t="s" s="0">
+      <c r="BN18" t="s">
         <v>152</v>
       </c>
       <c r="BO18" s="48">
@@ -63350,20 +63326,20 @@
       <c r="AQ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR20" t="e" s="0">
+      <c r="AR20" t="e">
         <f>ROUND(AN20+AO20+AP20,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS20" t="s" s="0">
+      <c r="AS20" t="s">
         <v>107</v>
       </c>
       <c r="AT20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU20" t="s" s="0">
+      <c r="AU20" t="s">
         <v>155</v>
       </c>
-      <c r="AV20" t="s" s="0">
+      <c r="AV20" t="s">
         <v>156</v>
       </c>
       <c r="AW20" s="48">
@@ -63402,10 +63378,10 @@
       <c r="BL20" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM20" t="s" s="0">
+      <c r="BM20" t="s">
         <v>156</v>
       </c>
-      <c r="BN20" t="s" s="0">
+      <c r="BN20" t="s">
         <v>127</v>
       </c>
       <c r="BO20" s="48" t="e">
@@ -63575,20 +63551,20 @@
       <c r="AQ21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" t="e" s="0">
+      <c r="AR21" t="e">
         <f t="shared" ref="AR21:AR23" si="30">ROUND(AN21+AO21+AP21,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS21" t="s" s="0">
+      <c r="AS21" t="s">
         <v>107</v>
       </c>
       <c r="AT21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU21" t="s" s="0">
+      <c r="AU21" t="s">
         <v>131</v>
       </c>
-      <c r="AV21" t="s" s="0">
+      <c r="AV21" t="s">
         <v>157</v>
       </c>
       <c r="AW21" s="48">
@@ -63627,10 +63603,10 @@
       <c r="BL21" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM21" t="s" s="0">
+      <c r="BM21" t="s">
         <v>108</v>
       </c>
-      <c r="BN21" t="s" s="0">
+      <c r="BN21" t="s">
         <v>108</v>
       </c>
       <c r="BO21" s="48" t="e">
@@ -63800,20 +63776,20 @@
       <c r="AQ22" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR22" t="e" s="0">
+      <c r="AR22" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS22" t="s" s="0">
+      <c r="AS22" t="s">
         <v>107</v>
       </c>
       <c r="AT22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU22" t="s" s="0">
+      <c r="AU22" t="s">
         <v>158</v>
       </c>
-      <c r="AV22" t="s" s="0">
+      <c r="AV22" t="s">
         <v>159</v>
       </c>
       <c r="AW22" s="48">
@@ -63852,10 +63828,10 @@
       <c r="BL22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM22" t="s" s="0">
+      <c r="BM22" t="s">
         <v>108</v>
       </c>
-      <c r="BN22" t="s" s="0">
+      <c r="BN22" t="s">
         <v>108</v>
       </c>
       <c r="BO22" s="48" t="e">
@@ -64025,20 +64001,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" t="e" s="0">
+      <c r="AR23" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>160</v>
       </c>
       <c r="AW23" s="48">
@@ -64077,10 +64053,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>108</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>108</v>
       </c>
       <c r="BO23" s="48" t="e">
@@ -64137,14 +64113,14 @@
       <c r="F31" s="46">
         <v>2</v>
       </c>
-      <c r="G31" t="s" s="0">
+      <c r="G31" t="s">
         <v>128</v>
       </c>
       <c r="H31" s="46">
         <f>F31*G31</f>
         <v>600</v>
       </c>
-      <c r="I31" t="s" s="0">
+      <c r="I31" t="s">
         <v>127</v>
       </c>
       <c r="J31" s="46">
@@ -64272,20 +64248,20 @@
       <c r="AQ31" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR31" s="0">
+      <c r="AR31">
         <f>ROUND(AN31+AO31+AP31,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS31" t="s" s="0">
+      <c r="AS31" t="s">
         <v>107</v>
       </c>
       <c r="AT31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU31" t="s" s="0">
+      <c r="AU31" t="s">
         <v>162</v>
       </c>
-      <c r="AV31" t="s" s="0">
+      <c r="AV31" t="s">
         <v>167</v>
       </c>
       <c r="AW31" s="48">
@@ -64324,10 +64300,10 @@
       <c r="BL31" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM31" t="s" s="0">
+      <c r="BM31" t="s">
         <v>108</v>
       </c>
-      <c r="BN31" t="s" s="0">
+      <c r="BN31" t="s">
         <v>108</v>
       </c>
       <c r="BO31" s="48">
@@ -64362,14 +64338,14 @@
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" t="s" s="0">
+      <c r="G32" t="s">
         <v>129</v>
       </c>
       <c r="H32" s="46">
         <f>F32*G32</f>
         <v>800</v>
       </c>
-      <c r="I32" t="s" s="0">
+      <c r="I32" t="s">
         <v>127</v>
       </c>
       <c r="J32" s="46">
@@ -64497,20 +64473,20 @@
       <c r="AQ32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR32" s="0">
+      <c r="AR32">
         <f>ROUND(AN32+AO32+AP32,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS32" t="s" s="0">
+      <c r="AS32" t="s">
         <v>107</v>
       </c>
       <c r="AT32" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU32" t="s" s="0">
+      <c r="AU32" t="s">
         <v>168</v>
       </c>
-      <c r="AV32" t="s" s="0">
+      <c r="AV32" t="s">
         <v>169</v>
       </c>
       <c r="AW32" s="48">
@@ -64549,10 +64525,10 @@
       <c r="BL32" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM32" t="s" s="0">
+      <c r="BM32" t="s">
         <v>108</v>
       </c>
-      <c r="BN32" t="s" s="0">
+      <c r="BN32" t="s">
         <v>108</v>
       </c>
       <c r="BO32" s="48">
@@ -64587,14 +64563,14 @@
       <c r="F33" s="46">
         <v>2</v>
       </c>
-      <c r="G33" t="s" s="0">
+      <c r="G33" t="s">
         <v>161</v>
       </c>
       <c r="H33" s="46">
         <f>F33*G33</f>
         <v>1000</v>
       </c>
-      <c r="I33" t="s" s="0">
+      <c r="I33" t="s">
         <v>127</v>
       </c>
       <c r="J33" s="46">
@@ -64722,20 +64698,20 @@
       <c r="AQ33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR33" s="0">
+      <c r="AR33">
         <f>ROUND(AN33+AO33+AP33,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS33" t="s" s="0">
+      <c r="AS33" t="s">
         <v>107</v>
       </c>
       <c r="AT33" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU33" t="s" s="0">
+      <c r="AU33" t="s">
         <v>108</v>
       </c>
-      <c r="AV33" t="s" s="0">
+      <c r="AV33" t="s">
         <v>170</v>
       </c>
       <c r="AW33" s="48">
@@ -64774,10 +64750,10 @@
       <c r="BL33" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM33" t="s" s="0">
+      <c r="BM33" t="s">
         <v>108</v>
       </c>
-      <c r="BN33" t="s" s="0">
+      <c r="BN33" t="s">
         <v>108</v>
       </c>
       <c r="BO33" s="48">
@@ -64813,14 +64789,14 @@
       <c r="F35" s="46">
         <v>2</v>
       </c>
-      <c r="G35" t="s" s="0">
+      <c r="G35" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="46">
         <f>F35*G35</f>
         <v>600</v>
       </c>
-      <c r="I35" t="s" s="0">
+      <c r="I35" t="s">
         <v>127</v>
       </c>
       <c r="J35" s="46">
@@ -64948,20 +64924,20 @@
       <c r="AQ35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR35" s="0">
+      <c r="AR35">
         <f>ROUND(AN35+AO35+AP35,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS35" t="s" s="0">
+      <c r="AS35" t="s">
         <v>107</v>
       </c>
       <c r="AT35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU35" t="s" s="0">
+      <c r="AU35" t="s">
         <v>171</v>
       </c>
-      <c r="AV35" t="s" s="0">
+      <c r="AV35" t="s">
         <v>172</v>
       </c>
       <c r="AW35" s="48">
@@ -65000,10 +64976,10 @@
       <c r="BL35" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM35" t="s" s="0">
+      <c r="BM35" t="s">
         <v>108</v>
       </c>
-      <c r="BN35" t="s" s="0">
+      <c r="BN35" t="s">
         <v>108</v>
       </c>
       <c r="BO35" s="48">
@@ -65038,14 +65014,14 @@
       <c r="F36" s="46">
         <v>2</v>
       </c>
-      <c r="G36" t="s" s="0">
+      <c r="G36" t="s">
         <v>129</v>
       </c>
       <c r="H36" s="46">
         <f>F36*G36</f>
         <v>800</v>
       </c>
-      <c r="I36" t="s" s="0">
+      <c r="I36" t="s">
         <v>127</v>
       </c>
       <c r="J36" s="46">
@@ -65173,20 +65149,20 @@
       <c r="AQ36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR36" s="0">
+      <c r="AR36">
         <f>ROUND(AN36+AO36+AP36,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS36" t="s" s="0">
+      <c r="AS36" t="s">
         <v>107</v>
       </c>
       <c r="AT36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU36" t="s" s="0">
+      <c r="AU36" t="s">
         <v>173</v>
       </c>
-      <c r="AV36" t="s" s="0">
+      <c r="AV36" t="s">
         <v>174</v>
       </c>
       <c r="AW36" s="48">
@@ -65225,10 +65201,10 @@
       <c r="BL36" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM36" t="s" s="0">
+      <c r="BM36" t="s">
         <v>108</v>
       </c>
-      <c r="BN36" t="s" s="0">
+      <c r="BN36" t="s">
         <v>108</v>
       </c>
       <c r="BO36" s="48">
@@ -65263,14 +65239,14 @@
       <c r="F37" s="46">
         <v>2</v>
       </c>
-      <c r="G37" t="s" s="0">
+      <c r="G37" t="s">
         <v>161</v>
       </c>
       <c r="H37" s="46">
         <f>F37*G37</f>
         <v>1000</v>
       </c>
-      <c r="I37" t="s" s="0">
+      <c r="I37" t="s">
         <v>127</v>
       </c>
       <c r="J37" s="46">
@@ -65398,20 +65374,20 @@
       <c r="AQ37" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR37" s="0">
+      <c r="AR37">
         <f>ROUND(AN37+AO37+AP37,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS37" t="s" s="0">
+      <c r="AS37" t="s">
         <v>107</v>
       </c>
       <c r="AT37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU37" t="s" s="0">
+      <c r="AU37" t="s">
         <v>108</v>
       </c>
-      <c r="AV37" t="s" s="0">
+      <c r="AV37" t="s">
         <v>170</v>
       </c>
       <c r="AW37" s="48">
@@ -65450,10 +65426,10 @@
       <c r="BL37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM37" t="s" s="0">
+      <c r="BM37" t="s">
         <v>108</v>
       </c>
-      <c r="BN37" t="s" s="0">
+      <c r="BN37" t="s">
         <v>108</v>
       </c>
       <c r="BO37" s="48">
@@ -65479,34 +65455,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -67167,20 +67143,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -67219,10 +67195,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="0">
+      <c r="BM23" t="s">
         <v>149</v>
       </c>
-      <c r="BN23" t="s" s="0">
+      <c r="BN23" t="s">
         <v>155</v>
       </c>
       <c r="BO23" s="48">
@@ -67395,36 +67371,36 @@
   <dimension ref="A1:BU25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="26.85546875"/>
-    <col min="3" max="3" customWidth="true" width="19.28515625"/>
-    <col min="4" max="4" customWidth="true" width="80.42578125"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" customWidth="true" width="8.28515625"/>
-    <col min="7" max="7" customWidth="true" width="10.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="6.28515625"/>
-    <col min="18" max="18" customWidth="true" width="14.85546875"/>
-    <col min="29" max="29" customWidth="true" width="10.28515625"/>
-    <col min="30" max="30" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" customWidth="true" width="8.7109375"/>
-    <col min="35" max="35" customWidth="true" width="14.28515625"/>
-    <col min="43" max="43" customWidth="true" width="11.85546875"/>
-    <col min="44" max="44" customWidth="true" width="23.28515625"/>
-    <col min="46" max="46" customWidth="true" width="11.85546875"/>
-    <col min="47" max="47" customWidth="true" width="15.28515625"/>
-    <col min="48" max="48" customWidth="true" width="20.28515625"/>
-    <col min="49" max="49" customWidth="true" width="11.42578125"/>
-    <col min="51" max="51" customWidth="true" width="13.85546875"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="60" max="60" customWidth="true" width="12.5703125"/>
-    <col min="61" max="61" customWidth="true" width="21.7109375"/>
-    <col min="62" max="63" customWidth="true" width="30.5703125"/>
-    <col min="65" max="65" customWidth="true" width="41.140625"/>
-    <col min="66" max="66" customWidth="true" width="37.0"/>
-    <col min="67" max="67" customWidth="true" width="18.85546875"/>
-    <col min="68" max="68" customWidth="true" width="34.42578125"/>
-    <col min="71" max="71" customWidth="true" width="22.140625"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="80.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" customWidth="1"/>
+    <col min="29" max="29" width="10.28515625" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" customWidth="1"/>
+    <col min="43" max="43" width="11.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23.28515625" customWidth="1"/>
+    <col min="46" max="46" width="11.85546875" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" customWidth="1"/>
+    <col min="48" max="48" width="20.28515625" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" customWidth="1"/>
+    <col min="51" max="51" width="13.85546875" customWidth="1"/>
+    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.5703125" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" customWidth="1"/>
+    <col min="62" max="63" width="30.5703125" customWidth="1"/>
+    <col min="65" max="65" width="41.140625" customWidth="1"/>
+    <col min="66" max="66" width="37" customWidth="1"/>
+    <col min="67" max="67" width="18.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="71" max="71" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -69097,20 +69073,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" s="0">
+      <c r="AR23">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS23" t="s" s="0">
+      <c r="AS23" t="s">
         <v>188</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="0">
+      <c r="AU23" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="0">
+      <c r="AV23" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -69149,10 +69125,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" s="0">
+      <c r="BM23">
         <v>292.60462000000001</v>
       </c>
-      <c r="BN23" s="0">
+      <c r="BN23">
         <v>682</v>
       </c>
       <c r="BO23" s="48">
@@ -69176,7 +69152,7 @@
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s" s="0">
+      <c r="BU23" t="s">
         <v>204</v>
       </c>
     </row>

--- a/testdata/DirectGrnDetails.xlsx
+++ b/testdata/DirectGrnDetails.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="11" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="DirectGrnGenUD" sheetId="38" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5914" uniqueCount="251">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -593,9 +593,6 @@
     <t>846.99</t>
   </si>
   <si>
-    <t>1.334</t>
-  </si>
-  <si>
     <t>185.02695</t>
   </si>
   <si>
@@ -641,25 +638,7 @@
     <t>558.96</t>
   </si>
   <si>
-    <t>8.671</t>
-  </si>
-  <si>
-    <t>9.338</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>187.21935</t>
-  </si>
-  <si>
     <t>33.35</t>
-  </si>
-  <si>
-    <t>48.024</t>
-  </si>
-  <si>
-    <t>565.52002</t>
   </si>
   <si>
     <t>Cost</t>
@@ -702,12 +681,6 @@
   </si>
   <si>
     <t>558.95</t>
-  </si>
-  <si>
-    <t>234.783</t>
-  </si>
-  <si>
-    <t>564.71998</t>
   </si>
   <si>
     <t>186.318</t>
@@ -798,6 +771,51 @@
   </si>
   <si>
     <t>1382.93517</t>
+  </si>
+  <si>
+    <t>9599</t>
+  </si>
+  <si>
+    <t>488.12216</t>
+  </si>
+  <si>
+    <t>2098</t>
+  </si>
+  <si>
+    <t>187.24408</t>
+  </si>
+  <si>
+    <t>270.802</t>
+  </si>
+  <si>
+    <t>272.136</t>
+  </si>
+  <si>
+    <t>288.477</t>
+  </si>
+  <si>
+    <t>843.82914</t>
+  </si>
+  <si>
+    <t>570.48</t>
+  </si>
+  <si>
+    <t>324.137</t>
+  </si>
+  <si>
+    <t>564.55297</t>
+  </si>
+  <si>
+    <t>325.804</t>
+  </si>
+  <si>
+    <t>564.54791</t>
+  </si>
+  <si>
+    <t>272.803</t>
+  </si>
+  <si>
+    <t>273.47</t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1526,7 @@
       <sheetName val="Sheet3"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="21">
           <cell r="C21">
             <v>1</v>
@@ -1537,14 +1555,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1838,44 +1856,44 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="99"/>
-    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
-    <col min="9" max="10" width="9" style="99"/>
-    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
-    <col min="12" max="28" width="9" style="99"/>
-    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
-    <col min="32" max="34" width="9" style="99"/>
-    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
-    <col min="36" max="42" width="9" style="99"/>
-    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
-    <col min="45" max="45" width="9" style="99"/>
-    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
-    <col min="50" max="50" width="9" style="99"/>
-    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
-    <col min="54" max="59" width="9" style="99"/>
-    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
-    <col min="64" max="64" width="9" style="99"/>
-    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
-    <col min="66" max="66" width="37" style="99" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
-    <col min="69" max="16384" width="9" style="99"/>
+    <col min="1" max="1" style="99" width="9.0"/>
+    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
+    <col min="9" max="10" style="99" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
+    <col min="12" max="28" style="99" width="9.0"/>
+    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
+    <col min="32" max="34" style="99" width="9.0"/>
+    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
+    <col min="36" max="42" style="99" width="9.0"/>
+    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
+    <col min="45" max="45" style="99" width="9.0"/>
+    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
+    <col min="50" max="50" style="99" width="9.0"/>
+    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
+    <col min="54" max="59" style="99" width="9.0"/>
+    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
+    <col min="64" max="64" style="99" width="9.0"/>
+    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
+    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
+    <col min="69" max="16384" style="99" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -3382,7 +3400,7 @@
         <v>61</v>
       </c>
       <c r="BR22" s="118" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:70" ht="15.75" thickBot="1">
@@ -3390,10 +3408,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -3544,7 +3562,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT23" s="112" t="s">
         <v>12</v>
@@ -3592,10 +3610,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -3770,36 +3788,36 @@
   <dimension ref="A1:BU25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
-    <col min="71" max="71" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="18" max="18" customWidth="true" width="14.85546875"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="71" max="71" customWidth="true" width="22.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -5306,16 +5324,16 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="BS22" s="69" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="BT22" s="69" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="BU22" s="95" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:73" ht="15.75" thickBot="1">
@@ -5323,10 +5341,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -5472,20 +5490,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -5524,10 +5542,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23">
+      <c r="BM23" s="0">
         <v>292.60462000000001</v>
       </c>
-      <c r="BN23">
+      <c r="BN23" s="0">
         <v>682</v>
       </c>
       <c r="BO23" s="48">
@@ -5546,13 +5564,13 @@
         <v>400</v>
       </c>
       <c r="BS23" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s">
-        <v>204</v>
+      <c r="BU23" t="s" s="0">
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:73" ht="15.75" thickBot="1">
@@ -5712,41 +5730,41 @@
   <dimension ref="A1:CC25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="18" max="18" width="11.28515625" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="23.85546875" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="50" max="50" width="11" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
-    <col min="74" max="74" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="18" max="18" customWidth="true" width="11.28515625"/>
+    <col min="19" max="19" customWidth="true" width="11.140625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="23.85546875"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="50" max="50" customWidth="true" width="11.0"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="74" max="74" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="75" max="75" bestFit="true" customWidth="true" width="9.140625"/>
+    <col min="78" max="78" bestFit="true" customWidth="true" width="17.5703125"/>
+    <col min="79" max="79" bestFit="true" customWidth="true" width="14.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -7253,40 +7271,40 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="BS22" s="69" t="s">
+        <v>193</v>
+      </c>
+      <c r="BT22" s="69" t="s">
+        <v>194</v>
+      </c>
+      <c r="BU22" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="BV22" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="BW22" s="89" t="s">
         <v>199</v>
       </c>
-      <c r="BS22" s="69" t="s">
+      <c r="BX22" s="89" t="s">
         <v>200</v>
       </c>
-      <c r="BT22" s="69" t="s">
+      <c r="BY22" s="89" t="s">
         <v>201</v>
       </c>
-      <c r="BU22" s="95" t="s">
+      <c r="BZ22" s="89" t="s">
+        <v>202</v>
+      </c>
+      <c r="CA22" s="89" t="s">
         <v>203</v>
       </c>
-      <c r="BV22" s="89" t="s">
-        <v>205</v>
-      </c>
-      <c r="BW22" s="89" t="s">
-        <v>206</v>
-      </c>
-      <c r="BX22" s="89" t="s">
-        <v>207</v>
-      </c>
-      <c r="BY22" s="89" t="s">
-        <v>208</v>
-      </c>
-      <c r="BZ22" s="89" t="s">
+      <c r="CB22" s="89" t="s">
         <v>209</v>
       </c>
-      <c r="CA22" s="89" t="s">
+      <c r="CC22" s="89" t="s">
         <v>210</v>
-      </c>
-      <c r="CB22" s="89" t="s">
-        <v>218</v>
-      </c>
-      <c r="CC22" s="89" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:81" ht="15.75" thickBot="1">
@@ -7294,10 +7312,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -7308,14 +7326,14 @@
       <c r="F23" s="65">
         <v>5</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H23" s="65">
         <f>F23*G23</f>
         <v>1500</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="65">
@@ -7443,21 +7461,21 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>AN23+AO23+AP23</f>
         <v>279.476</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>215</v>
+      <c r="AV23" t="s" s="0">
+        <v>206</v>
       </c>
       <c r="AW23" s="66">
         <f>AM23</f>
@@ -7495,11 +7513,11 @@
       <c r="BL23" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>221</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>220</v>
+      <c r="BM23" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>211</v>
       </c>
       <c r="BO23" s="66">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -7517,24 +7535,24 @@
         <v>400</v>
       </c>
       <c r="BS23" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s">
-        <v>204</v>
-      </c>
-      <c r="BV23" t="s">
-        <v>216</v>
-      </c>
-      <c r="BW23" t="s">
-        <v>216</v>
-      </c>
-      <c r="BX23" t="s">
-        <v>217</v>
-      </c>
-      <c r="BY23" t="s">
+      <c r="BU23" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="BV23" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="BW23" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="BX23" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="BY23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="BZ23" s="97">
@@ -7709,40 +7727,40 @@
   <dimension ref="A1:CC25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="18" max="18" width="11.28515625" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="23.85546875" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="50" max="50" width="11" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
-    <col min="78" max="78" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="14" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="18" max="18" customWidth="true" width="11.28515625"/>
+    <col min="19" max="19" customWidth="true" width="11.140625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="23.85546875"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="50" max="50" customWidth="true" width="11.0"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="78" max="78" bestFit="true" customWidth="true" width="17.5703125"/>
+    <col min="79" max="79" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="81" max="81" bestFit="true" customWidth="true" width="17.28515625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -9249,40 +9267,40 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="BS22" s="69" t="s">
+        <v>193</v>
+      </c>
+      <c r="BT22" s="69" t="s">
+        <v>194</v>
+      </c>
+      <c r="BU22" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="BV22" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="BW22" s="89" t="s">
         <v>199</v>
       </c>
-      <c r="BS22" s="69" t="s">
+      <c r="BX22" s="89" t="s">
         <v>200</v>
       </c>
-      <c r="BT22" s="69" t="s">
+      <c r="BY22" s="89" t="s">
         <v>201</v>
       </c>
-      <c r="BU22" s="95" t="s">
+      <c r="BZ22" s="89" t="s">
+        <v>202</v>
+      </c>
+      <c r="CA22" s="89" t="s">
         <v>203</v>
       </c>
-      <c r="BV22" s="89" t="s">
-        <v>205</v>
-      </c>
-      <c r="BW22" s="89" t="s">
-        <v>206</v>
-      </c>
-      <c r="BX22" s="89" t="s">
-        <v>207</v>
-      </c>
-      <c r="BY22" s="89" t="s">
-        <v>208</v>
-      </c>
-      <c r="BZ22" s="89" t="s">
+      <c r="CB22" s="89" t="s">
         <v>209</v>
       </c>
-      <c r="CA22" s="89" t="s">
+      <c r="CC22" s="89" t="s">
         <v>210</v>
-      </c>
-      <c r="CB22" s="89" t="s">
-        <v>218</v>
-      </c>
-      <c r="CC22" s="89" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:81" ht="15.75" thickBot="1">
@@ -9290,10 +9308,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -9304,14 +9322,14 @@
       <c r="F23" s="46">
         <v>5</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>1500</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -9439,21 +9457,21 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>279.476</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>215</v>
+      <c r="AV23" t="s" s="0">
+        <v>206</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -9491,11 +9509,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>223</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>222</v>
+      <c r="BM23" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>213</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -9513,19 +9531,19 @@
         <v>400</v>
       </c>
       <c r="BS23" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s">
+      <c r="BU23" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="BV23" s="74" t="s">
         <v>204</v>
       </c>
-      <c r="BV23" s="74" t="s">
-        <v>211</v>
-      </c>
       <c r="BW23" s="74" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="BX23" s="74">
         <v>5</v>
@@ -9643,11 +9661,11 @@
       <c r="AQ24" s="56"/>
       <c r="AR24" s="56"/>
       <c r="AS24" s="8"/>
-      <c r="CB24">
+      <c r="CB24" s="0">
         <f>300*U23</f>
         <v>54</v>
       </c>
-      <c r="CC24">
+      <c r="CC24" s="0">
         <f>600*U23</f>
         <v>108</v>
       </c>
@@ -9715,32 +9733,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -11252,10 +11270,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -11401,20 +11419,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -11453,10 +11471,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>164</v>
       </c>
       <c r="BO23" s="48">
@@ -11631,32 +11649,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -13168,10 +13186,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -13317,12 +13335,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -13532,34 +13550,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -15071,10 +15089,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -15085,14 +15103,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -15220,21 +15238,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AT23" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="AV23" t="s" s="0">
         <v>188</v>
-      </c>
-      <c r="AT23" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="AU23" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>189</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -15272,10 +15290,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -15448,32 +15466,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -16985,10 +17003,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -16999,14 +17017,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -17054,26 +17072,26 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
         <v>50.82</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
         <v>50.82</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
+        <f>IF($C32=3,0,S23*Z23)</f>
         <v>33.879599999999996</v>
       </c>
       <c r="AB23" s="46">
@@ -17081,35 +17099,35 @@
         <v>135.5196</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
+        <f>IF($V32=1,S23+AB23,S23)</f>
         <v>564.66</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>564.66</v>
+        <f>S23*$M$21</f>
+        <v>28233</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -17121,7 +17139,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>282.33</v>
+        <v>14116.5</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -17134,12 +17152,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>282.33</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>14116.5</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -17150,7 +17168,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>282.33</v>
+        <v>14116.5</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -17158,7 +17176,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>282.33</v>
+        <v>14116.5</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -17182,7 +17200,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>282.33</v>
+        <v>14116.5</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -17268,7 +17286,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>564.66</v>
+        <v>28233</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -17349,34 +17367,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -18888,10 +18906,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -18902,14 +18920,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -19037,21 +19055,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV23" t="s">
-        <v>177</v>
+      <c r="AV23" t="s" s="0">
+        <v>176</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -19089,10 +19107,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>178</v>
-      </c>
-      <c r="BN23" t="s">
+      <c r="BM23" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="BN23" t="s" s="0">
         <v>131</v>
       </c>
       <c r="BO23" s="48">
@@ -19268,32 +19286,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -20805,10 +20823,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -20819,14 +20837,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -20874,26 +20892,26 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
+        <f>IF($C32=3,0,S23*Z23)</f>
         <v>2.2589999999999999</v>
       </c>
       <c r="AB23" s="46">
@@ -20901,35 +20919,35 @@
         <v>9.0389999999999997</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
+        <f>IF($V32=1,S23+AB23,S23)</f>
         <v>37.65</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>37.65</v>
+        <f>S23*$M$21</f>
+        <v>1882.5</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -20941,7 +20959,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -20954,12 +20972,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>18.824999999999999</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>941.25</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -20970,7 +20988,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -20978,7 +20996,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -21002,7 +21020,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -21088,7 +21106,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>37.65</v>
+        <v>1882.5</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -21170,34 +21188,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -22709,10 +22727,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -22723,14 +22741,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -22858,20 +22876,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW23" s="48">
@@ -22910,10 +22928,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48">
@@ -23088,44 +23106,44 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="99"/>
-    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
-    <col min="9" max="10" width="9" style="99"/>
-    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
-    <col min="12" max="28" width="9" style="99"/>
-    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
-    <col min="32" max="34" width="9" style="99"/>
-    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
-    <col min="36" max="42" width="9" style="99"/>
-    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
-    <col min="45" max="45" width="9" style="99"/>
-    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
-    <col min="50" max="50" width="9" style="99"/>
-    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
-    <col min="54" max="59" width="9" style="99"/>
-    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
-    <col min="64" max="64" width="9" style="99"/>
-    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
-    <col min="66" max="66" width="37" style="99" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
-    <col min="69" max="16384" width="9" style="99"/>
+    <col min="1" max="1" style="99" width="9.0"/>
+    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
+    <col min="9" max="10" style="99" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
+    <col min="12" max="28" style="99" width="9.0"/>
+    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
+    <col min="32" max="34" style="99" width="9.0"/>
+    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
+    <col min="36" max="42" style="99" width="9.0"/>
+    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
+    <col min="45" max="45" style="99" width="9.0"/>
+    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
+    <col min="50" max="50" style="99" width="9.0"/>
+    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
+    <col min="54" max="59" style="99" width="9.0"/>
+    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
+    <col min="64" max="64" style="99" width="9.0"/>
+    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
+    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
+    <col min="69" max="16384" style="99" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -24637,10 +24655,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -24791,7 +24809,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT23" s="112" t="s">
         <v>12</v>
@@ -24839,10 +24857,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -24862,10 +24880,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -25016,7 +25034,7 @@
         <v>282.33</v>
       </c>
       <c r="AS24" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT24" s="112" t="s">
         <v>12</v>
@@ -25064,10 +25082,10 @@
         <v>148</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -25238,34 +25256,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -26777,10 +26795,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -26791,14 +26809,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -26926,20 +26944,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>165</v>
       </c>
       <c r="AW23" s="48">
@@ -26978,10 +26996,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO23" s="48">
@@ -27156,32 +27174,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -28693,10 +28711,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -28707,14 +28725,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -28762,26 +28780,26 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
+        <f>IF($C32=3,0,S23*Z23)</f>
         <v>2.2589999999999999</v>
       </c>
       <c r="AB23" s="46">
@@ -28789,35 +28807,35 @@
         <v>9.0389999999999997</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
+        <f>IF($V32=1,S23+AB23,S23)</f>
         <v>37.65</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>37.65</v>
+        <f>S23*$M$21</f>
+        <v>1882.5</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -28829,7 +28847,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -28842,12 +28860,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>18.824999999999999</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>941.25</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -28858,7 +28876,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -28866,7 +28884,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -28890,7 +28908,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -28976,7 +28994,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>37.65</v>
+        <v>1882.5</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -29057,34 +29075,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -30596,10 +30614,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -30610,14 +30628,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -30745,21 +30763,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AT23" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="AV23" t="s" s="0">
         <v>188</v>
-      </c>
-      <c r="AT23" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="AU23" t="s">
-        <v>164</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>165</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -30797,11 +30815,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>163</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>127</v>
+      <c r="BM23" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>236</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -30975,32 +30993,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -32512,10 +32530,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -32526,14 +32544,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -32581,26 +32599,26 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
+        <f>IF($C32=3,0,S23*Z23)</f>
         <v>2.2589999999999999</v>
       </c>
       <c r="AB23" s="46">
@@ -32608,35 +32626,35 @@
         <v>9.0389999999999997</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
+        <f>IF($V32=1,S23+AB23,S23)</f>
         <v>37.65</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>37.65</v>
+        <f>S23*$M$21</f>
+        <v>1882.5</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -32648,7 +32666,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -32661,12 +32679,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>18.824999999999999</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>941.25</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -32677,7 +32695,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -32685,7 +32703,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -32709,7 +32727,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -32795,7 +32813,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>37.65</v>
+        <v>1882.5</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -32876,34 +32894,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -34415,10 +34433,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -34429,14 +34447,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -34564,21 +34582,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>186.32</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="AT23" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="AV23" t="s" s="0">
         <v>188</v>
-      </c>
-      <c r="AT23" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="AU23" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>189</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -34616,11 +34634,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>195</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>194</v>
+      <c r="BM23" t="s" s="0">
+        <v>239</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>238</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -34794,32 +34812,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -36331,10 +36349,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -36345,14 +36363,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -36400,26 +36418,26 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
+        <f>IF($C32=3,0,S23*Z23)</f>
         <v>2.2589999999999999</v>
       </c>
       <c r="AB23" s="46">
@@ -36427,35 +36445,35 @@
         <v>9.0389999999999997</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
+        <f>IF($V32=1,S23+AB23,S23)</f>
         <v>37.65</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>37.65</v>
+        <f>S23*$M$21</f>
+        <v>1882.5</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -36467,7 +36485,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -36480,12 +36498,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>18.824999999999999</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>941.25</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -36496,7 +36514,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -36504,7 +36522,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -36528,7 +36546,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -36614,7 +36632,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>37.65</v>
+        <v>1882.5</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -36695,34 +36713,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -38234,10 +38252,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -38383,20 +38401,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -38435,15 +38453,15 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>175</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>176</v>
+      <c r="BM23" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>242</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>846.99</v>
+        <v>843.82912999999996</v>
       </c>
       <c r="BP23" s="61">
         <f>ROUND((BN23+AW23),3)</f>
@@ -38610,34 +38628,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -40149,10 +40167,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -40298,20 +40316,20 @@
       <c r="AQ23" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>846.99</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>175</v>
       </c>
       <c r="AW23" s="48">
@@ -40350,11 +40368,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="BN23" t="s">
-        <v>196</v>
+      <c r="BN23" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -40525,32 +40543,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -42062,10 +42080,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -42076,14 +42094,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>162</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>40</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>115</v>
       </c>
       <c r="J23" s="46">
@@ -42131,26 +42149,26 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
+        <f>IF($C32=3,0,S23*Z23)</f>
         <v>2.2589999999999999</v>
       </c>
       <c r="AB23" s="46">
@@ -42158,35 +42176,35 @@
         <v>9.0389999999999997</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
+        <f>IF($V32=1,S23+AB23,S23)</f>
         <v>37.65</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>37.65</v>
+        <f>S23*$M$21</f>
+        <v>1882.5</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -42198,7 +42216,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -42211,12 +42229,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>18.824999999999999</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>941.25</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -42227,7 +42245,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -42235,7 +42253,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -42259,7 +42277,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -42345,7 +42363,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>37.65</v>
+        <v>1882.5</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -42426,34 +42444,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -43965,10 +43983,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -43979,14 +43997,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -44114,21 +44132,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>570.48</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>191</v>
+      <c r="AV23" t="s" s="0">
+        <v>244</v>
       </c>
       <c r="AW23" s="16">
         <f>AM23</f>
@@ -44166,11 +44184,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>198</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>197</v>
+      <c r="BM23" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>245</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -44341,44 +44359,44 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="99"/>
-    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
-    <col min="9" max="10" width="9" style="99"/>
-    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
-    <col min="12" max="28" width="9" style="99"/>
-    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
-    <col min="32" max="34" width="9" style="99"/>
-    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
-    <col min="36" max="42" width="9" style="99"/>
-    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
-    <col min="45" max="45" width="9" style="99"/>
-    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
-    <col min="50" max="50" width="9" style="99"/>
-    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
-    <col min="54" max="59" width="9" style="99"/>
-    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="99" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
-    <col min="66" max="66" width="37" style="99" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
-    <col min="69" max="16384" width="9" style="99"/>
+    <col min="1" max="1" style="99" width="9.0"/>
+    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
+    <col min="9" max="10" style="99" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
+    <col min="12" max="28" style="99" width="9.0"/>
+    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
+    <col min="32" max="34" style="99" width="9.0"/>
+    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
+    <col min="36" max="42" style="99" width="9.0"/>
+    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
+    <col min="45" max="45" style="99" width="9.0"/>
+    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
+    <col min="50" max="50" style="99" width="9.0"/>
+    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
+    <col min="54" max="59" style="99" width="9.0"/>
+    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="99" width="10.5703125"/>
+    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
+    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
+    <col min="69" max="16384" style="99" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -45890,10 +45908,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -46044,7 +46062,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT23" s="112" t="s">
         <v>12</v>
@@ -46089,13 +46107,13 @@
       <c r="BH23" s="113"/>
       <c r="BI23" s="112"/>
       <c r="BL23" s="112" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -46115,10 +46133,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -46269,7 +46287,7 @@
         <v>282.33</v>
       </c>
       <c r="AS24" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT24" s="112" t="s">
         <v>12</v>
@@ -46314,13 +46332,13 @@
       <c r="BH24" s="113"/>
       <c r="BI24" s="112"/>
       <c r="BL24" s="112" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -46491,34 +46509,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -48030,10 +48048,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -48044,14 +48062,14 @@
       <c r="F23" s="46">
         <v>3</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>600</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -48179,21 +48197,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>AN23+AO23+AP23</f>
         <v>558.95000000000005</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>212</v>
+      <c r="AV23" t="s" s="0">
+        <v>205</v>
       </c>
       <c r="AW23" s="48">
         <f>AM23</f>
@@ -48231,11 +48249,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>214</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>213</v>
+      <c r="BM23" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>247</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -48406,32 +48424,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -49943,10 +49961,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -49957,14 +49975,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -49979,31 +49997,31 @@
       </c>
       <c r="M23" s="46">
         <f>ROUND(L23*I23%,2)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N23" s="46">
         <f>H23-M23</f>
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O23" s="46">
         <f>ROUND(N23*J23%,2)</f>
-        <v>7.92</v>
+        <v>7.84</v>
       </c>
       <c r="P23" s="46">
         <f>ROUND(N23-O23,2)</f>
-        <v>388.08</v>
+        <v>384.16</v>
       </c>
       <c r="Q23" s="46">
         <f>ROUND(P23*K23%,2)</f>
-        <v>11.64</v>
+        <v>11.52</v>
       </c>
       <c r="R23" s="46">
         <f>M23+O23+Q23</f>
-        <v>23.560000000000002</v>
+        <v>27.36</v>
       </c>
       <c r="S23" s="46">
         <f>(H23-R23)</f>
-        <v>376.44</v>
+        <v>372.64</v>
       </c>
       <c r="T23" s="46" t="s">
         <v>151</v>
@@ -50012,62 +50030,62 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
-        <v>33.880000000000003</v>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <v>33.54</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
-        <v>33.880000000000003</v>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <v>33.54</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
-        <v>22.586399999999998</v>
+        <f>IF($C32=3,0,S23*Z23)</f>
+        <v>22.3584</v>
       </c>
       <c r="AB23" s="46">
         <f>V23+W23+X23+Y23+AA23</f>
-        <v>90.346400000000003</v>
+        <v>89.438400000000001</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
-        <v>376.44</v>
+        <f>IF($V32=1,S23+AB23,S23)</f>
+        <v>372.64</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>376.44</v>
+        <f>S23*$M$21</f>
+        <v>18632</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -50079,7 +50097,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>188.22</v>
+        <v>9316</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -50092,12 +50110,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>188.22</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>9316</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -50108,7 +50126,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>188.22</v>
+        <v>9316</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -50116,7 +50134,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>188.22</v>
+        <v>9316</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -50140,7 +50158,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>188.22</v>
+        <v>9316</v>
       </c>
       <c r="BP23" s="4">
         <f>ROUND((BN23+AW23),3)</f>
@@ -50176,21 +50194,21 @@
       <c r="Q24" s="45"/>
       <c r="R24" s="53">
         <f>SUM(R23:R23)</f>
-        <v>23.560000000000002</v>
+        <v>27.36</v>
       </c>
       <c r="S24" s="54">
         <f>SUM(S23:S23)</f>
-        <v>376.44</v>
+        <v>372.64</v>
       </c>
       <c r="T24" s="53"/>
       <c r="U24" s="53"/>
       <c r="V24" s="55">
         <f t="shared" ref="V24:AE24" si="1">SUM(V23:V23)</f>
-        <v>33.880000000000003</v>
+        <v>33.54</v>
       </c>
       <c r="W24" s="55">
         <f t="shared" si="1"/>
-        <v>33.880000000000003</v>
+        <v>33.54</v>
       </c>
       <c r="X24" s="55">
         <f t="shared" si="1"/>
@@ -50201,11 +50219,11 @@
       <c r="AA24" s="55"/>
       <c r="AB24" s="53">
         <f t="shared" si="1"/>
-        <v>90.346400000000003</v>
+        <v>89.438400000000001</v>
       </c>
       <c r="AC24" s="56">
         <f t="shared" si="1"/>
-        <v>376.44</v>
+        <v>372.64</v>
       </c>
       <c r="AD24" s="57">
         <f t="shared" si="1"/>
@@ -50226,7 +50244,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>376.44</v>
+        <v>18632</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -50307,34 +50325,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -51846,10 +51864,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -51860,14 +51878,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -51995,21 +52013,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>191</v>
+      <c r="AV23" t="s" s="0">
+        <v>190</v>
       </c>
       <c r="AW23" s="16">
         <f>AM23</f>
@@ -52047,11 +52065,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>191</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>193</v>
+      <c r="BM23" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>250</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -52225,34 +52243,34 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="36.0"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -53764,10 +53782,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -53778,14 +53796,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
         <v>400</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -53913,21 +53931,21 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>564.66</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
-        <v>191</v>
+      <c r="AV23" t="s" s="0">
+        <v>190</v>
       </c>
       <c r="AW23" s="16">
         <f>AM23</f>
@@ -53965,11 +53983,11 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
-        <v>191</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>192</v>
+      <c r="BM23" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="BN23" t="s" s="0">
+        <v>241</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -54143,32 +54161,32 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -55680,10 +55698,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -55694,14 +55712,14 @@
       <c r="F23" s="46">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="0">
         <v>109</v>
       </c>
       <c r="H23" s="46">
         <f>F23*G23</f>
-        <v>40</v>
-      </c>
-      <c r="I23" t="s">
+        <v>400</v>
+      </c>
+      <c r="I23" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J23" s="46">
@@ -55749,26 +55767,26 @@
         <v>0.18</v>
       </c>
       <c r="V23" s="46">
-        <f>IF(OR(DirectGrnMatUDD!$C$21=1,DirectGrnMatUDD!$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF(OR($C$21=1,$C$21=4),ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="W23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=1,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=1,ROUND(((S23*U23)/2),2),0)</f>
         <v>3.39</v>
       </c>
       <c r="X23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=2,ROUND(((S23*U23)),2),0)</f>
+        <f>IF($C$21=2,ROUND(((S23*U23)),2),0)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=4,ROUND(((S23*U23)/2),2),0)</f>
+        <f>IF($C$21=4,ROUND(((S23*U23)/2),2),0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="47">
         <v>0.06</v>
       </c>
       <c r="AA23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C32=3,0,S23*Z23)</f>
+        <f>IF($C32=3,0,S23*Z23)</f>
         <v>2.2589999999999999</v>
       </c>
       <c r="AB23" s="46">
@@ -55776,35 +55794,35 @@
         <v>9.0389999999999997</v>
       </c>
       <c r="AC23" s="46">
-        <f>IF([1]DirectGrnGenUD!$V32=1,S23+AB23,S23)</f>
+        <f>IF($V32=1,S23+AB23,S23)</f>
         <v>37.65</v>
       </c>
       <c r="AD23" s="46">
         <v>120</v>
       </c>
       <c r="AE23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$35,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$35)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$35,AD23/$AD$24*$E$35)</f>
         <v>0</v>
       </c>
       <c r="AF23" s="46"/>
       <c r="AG23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AH23" s="46">
-        <f>IF([1]DirectGrnGenUD!$P$21=1,(S23/[1]DirectGrnGenUD!$S$24)*[1]DirectGrnGenUD!$E$37,AD23/[1]DirectGrnGenUD!$AD$24*[1]DirectGrnGenUD!$E$37)</f>
+        <f>IF($P$21=1,(S23/$S$24)*$E$37,AD23/$AD$24*$E$37)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="46">
-        <f>S23*[1]DirectGrnGenUD!$M$21</f>
-        <v>37.65</v>
+        <f>S23*$M$21</f>
+        <v>1882.5</v>
       </c>
       <c r="AJ23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,0,AG23+AH23)</f>
+        <f>IF($C$21=3,0,AG23+AH23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="46">
-        <f>IF([1]DirectGrnGenUD!$C$21=3,AE23+AG23+AH23,0)</f>
+        <f>IF($C$21=3,AE23+AG23+AH23,0)</f>
         <v>0</v>
       </c>
       <c r="AL23" s="46">
@@ -55816,7 +55834,7 @@
       </c>
       <c r="AN23" s="46">
         <f>AI23/AM23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AO23" s="46">
         <f>AJ23/AM23</f>
@@ -55829,12 +55847,12 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
-        <v>18.824999999999999</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+        <v>941.25</v>
+      </c>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
@@ -55845,7 +55863,7 @@
       </c>
       <c r="AX23" s="48">
         <f>AR23</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="AY23" s="48">
         <f>AU23+AW23</f>
@@ -55853,7 +55871,7 @@
       </c>
       <c r="AZ23" s="48">
         <f>ROUND(((AU23*AV23)+(AW23*AX23))/(AU23+AW23),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3" t="s">
@@ -55877,7 +55895,7 @@
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
-        <v>18.824999999999999</v>
+        <v>941.25</v>
       </c>
       <c r="BP23" s="4">
         <f>BN23+AW23</f>
@@ -55963,7 +55981,7 @@
       </c>
       <c r="AI24" s="57">
         <f>SUM(AI23:AI23)</f>
-        <v>37.65</v>
+        <v>1882.5</v>
       </c>
       <c r="AJ24" s="57">
         <f>SUM(AJ23:AJ23)</f>
@@ -56044,44 +56062,44 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="99"/>
-    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
-    <col min="9" max="10" width="9" style="99"/>
-    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
-    <col min="12" max="28" width="9" style="99"/>
-    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
-    <col min="32" max="34" width="9" style="99"/>
-    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
-    <col min="36" max="42" width="9" style="99"/>
-    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
-    <col min="45" max="45" width="9" style="99"/>
-    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
-    <col min="50" max="50" width="9" style="99"/>
-    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
-    <col min="54" max="59" width="9" style="99"/>
-    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="99" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
-    <col min="66" max="66" width="37" style="99" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
-    <col min="69" max="16384" width="9" style="99"/>
+    <col min="1" max="1" style="99" width="9.0"/>
+    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
+    <col min="9" max="10" style="99" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
+    <col min="12" max="28" style="99" width="9.0"/>
+    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
+    <col min="32" max="34" style="99" width="9.0"/>
+    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
+    <col min="36" max="42" style="99" width="9.0"/>
+    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
+    <col min="45" max="45" style="99" width="9.0"/>
+    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
+    <col min="50" max="50" style="99" width="9.0"/>
+    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
+    <col min="54" max="59" style="99" width="9.0"/>
+    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="99" width="10.5703125"/>
+    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
+    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
+    <col min="69" max="16384" style="99" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -57593,10 +57611,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -57747,7 +57765,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT23" s="112" t="s">
         <v>12</v>
@@ -57792,10 +57810,10 @@
       <c r="BH23" s="113"/>
       <c r="BI23" s="112"/>
       <c r="BL23" s="112" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="BN23" s="99" t="s">
         <v>173</v>
@@ -57969,44 +57987,44 @@
   <dimension ref="A1:BR26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="99"/>
-    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
-    <col min="9" max="10" width="9" style="99"/>
-    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
-    <col min="12" max="28" width="9" style="99"/>
-    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
-    <col min="32" max="34" width="9" style="99"/>
-    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
-    <col min="36" max="42" width="9" style="99"/>
-    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
-    <col min="45" max="45" width="9" style="99"/>
-    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
-    <col min="50" max="50" width="9" style="99"/>
-    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
-    <col min="54" max="59" width="9" style="99"/>
-    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
-    <col min="64" max="64" width="9" style="99"/>
-    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
-    <col min="66" max="66" width="37" style="99" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
-    <col min="69" max="16384" width="9" style="99"/>
+    <col min="1" max="1" style="99" width="9.0"/>
+    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
+    <col min="9" max="10" style="99" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
+    <col min="12" max="28" style="99" width="9.0"/>
+    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
+    <col min="32" max="34" style="99" width="9.0"/>
+    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
+    <col min="36" max="42" style="99" width="9.0"/>
+    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
+    <col min="45" max="45" style="99" width="9.0"/>
+    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
+    <col min="50" max="50" style="99" width="9.0"/>
+    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
+    <col min="54" max="59" style="99" width="9.0"/>
+    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
+    <col min="64" max="64" style="99" width="9.0"/>
+    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
+    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
+    <col min="69" max="16384" style="99" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -59518,10 +59536,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -59672,7 +59690,7 @@
         <v>282.33</v>
       </c>
       <c r="AS23" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT23" s="112" t="s">
         <v>12</v>
@@ -59681,7 +59699,7 @@
         <v>108</v>
       </c>
       <c r="AV23" s="99" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AW23" s="112">
         <f>AM23</f>
@@ -59720,10 +59738,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -59743,10 +59761,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -59897,7 +59915,7 @@
         <v>282.33</v>
       </c>
       <c r="AS24" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT24" s="112" t="s">
         <v>12</v>
@@ -59906,7 +59924,7 @@
         <v>108</v>
       </c>
       <c r="AV24" s="99" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AW24" s="112">
         <f>AM24</f>
@@ -59945,10 +59963,10 @@
         <v>148</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -60119,44 +60137,44 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="99"/>
-    <col min="2" max="2" width="26.85546875" style="99" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="99" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" style="99" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="99" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="99" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="99" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="99" customWidth="1"/>
-    <col min="9" max="10" width="9" style="99"/>
-    <col min="11" max="11" width="6.28515625" style="99" customWidth="1"/>
-    <col min="12" max="28" width="9" style="99"/>
-    <col min="29" max="29" width="10.28515625" style="99" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="99" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="99" customWidth="1"/>
-    <col min="32" max="34" width="9" style="99"/>
-    <col min="35" max="35" width="14.28515625" style="99" customWidth="1"/>
-    <col min="36" max="42" width="9" style="99"/>
-    <col min="43" max="43" width="11.85546875" style="99" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" style="99" customWidth="1"/>
-    <col min="45" max="45" width="9" style="99"/>
-    <col min="46" max="46" width="11.85546875" style="99" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" style="99" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" style="99" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" style="99" customWidth="1"/>
-    <col min="50" max="50" width="9" style="99"/>
-    <col min="51" max="51" width="13.85546875" style="99" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" style="99" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" style="99" bestFit="1" customWidth="1"/>
-    <col min="54" max="59" width="9" style="99"/>
-    <col min="60" max="60" width="12.5703125" style="99" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" style="99" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" style="99" customWidth="1"/>
-    <col min="64" max="64" width="9" style="99"/>
-    <col min="65" max="65" width="41.140625" style="99" customWidth="1"/>
-    <col min="66" max="66" width="37" style="99" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" style="99" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" style="99" customWidth="1"/>
-    <col min="69" max="16384" width="9" style="99"/>
+    <col min="1" max="1" style="99" width="9.0"/>
+    <col min="2" max="2" customWidth="true" style="99" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" style="99" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" style="99" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" style="99" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" style="99" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" style="99" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" style="99" width="11.85546875"/>
+    <col min="9" max="10" style="99" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="99" width="6.28515625"/>
+    <col min="12" max="28" style="99" width="9.0"/>
+    <col min="29" max="29" customWidth="true" style="99" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" style="99" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" style="99" width="8.7109375"/>
+    <col min="32" max="34" style="99" width="9.0"/>
+    <col min="35" max="35" customWidth="true" style="99" width="14.28515625"/>
+    <col min="36" max="42" style="99" width="9.0"/>
+    <col min="43" max="43" customWidth="true" style="99" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" style="99" width="23.28515625"/>
+    <col min="45" max="45" style="99" width="9.0"/>
+    <col min="46" max="46" customWidth="true" style="99" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" style="99" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" style="99" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" style="99" width="11.42578125"/>
+    <col min="50" max="50" style="99" width="9.0"/>
+    <col min="51" max="51" customWidth="true" style="99" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="99" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="99" width="19.0"/>
+    <col min="54" max="59" style="99" width="9.0"/>
+    <col min="60" max="60" customWidth="true" style="99" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" style="99" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" style="99" width="30.5703125"/>
+    <col min="64" max="64" style="99" width="9.0"/>
+    <col min="65" max="65" customWidth="true" style="99" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" style="99" width="37.0"/>
+    <col min="67" max="67" customWidth="true" style="99" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" style="99" width="34.42578125"/>
+    <col min="69" max="16384" style="99" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -61668,10 +61686,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -61822,7 +61840,7 @@
         <v>28.23</v>
       </c>
       <c r="AS23" s="99" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT23" s="112" t="s">
         <v>12</v>
@@ -61831,7 +61849,7 @@
         <v>108</v>
       </c>
       <c r="AV23" s="99" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AW23" s="112">
         <f>AM23</f>
@@ -61870,10 +61888,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -62044,7 +62062,7 @@
   <dimension ref="A8:BR37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="27.28515625"/>
   </cols>
   <sheetData>
     <row r="8" spans="1:70" ht="15.75" thickBot="1"/>
@@ -62212,10 +62230,10 @@
       <c r="AT9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU9" t="s">
+      <c r="AU9" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AV9" t="s" s="0">
         <v>143</v>
       </c>
       <c r="AW9" s="48">
@@ -62256,10 +62274,10 @@
       <c r="BL9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" t="s">
+      <c r="BM9" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BN9" t="s" s="0">
         <v>147</v>
       </c>
       <c r="BO9" s="48" t="e">
@@ -62431,20 +62449,20 @@
       <c r="AQ15" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR15" t="e">
+      <c r="AR15" t="e" s="0">
         <f>ROUND(AN15+AO15+AP15,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS15" t="s">
+      <c r="AS15" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU15" t="s">
+      <c r="AU15" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV15" t="s">
+      <c r="AV15" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW15" s="48">
@@ -62483,10 +62501,10 @@
       <c r="BL15" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM15" t="s">
+      <c r="BM15" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN15" t="s">
+      <c r="BN15" t="s" s="0">
         <v>150</v>
       </c>
       <c r="BO15" s="48" t="e">
@@ -62656,20 +62674,20 @@
       <c r="AQ16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="0">
         <f>ROUND(AN16+AO16+AP16,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS16" t="s">
+      <c r="AS16" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU16" t="s">
+      <c r="AU16" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="AV16" t="s">
+      <c r="AV16" t="s" s="0">
         <v>136</v>
       </c>
       <c r="AW16" s="48">
@@ -62708,10 +62726,10 @@
       <c r="BL16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM16" t="s">
+      <c r="BM16" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="BN16" t="s">
+      <c r="BN16" t="s" s="0">
         <v>133</v>
       </c>
       <c r="BO16" s="48">
@@ -62881,20 +62899,20 @@
       <c r="AQ17" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR17">
+      <c r="AR17" s="0">
         <f>ROUND(AN17+AO17+AP17,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS17" t="s">
+      <c r="AS17" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT17" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU17" t="s">
+      <c r="AU17" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AV17" t="s" s="0">
         <v>132</v>
       </c>
       <c r="AW17" s="48">
@@ -63100,20 +63118,20 @@
       <c r="AQ18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR18">
+      <c r="AR18" s="0">
         <f>ROUND(AN18+AO18+AP18,5)</f>
         <v>234.33</v>
       </c>
-      <c r="AS18" t="s">
+      <c r="AS18" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT18" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU18" t="s">
+      <c r="AU18" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="AV18" t="s">
+      <c r="AV18" t="s" s="0">
         <v>137</v>
       </c>
       <c r="AW18" s="48">
@@ -63152,10 +63170,10 @@
       <c r="BL18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="BM18" t="s">
+      <c r="BM18" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="BN18" t="s">
+      <c r="BN18" t="s" s="0">
         <v>152</v>
       </c>
       <c r="BO18" s="48">
@@ -63326,20 +63344,20 @@
       <c r="AQ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR20" t="e">
+      <c r="AR20" t="e" s="0">
         <f>ROUND(AN20+AO20+AP20,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS20" t="s">
+      <c r="AS20" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT20" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU20" t="s">
+      <c r="AU20" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="AV20" t="s">
+      <c r="AV20" t="s" s="0">
         <v>156</v>
       </c>
       <c r="AW20" s="48">
@@ -63378,10 +63396,10 @@
       <c r="BL20" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM20" t="s">
+      <c r="BM20" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="BN20" t="s">
+      <c r="BN20" t="s" s="0">
         <v>127</v>
       </c>
       <c r="BO20" s="48" t="e">
@@ -63551,20 +63569,20 @@
       <c r="AQ21" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR21" t="e">
+      <c r="AR21" t="e" s="0">
         <f t="shared" ref="AR21:AR23" si="30">ROUND(AN21+AO21+AP21,5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS21" t="s">
+      <c r="AS21" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU21" t="s">
+      <c r="AU21" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="AV21" t="s">
+      <c r="AV21" t="s" s="0">
         <v>157</v>
       </c>
       <c r="AW21" s="48">
@@ -63603,10 +63621,10 @@
       <c r="BL21" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM21" t="s">
+      <c r="BM21" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN21" t="s">
+      <c r="BN21" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO21" s="48" t="e">
@@ -63776,20 +63794,20 @@
       <c r="AQ22" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR22" t="e">
+      <c r="AR22" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS22" t="s">
+      <c r="AS22" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT22" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU22" t="s">
+      <c r="AU22" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="AV22" t="s">
+      <c r="AV22" t="s" s="0">
         <v>159</v>
       </c>
       <c r="AW22" s="48">
@@ -63828,10 +63846,10 @@
       <c r="BL22" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM22" t="s">
+      <c r="BM22" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN22" t="s">
+      <c r="BN22" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO22" s="48" t="e">
@@ -64001,20 +64019,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23" t="e">
+      <c r="AR23" t="e" s="0">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AS23" t="s">
+      <c r="AS23" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>160</v>
       </c>
       <c r="AW23" s="48">
@@ -64053,10 +64071,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO23" s="48" t="e">
@@ -64113,14 +64131,14 @@
       <c r="F31" s="46">
         <v>2</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H31" s="46">
         <f>F31*G31</f>
         <v>600</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J31" s="46">
@@ -64248,20 +64266,20 @@
       <c r="AQ31" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR31">
+      <c r="AR31" s="0">
         <f>ROUND(AN31+AO31+AP31,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS31" t="s">
+      <c r="AS31" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT31" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU31" t="s">
+      <c r="AU31" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="AV31" t="s">
+      <c r="AV31" t="s" s="0">
         <v>167</v>
       </c>
       <c r="AW31" s="48">
@@ -64300,10 +64318,10 @@
       <c r="BL31" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM31" t="s">
+      <c r="BM31" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN31" t="s">
+      <c r="BN31" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO31" s="48">
@@ -64338,14 +64356,14 @@
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H32" s="46">
         <f>F32*G32</f>
         <v>800</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J32" s="46">
@@ -64473,20 +64491,20 @@
       <c r="AQ32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR32">
+      <c r="AR32" s="0">
         <f>ROUND(AN32+AO32+AP32,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS32" t="s">
+      <c r="AS32" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT32" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU32" t="s">
+      <c r="AU32" t="s" s="0">
         <v>168</v>
       </c>
-      <c r="AV32" t="s">
+      <c r="AV32" t="s" s="0">
         <v>169</v>
       </c>
       <c r="AW32" s="48">
@@ -64525,10 +64543,10 @@
       <c r="BL32" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM32" t="s">
+      <c r="BM32" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN32" t="s">
+      <c r="BN32" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO32" s="48">
@@ -64563,14 +64581,14 @@
       <c r="F33" s="46">
         <v>2</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H33" s="46">
         <f>F33*G33</f>
         <v>1000</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J33" s="46">
@@ -64698,20 +64716,20 @@
       <c r="AQ33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR33">
+      <c r="AR33" s="0">
         <f>ROUND(AN33+AO33+AP33,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS33" t="s">
+      <c r="AS33" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT33" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU33" t="s">
+      <c r="AU33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV33" t="s">
+      <c r="AV33" t="s" s="0">
         <v>170</v>
       </c>
       <c r="AW33" s="48">
@@ -64750,10 +64768,10 @@
       <c r="BL33" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM33" t="s">
+      <c r="BM33" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN33" t="s">
+      <c r="BN33" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO33" s="48">
@@ -64789,14 +64807,14 @@
       <c r="F35" s="46">
         <v>2</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" t="s" s="0">
         <v>128</v>
       </c>
       <c r="H35" s="46">
         <f>F35*G35</f>
         <v>600</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J35" s="46">
@@ -64924,20 +64942,20 @@
       <c r="AQ35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR35">
+      <c r="AR35" s="0">
         <f>ROUND(AN35+AO35+AP35,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS35" t="s">
+      <c r="AS35" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT35" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU35" t="s">
+      <c r="AU35" t="s" s="0">
         <v>171</v>
       </c>
-      <c r="AV35" t="s">
+      <c r="AV35" t="s" s="0">
         <v>172</v>
       </c>
       <c r="AW35" s="48">
@@ -64976,10 +64994,10 @@
       <c r="BL35" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM35" t="s">
+      <c r="BM35" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN35" t="s">
+      <c r="BN35" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO35" s="48">
@@ -65014,14 +65032,14 @@
       <c r="F36" s="46">
         <v>2</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" t="s" s="0">
         <v>129</v>
       </c>
       <c r="H36" s="46">
         <f>F36*G36</f>
         <v>800</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J36" s="46">
@@ -65149,20 +65167,20 @@
       <c r="AQ36" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR36">
+      <c r="AR36" s="0">
         <f>ROUND(AN36+AO36+AP36,5)</f>
         <v>372.63499999999999</v>
       </c>
-      <c r="AS36" t="s">
+      <c r="AS36" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU36" t="s">
+      <c r="AU36" t="s" s="0">
         <v>173</v>
       </c>
-      <c r="AV36" t="s">
+      <c r="AV36" t="s" s="0">
         <v>174</v>
       </c>
       <c r="AW36" s="48">
@@ -65201,10 +65219,10 @@
       <c r="BL36" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM36" t="s">
+      <c r="BM36" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN36" t="s">
+      <c r="BN36" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO36" s="48">
@@ -65239,14 +65257,14 @@
       <c r="F37" s="46">
         <v>2</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" t="s" s="0">
         <v>161</v>
       </c>
       <c r="H37" s="46">
         <f>F37*G37</f>
         <v>1000</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" t="s" s="0">
         <v>127</v>
       </c>
       <c r="J37" s="46">
@@ -65374,20 +65392,20 @@
       <c r="AQ37" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR37">
+      <c r="AR37" s="0">
         <f>ROUND(AN37+AO37+AP37,5)</f>
         <v>465.79500000000002</v>
       </c>
-      <c r="AS37" t="s">
+      <c r="AS37" t="s" s="0">
         <v>107</v>
       </c>
       <c r="AT37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU37" t="s">
+      <c r="AU37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV37" t="s">
+      <c r="AV37" t="s" s="0">
         <v>170</v>
       </c>
       <c r="AW37" s="48">
@@ -65426,10 +65444,10 @@
       <c r="BL37" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM37" t="s">
+      <c r="BM37" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BN37" t="s">
+      <c r="BN37" t="s" s="0">
         <v>108</v>
       </c>
       <c r="BO37" s="48">
@@ -65455,34 +65473,34 @@
   <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -66994,10 +67012,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -67143,20 +67161,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>282.33</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -67195,10 +67213,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s">
+      <c r="BM23" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="BN23" t="s">
+      <c r="BN23" t="s" s="0">
         <v>155</v>
       </c>
       <c r="BO23" s="48">
@@ -67371,36 +67389,36 @@
   <dimension ref="A1:BU25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="80.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" customWidth="1"/>
-    <col min="43" max="43" width="11.85546875" customWidth="1"/>
-    <col min="44" max="44" width="23.28515625" customWidth="1"/>
-    <col min="46" max="46" width="11.85546875" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" customWidth="1"/>
-    <col min="48" max="48" width="20.28515625" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" customWidth="1"/>
-    <col min="51" max="51" width="13.85546875" customWidth="1"/>
-    <col min="52" max="52" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.5703125" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" customWidth="1"/>
-    <col min="62" max="63" width="30.5703125" customWidth="1"/>
-    <col min="65" max="65" width="41.140625" customWidth="1"/>
-    <col min="66" max="66" width="37" customWidth="1"/>
-    <col min="67" max="67" width="18.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.42578125" customWidth="1"/>
-    <col min="71" max="71" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="26.85546875"/>
+    <col min="3" max="3" customWidth="true" width="19.28515625"/>
+    <col min="4" max="4" customWidth="true" width="80.42578125"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" customWidth="true" width="8.28515625"/>
+    <col min="7" max="7" customWidth="true" width="10.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="6.28515625"/>
+    <col min="18" max="18" customWidth="true" width="14.85546875"/>
+    <col min="29" max="29" customWidth="true" width="10.28515625"/>
+    <col min="30" max="30" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" customWidth="true" width="8.7109375"/>
+    <col min="35" max="35" customWidth="true" width="14.28515625"/>
+    <col min="43" max="43" customWidth="true" width="11.85546875"/>
+    <col min="44" max="44" customWidth="true" width="23.28515625"/>
+    <col min="46" max="46" customWidth="true" width="11.85546875"/>
+    <col min="47" max="47" customWidth="true" width="15.28515625"/>
+    <col min="48" max="48" customWidth="true" width="20.28515625"/>
+    <col min="49" max="49" customWidth="true" width="11.42578125"/>
+    <col min="51" max="51" customWidth="true" width="13.85546875"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" width="18.85546875"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="60" max="60" customWidth="true" width="12.5703125"/>
+    <col min="61" max="61" customWidth="true" width="21.7109375"/>
+    <col min="62" max="63" customWidth="true" width="30.5703125"/>
+    <col min="65" max="65" customWidth="true" width="41.140625"/>
+    <col min="66" max="66" customWidth="true" width="37.0"/>
+    <col min="67" max="67" customWidth="true" width="18.85546875"/>
+    <col min="68" max="68" customWidth="true" width="34.42578125"/>
+    <col min="71" max="71" customWidth="true" width="22.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="18">
@@ -68907,16 +68925,16 @@
         <v>61</v>
       </c>
       <c r="BR22" s="69" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="BS22" s="69" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="BT22" s="69" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="BU22" s="95" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:73" ht="15.75" thickBot="1">
@@ -68924,10 +68942,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>12</v>
@@ -69073,20 +69091,20 @@
       <c r="AQ23" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="0">
         <f>ROUND(AN23+AO23+AP23,5)</f>
         <v>279.47500000000002</v>
       </c>
-      <c r="AS23" t="s">
-        <v>188</v>
+      <c r="AS23" t="s" s="0">
+        <v>187</v>
       </c>
       <c r="AT23" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s">
+      <c r="AU23" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AV23" t="s" s="0">
         <v>149</v>
       </c>
       <c r="AW23" s="48">
@@ -69125,10 +69143,10 @@
       <c r="BL23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="BM23">
+      <c r="BM23" s="0">
         <v>292.60462000000001</v>
       </c>
-      <c r="BN23">
+      <c r="BN23" s="0">
         <v>682</v>
       </c>
       <c r="BO23" s="48">
@@ -69147,13 +69165,13 @@
         <v>400</v>
       </c>
       <c r="BS23" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="BT23" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="BU23" t="s">
-        <v>204</v>
+      <c r="BU23" t="s" s="0">
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:73" ht="15.75" thickBot="1">
